--- a/tame_output/ON/bt/strategyON_20240812.xlsx
+++ b/tame_output/ON/bt/strategyON_20240812.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>55.2%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.1%</t>
+          <t>110.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>124.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-13.6%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.5%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.8%</t>
+          <t>430.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-636.9%</t>
+          <t>-634.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.4%</t>
+          <t>-156.7%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-313.4%</t>
+          <t>-327.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-157.1%</t>
+          <t>-157.2%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>83.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.0%</t>
         </is>
       </c>
     </row>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213492</v>
+        <v>3.223539378213493</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382324</v>
+        <v>3.235981977382325</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.29913614634705</v>
+        <v>3.299136146347051</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130012</v>
+        <v>3.287377576130013</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178238</v>
+        <v>3.315884374178239</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310977</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309419</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.3047157169709</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770576</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615279</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812098</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646213</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611564</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017768</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987899</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409203</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792048</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011494</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632777</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942105</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111297</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803193</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.05391335184853</v>
+        <v>-3.963841082329828</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.012334292808112</v>
+        <v>1.048363200615594</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6353796455330524</v>
+        <v>0.7053048553229899</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.015483845181103</v>
+        <v>3.057438971055066</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.162527430291862</v>
+        <v>-4.072455160773159</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.089038322149986</v>
+        <v>1.125067229957467</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6353796455330524</v>
+        <v>0.7053048553229899</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.135633505900309</v>
+        <v>3.177588631774272</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.127118392043719</v>
+        <v>-4.037046122525016</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.117714963551566</v>
+        <v>1.153743871359047</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6353796455330524</v>
+        <v>0.7053048553229899</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.150146532002632</v>
+        <v>3.192101657876595</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.088734729485568</v>
+        <v>-3.998662459966865</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.130487869917195</v>
+        <v>1.166516777724676</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6737633080912035</v>
+        <v>0.7436885178811411</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.170596170879892</v>
+        <v>3.212551296753854</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532487</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.911618399450401</v>
+        <v>-3.821546129931699</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.198063430776563</v>
+        <v>1.234092338584044</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6737633080912035</v>
+        <v>0.7436885178811411</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.167325199725194</v>
+        <v>3.209280325599156</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.956710644283947</v>
+        <v>-3.866638374765245</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.180709924605058</v>
+        <v>1.216738832412539</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6118672649218138</v>
+        <v>0.6817924747117513</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.130870965585473</v>
+        <v>3.172826091459435</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.77733522304518</v>
+        <v>-3.687262953526477</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.24624706840698</v>
+        <v>1.282275976214461</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7686440230925324</v>
+        <v>0.83856923288247</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.218723995794318</v>
+        <v>3.260679121668281</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.822349436565786</v>
+        <v>-3.732277167047083</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.209048838330327</v>
+        <v>1.245077746137808</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7382951277779278</v>
+        <v>0.8082203375678654</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.181322113937145</v>
+        <v>3.223277239811108</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.089353946838221</v>
+        <v>-3.999281677319519</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.107938596560298</v>
+        <v>1.143967504367779</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5439320897349793</v>
+        <v>0.6138572995249167</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.070395853450322</v>
+        <v>3.112350979324285</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.190551728275394</v>
+        <v>-4.100479458756691</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.066663405881931</v>
+        <v>1.102692313689412</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4755232761896601</v>
+        <v>0.5454484859795976</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.028554487219632</v>
+        <v>3.070509613093594</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.184040761661081</v>
+        <v>-4.093968492142379</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.066867754081972</v>
+        <v>1.102896661889454</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4755232761896601</v>
+        <v>0.5454484859795976</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.026154448773949</v>
+        <v>3.068109574647911</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.165002633953784</v>
+        <v>-4.074930364435081</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.071007724373136</v>
+        <v>1.107036632180617</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4173396648584656</v>
+        <v>0.4872648746484031</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.987769001183477</v>
+        <v>3.029724127057439</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.217518436228604</v>
+        <v>-4.127446166709902</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.169295805097398</v>
+        <v>1.20532471290488</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4173396648584656</v>
+        <v>0.4872648746484031</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.107063402817667</v>
+        <v>3.149018528691629</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.231385197562522</v>
+        <v>-4.14131292804382</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.164582429549965</v>
+        <v>1.200611337357446</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3794817481246426</v>
+        <v>0.4494069579145801</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.085181981763507</v>
+        <v>3.127137107637469</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.186581026022592</v>
+        <v>-4.09650875650389</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.188512628562863</v>
+        <v>1.224541536370344</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3794817481246426</v>
+        <v>0.4494069579145801</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.091190512160433</v>
+        <v>3.133145638034395</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.03883805578759</v>
+        <v>-3.948765786268888</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.145560037934063</v>
+        <v>1.181588945741544</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5472891053595258</v>
+        <v>0.6172143151494633</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.089825147778562</v>
+        <v>3.131780273652525</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.122659277062288</v>
+        <v>-4.032587007543586</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.114825170955665</v>
+        <v>1.150854078763146</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5472891053595258</v>
+        <v>0.6172143151494633</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.092618769310043</v>
+        <v>3.134573895184006</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.116506571009504</v>
+        <v>-4.026434301490801</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.117948601768437</v>
+        <v>1.153977509575918</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5534418114123101</v>
+        <v>0.6233670212022476</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.096972741333372</v>
+        <v>3.138927867207335</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.133315869160006</v>
+        <v>-4.043243599641303</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.110305359248347</v>
+        <v>1.146334267055828</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5366325132618084</v>
+        <v>0.606557723051746</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.085967639183181</v>
+        <v>3.127922765057144</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.071017870383884</v>
+        <v>-3.980945600865181</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.201560112555616</v>
+        <v>1.237589020363097</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5819267775362504</v>
+        <v>0.6518519873261881</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.179479751544668</v>
+        <v>3.22143487741863</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.869227672718726</v>
+        <v>-3.779155403200023</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.084568193335806</v>
+        <v>1.120597101143287</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7799449697054048</v>
+        <v>0.8498701794953425</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.100582668560287</v>
+        <v>3.14253779443425</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.92011438540492</v>
+        <v>-3.830042115886218</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.134503740583504</v>
+        <v>1.170532648390985</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7290582570192103</v>
+        <v>0.798983466809148</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.140340873270746</v>
+        <v>3.182295999144708</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.833503642755113</v>
+        <v>-3.743431373236411</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.183775773759471</v>
+        <v>1.219804681566951</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8076839882243686</v>
+        <v>0.8776091980143063</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.202144048109884</v>
+        <v>3.244099173983847</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.893712940760397</v>
+        <v>-3.803640671241695</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.158228035382028</v>
+        <v>1.194256943189509</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7474746902190841</v>
+        <v>0.8173999000090217</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.164554450131385</v>
+        <v>3.206509576005348</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.817290894328471</v>
+        <v>-3.727218624809769</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.187288471994728</v>
+        <v>1.223317379802209</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7474746902190841</v>
+        <v>0.8173999000090217</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.163046068171314</v>
+        <v>3.205001194045277</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316248</v>
+        <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.772917762689902</v>
+        <v>-3.6828454931712</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.204900592085591</v>
+        <v>1.240929499893072</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7918478218576527</v>
+        <v>0.8617730316475903</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.189532814589891</v>
+        <v>3.231487940463854</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.795398113548787</v>
+        <v>-3.705325844030085</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.190302245880628</v>
+        <v>1.226331153688109</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7918478218576527</v>
+        <v>0.8617730316475903</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.183926608728482</v>
+        <v>3.225881734602444</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.747742382987731</v>
+        <v>-3.657670113469029</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.215746295132855</v>
+        <v>1.251775202940336</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8395035524187083</v>
+        <v>0.909428762208646</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.21890180409292</v>
+        <v>3.260856929966883</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.647224224488976</v>
+        <v>-3.557151954970275</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.260845931907081</v>
+        <v>1.296874839714562</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9400217109174629</v>
+        <v>1.009946920707401</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.284105072566897</v>
+        <v>3.32606019844086</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557295</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.631318895056624</v>
+        <v>-3.541246625537922</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.253962736155895</v>
+        <v>1.289991643963375</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8609090502082239</v>
+        <v>0.9308342599981616</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.223392148617226</v>
+        <v>3.265347274491189</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932768</v>
+        <v>3.81683703393277</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.586480493448226</v>
+        <v>-3.496408223929524</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.275995799409883</v>
+        <v>1.312024707217363</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8654524831530934</v>
+        <v>0.9353776929430311</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.230215910994776</v>
+        <v>3.272171036868739</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.605978949690234</v>
+        <v>-3.515906680171532</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.272357356544157</v>
+        <v>1.308386264351638</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8173678418731891</v>
+        <v>0.8872930516631268</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.205526065857912</v>
+        <v>3.247481191731874</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.561776112604333</v>
+        <v>-3.471703843085632</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.295918093906355</v>
+        <v>1.331947001713835</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8615706789590896</v>
+        <v>0.9314958887490272</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.237927370637289</v>
+        <v>3.279882496511252</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.56933577844138</v>
+        <v>-3.479263508922679</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.291304228040783</v>
+        <v>1.327333135848264</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9163740829689089</v>
+        <v>0.9862992927588465</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.269219413512428</v>
+        <v>3.311174539386391</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.411044360902108</v>
+        <v>-3.320972091383406</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.405868560239532</v>
+        <v>1.441897468047013</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9163740829689089</v>
+        <v>0.9862992927588465</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.320467178695468</v>
+        <v>3.362422304569431</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.865338681321024</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.203402357267632</v>
+        <v>-3.11333008774893</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.487366066287576</v>
+        <v>1.523394974095056</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.124016086603385</v>
+        <v>1.193941296393323</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.443493085470407</v>
+        <v>3.485448211344369</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475141</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.152370264545104</v>
+        <v>-3.062297995026402</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.502727131614857</v>
+        <v>1.538756039422337</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.175048179325913</v>
+        <v>1.244973389115851</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.469060569342194</v>
+        <v>3.511015695216156</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404856</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.087146083417898</v>
+        <v>-2.997073813899196</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.546004208158444</v>
+        <v>1.582033115965925</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.240272360453119</v>
+        <v>1.310197570243056</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.525382482111222</v>
+        <v>3.567337607985185</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.84006118688256</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.049719063346764</v>
+        <v>-2.959646793828063</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.556935988486178</v>
+        <v>1.592964896293659</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.2455238984823</v>
+        <v>1.315449108272238</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.524494377228011</v>
+        <v>3.566449503101974</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992661</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.069830719381473</v>
+        <v>-2.979758449862771</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.550148118403535</v>
+        <v>1.586177026211016</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.25655124347972</v>
+        <v>1.326476453269657</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.532367576557703</v>
+        <v>3.574322702431666</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636289</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.016085904954268</v>
+        <v>-2.926013635435566</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.732203815195628</v>
+        <v>1.768232723003108</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.266614552920182</v>
+        <v>1.336539762710119</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.698963333243191</v>
+        <v>3.740918459117154</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957626</v>
+        <v>3.813222820957628</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.941303643929255</v>
+        <v>-2.851231374410554</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.88222962882345</v>
+        <v>1.918258536630931</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.341396813945194</v>
+        <v>1.411322023735132</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.863945599076016</v>
+        <v>3.905900724949979</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998756</v>
+        <v>3.814230727998758</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.915219559665447</v>
+        <v>-2.825147290146746</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.884371238542832</v>
+        <v>1.920400146350313</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.341396813945194</v>
+        <v>1.411322023735132</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.855653575089875</v>
+        <v>3.897608700963838</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896931</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.827341646556327</v>
+        <v>-2.737269377037625</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.917715599370259</v>
+        <v>1.95374450717774</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.457322456368546</v>
+        <v>1.527247666158483</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.923402156127665</v>
+        <v>3.965357282001627</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959859</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.818449185163043</v>
+        <v>-2.728376915644342</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.938826989654364</v>
+        <v>1.974855897461845</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.457322456368546</v>
+        <v>1.527247666158483</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.940956561854456</v>
+        <v>3.982911687728419</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.986925302132921</v>
+        <v>-2.896853032614219</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.863291590270997</v>
+        <v>1.899320498078478</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.429374620651965</v>
+        <v>1.499299830441902</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.916042907829092</v>
+        <v>3.957998033703054</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.289125773271338</v>
+        <v>-2.199053503752636</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.123681099003492</v>
+        <v>2.159710006810973</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.359026561281554</v>
+        <v>1.428951771071492</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.855103769394708</v>
+        <v>3.89705889526867</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.266404669588185</v>
+        <v>-2.176332400069484</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.123433562973658</v>
+        <v>2.159462470781139</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.359026561281554</v>
+        <v>1.428951771071492</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.845767791891612</v>
+        <v>3.887722917765575</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777675</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.395606482882228</v>
+        <v>-2.305534213363526</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.23065896350721</v>
+        <v>2.266687871314691</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.229824747987512</v>
+        <v>1.299749957777449</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.927152829766356</v>
+        <v>3.969107955640318</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.550387489660483</v>
+        <v>-2.460315220141782</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.205824383289555</v>
+        <v>2.241853291097035</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.196457073933036</v>
+        <v>1.266382283722973</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.944210047827316</v>
+        <v>3.986165173701279</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799964</v>
+        <v>3.769443619799966</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.54333279944531</v>
+        <v>-2.453260529926608</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.205321615365169</v>
+        <v>2.24135052317265</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.20351176414821</v>
+        <v>1.273436973938147</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.945118217945966</v>
+        <v>3.987073343819929</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.516381575118822</v>
+        <v>-2.42630930560012</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.226108258740505</v>
+        <v>2.262137166547986</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.218392110175929</v>
+        <v>1.288317319965866</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.964052579207339</v>
+        <v>4.006007705081301</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.76805206778411</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.652334583175138</v>
+        <v>-2.562262313656436</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.355830187662939</v>
+        <v>2.391859095470419</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.218392110175929</v>
+        <v>1.288317319965866</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.148155711352299</v>
+        <v>4.190110837226261</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714426</v>
+        <v>3.743925505714428</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.67474270098001</v>
+        <v>-2.584670431461308</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.338983635443983</v>
+        <v>2.375012543251464</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.218392110175929</v>
+        <v>1.288317319965866</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.140272406255292</v>
+        <v>4.182227532129255</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.702966936557611</v>
+        <v>-2.612894667038909</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.329747940762581</v>
+        <v>2.365776848570061</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.236368862627237</v>
+        <v>1.306294072417175</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.153112457275714</v>
+        <v>4.195067583149677</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.712407862446141</v>
+        <v>-2.622335592927439</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.382225288129016</v>
+        <v>2.418254195936496</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.358795980170629</v>
+        <v>1.428721189960566</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.282822445523597</v>
+        <v>4.32477757139756</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.764681469781782</v>
+        <v>-2.67460920026308</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.36420693974006</v>
+        <v>2.400235847547541</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.306522372834988</v>
+        <v>1.376447582624925</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.254349375667513</v>
+        <v>4.296304501541475</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347704</v>
+        <v>3.727898186347706</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.841011447382688</v>
+        <v>-2.750939177863986</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.331786761593473</v>
+        <v>2.367815669400954</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.306522372834988</v>
+        <v>1.376447582624925</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.252461188561288</v>
+        <v>4.29441631443525</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.71065410488775</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.043265167707041</v>
+        <v>-2.953192898188339</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.245705503066594</v>
+        <v>2.281734410874074</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.104268652510634</v>
+        <v>1.174193862300571</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.125929185969538</v>
+        <v>4.1678843118435</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343067</v>
+        <v>3.712897612343069</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.204833593234296</v>
+        <v>-3.114761323715594</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.179512143065844</v>
+        <v>2.215541050873325</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9774857287127546</v>
+        <v>1.047410938502692</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.048293441900963</v>
+        <v>4.090248567774926</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.75459613538935</v>
+        <v>3.754596135389352</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.337134885331849</v>
+        <v>-3.247062615813148</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.139665033092741</v>
+        <v>2.175693940900222</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9774857287127546</v>
+        <v>1.047410938502692</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.061366848766881</v>
+        <v>4.103321974640844</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378392</v>
+        <v>3.749882691378394</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.523003196171079</v>
+        <v>-3.432930926652378</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.057322905539989</v>
+        <v>2.09335181334747</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8189201353928069</v>
+        <v>0.8888453451827445</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.958232689557853</v>
+        <v>4.000187815431815</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006977</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.550903983280552</v>
+        <v>-3.460831713761851</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.044686631823202</v>
+        <v>2.080715539630683</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7843232112498721</v>
+        <v>0.8542484210398097</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.935998576199093</v>
+        <v>3.977953702073057</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.673430085983446</v>
+        <v>-3.583357816464745</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.992440634719244</v>
+        <v>2.028469542526724</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6617971085469783</v>
+        <v>0.7317223183369158</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.859247358554557</v>
+        <v>3.901202484428519</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585939</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.903944582169035</v>
+        <v>-3.813872312650333</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.966940795835511</v>
+        <v>2.002969703642992</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4312826123613895</v>
+        <v>0.5012078221513271</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.787644620433707</v>
+        <v>3.829599746307669</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814666</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.160665400163859</v>
+        <v>-4.070593130645157</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.004564187639429</v>
+        <v>2.040593095446909</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3228680382175747</v>
+        <v>0.3927932480075123</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.862907594949265</v>
+        <v>3.904862720823227</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237096</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.31465181794</v>
+        <v>-4.224579548421298</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.011949889674613</v>
+        <v>2.047978797482093</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3228680382175747</v>
+        <v>0.3927932480075123</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.931887864094905</v>
+        <v>3.973842989968867</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.264129914112334</v>
+        <v>-4.174057644593632</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.0182098533258</v>
+        <v>2.054238761133281</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3228680382175747</v>
+        <v>0.3927932480075123</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.917939066215026</v>
+        <v>3.959894192088989</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.516605068120058</v>
+        <v>-4.426532798601357</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.929090280778124</v>
+        <v>1.965119188585605</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3228680382175747</v>
+        <v>0.3927932480075123</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.92980955527044</v>
+        <v>3.971764681144403</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.80950082459947</v>
+        <v>-4.719428555080769</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.813142512705303</v>
+        <v>1.849171420512784</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3228680382175747</v>
+        <v>0.3927932480075123</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.931020089789383</v>
+        <v>3.972975215663346</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251947</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.967044896328912</v>
+        <v>-4.87697262681021</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.754246626240848</v>
+        <v>1.790275534048328</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2559662330773002</v>
+        <v>0.3258914428672378</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.89500074893254</v>
+        <v>3.936955874806503</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.652149152916204</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.245009291912186</v>
+        <v>-5.154937022393484</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.638138720743727</v>
+        <v>1.674167628551208</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.166346498791816</v>
+        <v>0.2362717085817535</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.836306761097439</v>
+        <v>3.878261886971401</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.66796230683033</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.361976984551077</v>
+        <v>-5.271904715032375</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.753555700387215</v>
+        <v>1.789584608194696</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.166346498791816</v>
+        <v>0.2362717085817535</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.998510817796483</v>
+        <v>4.040465943670446</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.696539468071553</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.44669492677203</v>
+        <v>-5.356622657253328</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.714515161462648</v>
+        <v>1.750544069270129</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.08123046986376958</v>
+        <v>0.1511556796537071</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.94228783840347</v>
+        <v>3.984242964277432</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868149</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.528629745040913</v>
+        <v>-5.438557475522211</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.691970651723586</v>
+        <v>1.727999559531067</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.0712957242766894</v>
+        <v>0.1412209340666269</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.946556408619712</v>
+        <v>3.988511534493675</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332692</v>
+        <v>3.783632867332694</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.63060586728932</v>
+        <v>-5.540533597770619</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.660105841280126</v>
+        <v>1.696134749087606</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.03068039797171818</v>
+        <v>0.03924481181821937</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.89429637372657</v>
+        <v>3.936251499600533</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231809</v>
+        <v>3.798296784231811</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.520599583812099</v>
+        <v>-5.430527314293397</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.696261241915189</v>
+        <v>1.73229014972267</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.007475826054442969</v>
+        <v>0.06244938373549458</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.900372004121111</v>
+        <v>3.942327129995073</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818522</v>
+        <v>3.785563924818524</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.377540008071174</v>
+        <v>-5.287467738552472</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.757735082933534</v>
+        <v>1.793763990741015</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.0005376005355363089</v>
+        <v>0.07046281032547386</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.909430070797073</v>
+        <v>3.951385196671035</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.77723741205179</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.076093282599336</v>
+        <v>-4.986021013080634</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.885574656004805</v>
+        <v>1.921603563812286</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3019843260073736</v>
+        <v>0.3719095357973111</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.097558988962711</v>
+        <v>4.139514114836674</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679624</v>
+        <v>3.812635940679626</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.10068352683452</v>
+        <v>-5.010611257315818</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.876709736063442</v>
+        <v>1.912738643870923</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3019843260073736</v>
+        <v>0.3719095357973111</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.098530166715422</v>
+        <v>4.140485292589384</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474161</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.049645150828</v>
+        <v>-4.959572881309298</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.897967990845805</v>
+        <v>1.933996898653286</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3019843260073736</v>
+        <v>0.3719095357973111</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.099373071095177</v>
+        <v>4.141328196969139</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969545</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.008505855961369</v>
+        <v>-4.918433586442667</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.933461807666603</v>
+        <v>1.969490715474084</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3431236208740044</v>
+        <v>0.4130488306639419</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.143094746889301</v>
+        <v>4.185049872763264</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700479</v>
+        <v>3.825752932700481</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.897899715881767</v>
+        <v>-4.807827446363065</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.793888259822378</v>
+        <v>1.829917167629859</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4537297609536064</v>
+        <v>0.5236549707435439</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.025642427060997</v>
+        <v>4.067597552934959</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077641</v>
+        <v>3.804688961077643</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.028480450412609</v>
+        <v>-4.938408180893908</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.745158010084005</v>
+        <v>1.781186917891486</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3231490264227639</v>
+        <v>0.3930742362127014</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.950796030416455</v>
+        <v>3.992751156290417</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.77502886083346</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.863984116221648</v>
+        <v>-4.773911846702946</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.795383362836472</v>
+        <v>1.831412270643953</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3231490264227639</v>
+        <v>0.3930742362127014</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.935222849492537</v>
+        <v>3.9771779753665</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077629</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.89135404890608</v>
+        <v>-4.801281779387378</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.783623100199129</v>
+        <v>1.81965200800661</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3231490264227639</v>
+        <v>0.3930742362127014</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.934410559928967</v>
+        <v>3.976365685802929</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.901739243795969</v>
+        <v>-4.811666974277268</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.789337801368246</v>
+        <v>1.825366709175726</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3127638315328746</v>
+        <v>0.3826890413228121</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.938048222120106</v>
+        <v>3.980003347994068</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735283</v>
+        <v>3.834415493735285</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.920327402518194</v>
+        <v>-4.830255132999492</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.852739543655781</v>
+        <v>1.888768451463262</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.2941756728106492</v>
+        <v>0.3641008826005868</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.997732332663196</v>
+        <v>4.039687458537158</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.92062594921423</v>
+        <v>-4.830553679695528</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.849489135795665</v>
+        <v>1.885518043603146</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.2941756728106492</v>
+        <v>0.3641008826005868</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.994601343481494</v>
+        <v>4.036556469355457</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108858</v>
+        <v>3.81564321210886</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.819802815523802</v>
+        <v>-4.729730546005101</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.894349284211228</v>
+        <v>1.930378192018708</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.306639888295003</v>
+        <v>0.3765650980849406</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.006610767711498</v>
+        <v>4.048565893585461</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121467</v>
+        <v>3.807356168121469</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.629021454771395</v>
+        <v>-4.538949185252694</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.970791081990733</v>
+        <v>2.006819989798214</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4974212490474104</v>
+        <v>0.567346458837348</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.121208837641485</v>
+        <v>4.163163963515448</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906081</v>
+        <v>3.775233033906082</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.610504600729575</v>
+        <v>-4.520432331210873</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.958034669345058</v>
+        <v>1.994063577152539</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5103513784726186</v>
+        <v>0.5802765882625562</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.108803761034207</v>
+        <v>4.15075888690817</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912985</v>
+        <v>3.785761685912987</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.585311416228257</v>
+        <v>-4.495239146709555</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.003078879757644</v>
+        <v>2.039107787565125</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.5355445629739369</v>
+        <v>0.6054697727638746</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.158886608347056</v>
+        <v>4.200841734221019</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539896</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.573257289315294</v>
+        <v>-4.483185019796593</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.001587098424267</v>
+        <v>2.037616006231747</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.5475986898868997</v>
+        <v>0.6175238996768374</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.159805652396272</v>
+        <v>4.201760778270234</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811009</v>
+        <v>3.725010844811011</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.579880536005652</v>
+        <v>-4.489808266486951</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.000818429932259</v>
+        <v>2.03684733773974</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5409754431965415</v>
+        <v>0.6109006529864791</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.157712334566193</v>
+        <v>4.199667460440155</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382921</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.47699994647706</v>
+        <v>-4.386927676958358</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.054821691621579</v>
+        <v>2.09085059942906</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6438560327251344</v>
+        <v>0.713781242515072</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.232291714161231</v>
+        <v>4.274246840035193</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760315</v>
+        <v>3.646857607760317</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.500441985657146</v>
+        <v>-4.410369716138445</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.065647546123139</v>
+        <v>2.101676453930619</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6438560327251344</v>
+        <v>0.713781242515072</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.252494384334825</v>
+        <v>4.294449510208787</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781707</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.518514493948758</v>
+        <v>-4.428442224430056</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.058418542806494</v>
+        <v>2.094447450613974</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6438560327251344</v>
+        <v>0.713781242515072</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.252494384334825</v>
+        <v>4.294449510208787</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082836</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.74968828782539</v>
+        <v>-4.659616018306688</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.926200938849308</v>
+        <v>1.962229846656788</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6438560327251344</v>
+        <v>0.713781242515072</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.212746297928292</v>
+        <v>4.254701423802254</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943587</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.718402267284935</v>
+        <v>-4.628329997766233</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.94573796606243</v>
+        <v>1.981766873869911</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.6751420532655897</v>
+        <v>0.7450672630555274</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.238540529249505</v>
+        <v>4.280495655123468</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677824</v>
+        <v>3.730590658677825</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.56537687517165</v>
+        <v>-4.475304605652949</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.106119122480647</v>
+        <v>2.142148030288128</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.8281674453788739</v>
+        <v>0.8980926551688115</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.429526764090379</v>
+        <v>4.471481889964342</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073883</v>
+        <v>3.741298518073885</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.593684189044921</v>
+        <v>-4.503611919526219</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.282262421839632</v>
+        <v>2.318291329647113</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.8281674453788739</v>
+        <v>0.8980926551688115</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.616992988998672</v>
+        <v>4.658948114872635</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.880402366955956</v>
+        <v>3.832564771447666</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.752845152638762</v>
+        <v>-4.733630007728853</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.188000987756178</v>
+        <v>2.195687045720141</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.6690064817850325</v>
+        <v>0.6680745669661778</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.490899362196449</v>
+        <v>4.490340213305137</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240812.xlsx
+++ b/tame_output/ON/bt/strategyON_20240812.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>56.3%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>82.0%</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.6%</t>
+          <t>124.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.7%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-634.9%</t>
+          <t>-634.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-35.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-156.7%</t>
+          <t>-171.9%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-327.8%</t>
+          <t>-327.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-157.2%</t>
+          <t>-157.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-20.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>83.1%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>-12.2%</t>
         </is>
       </c>
     </row>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416042</v>
+        <v>3.231167537416043</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382325</v>
+        <v>3.235981977382326</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495495</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792048</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318095</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942105</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417705</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225444</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111297</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532487</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067865</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265645</v>
+        <v>3.838199629265646</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
@@ -48261,19 +48261,19 @@
         <v>3.821184182474161</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.918182475490752</v>
+        <v>3.764550193486752</v>
       </c>
       <c r="D2031" t="n">
         <v>-4.959572881309298</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.933996898653286</v>
+        <v>1.780364616649285</v>
       </c>
       <c r="F2031" t="n">
         <v>0.3719095357973111</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.141328196969139</v>
+        <v>3.987695914965139</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969545</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.937220574364898</v>
+        <v>3.783588292360897</v>
       </c>
       <c r="D2032" t="n">
         <v>-4.918433586442667</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.969490715474084</v>
+        <v>1.815858433470083</v>
       </c>
       <c r="F2032" t="n">
         <v>0.4130488306639419</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.185049872763264</v>
+        <v>4.031417590759263</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700481</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.753404570488832</v>
+        <v>3.599772288484832</v>
       </c>
       <c r="D2033" t="n">
         <v>-4.807827446363065</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.829917167629859</v>
+        <v>1.676284885625858</v>
       </c>
       <c r="F2033" t="n">
         <v>0.5236549707435439</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.067597552934959</v>
+        <v>3.913965270930959</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077643</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.756906614562796</v>
+        <v>3.603274332558795</v>
       </c>
       <c r="D2034" t="n">
         <v>-4.938408180893908</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.781186917891486</v>
+        <v>1.627554635887485</v>
       </c>
       <c r="F2034" t="n">
         <v>0.3930742362127014</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.992751156290417</v>
+        <v>3.839118874286417</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.77502886083346</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.741333433638879</v>
+        <v>3.587701151634878</v>
       </c>
       <c r="D2035" t="n">
         <v>-4.773911846702946</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.831412270643953</v>
+        <v>1.677779988639952</v>
       </c>
       <c r="F2035" t="n">
         <v>0.3930742362127014</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.9771779753665</v>
+        <v>3.823545693362499</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077629</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.740521144075308</v>
+        <v>3.586888862071308</v>
       </c>
       <c r="D2036" t="n">
         <v>-4.801281779387378</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.81965200800661</v>
+        <v>1.666019726002609</v>
       </c>
       <c r="F2036" t="n">
         <v>0.3930742362127014</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.976365685802929</v>
+        <v>3.822733403798929</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.750389923200381</v>
+        <v>3.59675764119638</v>
       </c>
       <c r="D2037" t="n">
         <v>-4.811666974277268</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.825366709175726</v>
+        <v>1.671734427171726</v>
       </c>
       <c r="F2037" t="n">
         <v>0.3826890413228121</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.980003347994068</v>
+        <v>3.826371065990068</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735285</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.821226928976806</v>
+        <v>3.667594646972805</v>
       </c>
       <c r="D2038" t="n">
         <v>-4.830255132999492</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.888768451463262</v>
+        <v>1.735136169459261</v>
       </c>
       <c r="F2038" t="n">
         <v>0.3641008826005868</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.039687458537158</v>
+        <v>3.886055176533158</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.818095939795104</v>
+        <v>3.664463657791104</v>
       </c>
       <c r="D2039" t="n">
         <v>-4.830553679695528</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.885518043603146</v>
+        <v>1.731885761599145</v>
       </c>
       <c r="F2039" t="n">
         <v>0.3641008826005868</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.036556469355457</v>
+        <v>3.882924187351456</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.81564321210886</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.822626834734496</v>
+        <v>3.668994552730495</v>
       </c>
       <c r="D2040" t="n">
         <v>-4.729730546005101</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.930378192018708</v>
+        <v>1.776745910014708</v>
       </c>
       <c r="F2040" t="n">
         <v>0.3765650980849406</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.048565893585461</v>
+        <v>3.89493361158146</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121469</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.822756088213039</v>
+        <v>3.669123806209039</v>
       </c>
       <c r="D2041" t="n">
         <v>-4.538949185252694</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.006819989798214</v>
+        <v>1.853187707794214</v>
       </c>
       <c r="F2041" t="n">
         <v>0.567346458837348</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.163163963515448</v>
+        <v>4.009531681511447</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906082</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.802592933950636</v>
+        <v>3.648960651946635</v>
       </c>
       <c r="D2042" t="n">
         <v>-4.520432331210873</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.994063577152539</v>
+        <v>1.840431295148538</v>
       </c>
       <c r="F2042" t="n">
         <v>0.5802765882625562</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.15075888690817</v>
+        <v>3.997126604904169</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912987</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.837559870562694</v>
+        <v>3.683927588558694</v>
       </c>
       <c r="D2043" t="n">
         <v>-4.495239146709555</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.039107787565125</v>
+        <v>1.885475505561124</v>
       </c>
       <c r="F2043" t="n">
         <v>0.6054697727638746</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.200841734221019</v>
+        <v>4.047209452217018</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539896</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.831246438464132</v>
+        <v>3.677614156460131</v>
       </c>
       <c r="D2044" t="n">
         <v>-4.483185019796593</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.037616006231747</v>
+        <v>1.883983724227747</v>
       </c>
       <c r="F2044" t="n">
         <v>0.6175238996768374</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.201760778270234</v>
+        <v>4.048128496266234</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811011</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.833127068648268</v>
+        <v>3.679494786644267</v>
       </c>
       <c r="D2045" t="n">
         <v>-4.489808266486951</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.03684733773974</v>
+        <v>1.883215055735739</v>
       </c>
       <c r="F2045" t="n">
         <v>0.6109006529864791</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.199667460440155</v>
+        <v>4.046035178436155</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382921</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.84597809452615</v>
+        <v>3.69234581252215</v>
       </c>
       <c r="D2046" t="n">
         <v>-4.386927676958358</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.09085059942906</v>
+        <v>1.937218317425059</v>
       </c>
       <c r="F2046" t="n">
         <v>0.713781242515072</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.274246840035193</v>
+        <v>4.120614558031193</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.646857607760317</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.866180764699744</v>
+        <v>3.712548482695744</v>
       </c>
       <c r="D2047" t="n">
         <v>-4.410369716138445</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.101676453930619</v>
+        <v>1.948044171926619</v>
       </c>
       <c r="F2047" t="n">
         <v>0.713781242515072</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.294449510208787</v>
+        <v>4.140817228204787</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666767386781707</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.866180764699744</v>
+        <v>3.712548482695744</v>
       </c>
       <c r="D2048" t="n">
         <v>-4.428442224430056</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.094447450613974</v>
+        <v>1.940815168609974</v>
       </c>
       <c r="F2048" t="n">
         <v>0.713781242515072</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.294449510208787</v>
+        <v>4.140817228204787</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670068888082836</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.826432678293211</v>
+        <v>3.67280039628921</v>
       </c>
       <c r="D2049" t="n">
         <v>-4.659616018306688</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.962229846656788</v>
+        <v>1.808597564652788</v>
       </c>
       <c r="F2049" t="n">
         <v>0.713781242515072</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.254701423802254</v>
+        <v>4.101069141798254</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745593333943587</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.833455297290151</v>
+        <v>3.67982301528615</v>
       </c>
       <c r="D2050" t="n">
         <v>-4.628329997766233</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.981766873869911</v>
+        <v>1.82813459186591</v>
       </c>
       <c r="F2050" t="n">
         <v>0.7450672630555274</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.280495655123468</v>
+        <v>4.126863373119467</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730590658677825</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.932626296863055</v>
+        <v>3.778994014859055</v>
       </c>
       <c r="D2051" t="n">
         <v>-4.475304605652949</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.142148030288128</v>
+        <v>1.988515748284128</v>
       </c>
       <c r="F2051" t="n">
         <v>0.8980926551688115</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.471481889964342</v>
+        <v>4.317849607960342</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741298518073885</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.120092521771348</v>
+        <v>3.966460239767347</v>
       </c>
       <c r="D2052" t="n">
         <v>-4.503611919526219</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.318291329647113</v>
+        <v>2.164659047643112</v>
       </c>
       <c r="F2052" t="n">
         <v>0.8980926551688115</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.658948114872635</v>
+        <v>4.505315832868634</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.832564771447666</v>
+        <v>3.843336153821181</v>
       </c>
       <c r="C2053" t="n">
-        <v>4.08949547312543</v>
+        <v>3.935863191121429</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.733630007728853</v>
+        <v>-4.731651521224607</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.195687045720141</v>
+        <v>2.042846158317839</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.6680745669661778</v>
+        <v>0.6700530534704233</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.490340213305137</v>
+        <v>4.337895023203684</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240812.xlsx
+++ b/tame_output/ON/bt/strategyON_20240812.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>11.4%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>97.3%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.0%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.2%</t>
+          <t>109.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.5%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-13.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-47.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.7%</t>
+          <t>427.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-634.7%</t>
+          <t>-654.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.4%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-171.9%</t>
+          <t>-164.6%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-327.7%</t>
+          <t>-291.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-157.0%</t>
+          <t>-160.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>81.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>1.3%</t>
         </is>
       </c>
     </row>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213493</v>
+        <v>3.223539378213492</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416043</v>
+        <v>3.231167537416042</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382326</v>
+        <v>3.235981977382324</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495496</v>
+        <v>3.278199702495495</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347051</v>
+        <v>3.29913614634705</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130013</v>
+        <v>3.287377576130012</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178239</v>
+        <v>3.315884374178238</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309419</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.3047157169709</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.885076515482016</v>
+        <v>-9.063275597136876</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3756428403917771</v>
+        <v>-0.4469224730537209</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.398954367379046</v>
+        <v>-1.42616506495983</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.33937156968735</v>
+        <v>2.323045151138879</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.760497859144424</v>
+        <v>-8.938696940799284</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3246722333006811</v>
+        <v>-0.3959518659626253</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.398954367379046</v>
+        <v>-1.42616506495983</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.340510714243409</v>
+        <v>2.324184295694938</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.813393147188711</v>
+        <v>-8.991592228843571</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3431965743562881</v>
+        <v>-0.4144762070182324</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.393999021290599</v>
+        <v>-1.421209718871384</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.346117696058584</v>
+        <v>2.329791277510113</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.741259971900829</v>
+        <v>-8.919459053555689</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3086096000024994</v>
+        <v>-0.3798892326644432</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.393999021290599</v>
+        <v>-1.421209718871384</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.351851400297221</v>
+        <v>2.33552498174875</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.669893579291182</v>
+        <v>-8.848092660946042</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2898003053525056</v>
+        <v>-0.3610799380144494</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.349843326261736</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.384933973469144</v>
+        <v>2.368607554920673</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.576434545305958</v>
+        <v>-8.754633626960818</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2623001730713233</v>
+        <v>-0.3335798057332675</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.349843326261736</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.375050492156237</v>
+        <v>2.358724073607766</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.565781363752526</v>
+        <v>-8.743980445407386</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2598734609493243</v>
+        <v>-0.3311530936112685</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.349843326261736</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.373215931656863</v>
+        <v>2.356889513108392</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.467874325076036</v>
+        <v>-8.646073406730896</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.221010960452189</v>
+        <v>-0.2922905931141329</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.254646878820395</v>
+        <v>-1.28185757640118</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.413707066599736</v>
+        <v>2.397380648051265</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.443920784100078</v>
+        <v>-8.622119865754938</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2107610379163121</v>
+        <v>-0.2820406705782563</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.230693337844438</v>
+        <v>-1.257904035425222</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.428747697330804</v>
+        <v>2.412421278782333</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.179860845777281</v>
+        <v>-8.358059927432141</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1183973787489458</v>
+        <v>-0.1896770114108897</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.9666333995216414</v>
+        <v>-0.9938440971024258</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.57392334416273</v>
+        <v>2.557596925614259</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.472781222272443</v>
+        <v>-7.650980303927303</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1616474369926886</v>
+        <v>0.09036780433074476</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.9666333995216414</v>
+        <v>-0.9938440971024258</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.571136310502429</v>
+        <v>2.554809891953958</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.432596923906252</v>
+        <v>-7.610796005561112</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1780647802270061</v>
+        <v>0.1067851475650623</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9264491011554506</v>
+        <v>-0.9536597987362351</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.595590513409984</v>
+        <v>2.579264094861514</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.26919705296689</v>
+        <v>-7.44739613462175</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.242791549823508</v>
+        <v>0.1715119171615642</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.7630492302160882</v>
+        <v>-0.7902599277968726</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.692997257194359</v>
+        <v>2.676670838645888</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.035715830737291</v>
+        <v>-7.213914912392151</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3441084675532</v>
+        <v>0.2728288348912562</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5295680079864896</v>
+        <v>-0.556778705567274</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.841010419369971</v>
+        <v>2.8246840008215</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.886049439729776</v>
+        <v>-7.064248521384636</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4010828136432467</v>
+        <v>0.3298031809813029</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4366645167439537</v>
+        <v>-0.4638752143247381</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.893860303802533</v>
+        <v>2.877533885254062</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.75377396609889</v>
+        <v>-6.93197304775375</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4493604898426287</v>
+        <v>0.3780808571806844</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.304389043113067</v>
+        <v>-0.3315997406938515</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.968593074728092</v>
+        <v>2.952266656179621</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.598035633539148</v>
+        <v>-6.776234715194008</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.514470883554162</v>
+        <v>0.4431912508922178</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1486507105533255</v>
+        <v>-0.1758614081341099</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.064851134951573</v>
+        <v>3.048524716403103</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.513070966809828</v>
+        <v>-6.691270048464688</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5613630914695489</v>
+        <v>0.4900834588076046</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.06368604382400589</v>
+        <v>-0.09089674140479032</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.128736276212824</v>
+        <v>3.112409857664353</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.618660956582932</v>
+        <v>-6.796860038237792</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3911511659610882</v>
+        <v>0.3198715332991444</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1692760335971102</v>
+        <v>-0.1964867311778947</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.937406352749742</v>
+        <v>2.921079934201272</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.550426371957505</v>
+        <v>-6.728625453612365</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4669893416883455</v>
+        <v>0.3957097090264017</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1508607107245742</v>
+        <v>-0.1780714083053587</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.99699988835035</v>
+        <v>2.98067346980188</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.402486330549905</v>
+        <v>-6.580685412204765</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4062864355632176</v>
+        <v>0.3350068029012738</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1305397948160167</v>
+        <v>-0.1577504923968011</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.889313515207317</v>
+        <v>2.872987096658847</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.349516808295917</v>
+        <v>-6.527715889950777</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4187602582113348</v>
+        <v>0.347480625549391</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.1047809701428122</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.912381242306233</v>
+        <v>2.896054823757762</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.183728612335626</v>
+        <v>-6.361927693990486</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4781149245003582</v>
+        <v>0.4068352918384139</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.1047809701428122</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.90542063021114</v>
+        <v>2.889094211662669</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.150365405856857</v>
+        <v>-6.328564487511717</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5059225614730085</v>
+        <v>0.4346429288110647</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.1047809701428122</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.919882984592283</v>
+        <v>2.903556566043812</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.042106268734336</v>
+        <v>-6.220305350389196</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5437583367812122</v>
+        <v>0.4724787041192684</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.1047809701428122</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.914415105051478</v>
+        <v>2.898088686503007</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.918815133917205</v>
+        <v>-6.097014215572065</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5905728847186418</v>
+        <v>0.5192932520566975</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.04572086225510269</v>
+        <v>0.01851016467431826</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.985887879952333</v>
+        <v>2.969561461403862</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.866118266785914</v>
+        <v>-6.044317348440774</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6193526098084834</v>
+        <v>0.5480729771465391</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.09841772938639387</v>
+        <v>0.07120703180560944</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.025206978468433</v>
+        <v>3.008880559919962</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.622352824802469</v>
+        <v>-5.800551906457329</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7126394949489119</v>
+        <v>0.6413598622869676</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.09841772938639387</v>
+        <v>0.07120703180560944</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.020987686815483</v>
+        <v>3.004661268267013</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.532577152425997</v>
+        <v>-5.710776234080857</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7506740778195167</v>
+        <v>0.6793944451575729</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.1328064767199195</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.060071667684086</v>
+        <v>3.043745249135615</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.282726758476922</v>
+        <v>-5.460925840131782</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8433563103828488</v>
+        <v>0.7720766777209045</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.1328064767199195</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.052813742667788</v>
+        <v>3.036487324119317</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011494</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.10683466600949</v>
+        <v>-5.28503374766435</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9173122708904704</v>
+        <v>0.8460326382285261</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.1328064767199195</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.056412866188436</v>
+        <v>3.040086447639966</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.935388202987027</v>
+        <v>-5.113587284641887</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9992183621540094</v>
+        <v>0.9279387294920651</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.331463637323167</v>
+        <v>0.3042529397423826</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.172608250056468</v>
+        <v>3.156281831507997</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.861098637248688</v>
+        <v>-5.039297718903548</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.027954666065642</v>
+        <v>0.9566750334036977</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.4057532030615063</v>
+        <v>0.3785425054807219</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.216202467115768</v>
+        <v>3.199876048567297</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.797462895014753</v>
+        <v>-4.975661976669613</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.058103764013533</v>
+        <v>0.9868241313515891</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4693889452954408</v>
+        <v>0.4421782477146564</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.259078713510446</v>
+        <v>3.242752294961976</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.686036135688833</v>
+        <v>-4.864235217343693</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.083868726527697</v>
+        <v>1.012589093865753</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4693889452954408</v>
+        <v>0.4421782477146564</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.240272972294242</v>
+        <v>3.223946553745771</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.696538758754122</v>
+        <v>-4.874737840408982</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.081410753926459</v>
+        <v>1.010131121264515</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.458886322230152</v>
+        <v>0.4316756246493675</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.235714475079946</v>
+        <v>3.219388056531475</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.624296190582927</v>
+        <v>-4.802495272237787</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.114237095029757</v>
+        <v>1.042957462367813</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.458886322230152</v>
+        <v>0.4316756246493675</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.239643788914766</v>
+        <v>3.223317370366296</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.606582503705062</v>
+        <v>-4.784781585359922</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.122001153698243</v>
+        <v>1.050721521036299</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4620676511270688</v>
+        <v>0.4348569535462843</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.242231170170256</v>
+        <v>3.225904751621786</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.497777618225335</v>
+        <v>-4.675976699880195</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.162521179110127</v>
+        <v>1.091241546448183</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4620676511270688</v>
+        <v>0.4348569535462843</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.23922924139025</v>
+        <v>3.222902822841779</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.277756820188324</v>
+        <v>-4.455955901843184</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.252108535335545</v>
+        <v>1.180828902673601</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.603287496195049</v>
+        <v>0.5760767986142645</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.325540185441652</v>
+        <v>3.309213766893182</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.144889131125047</v>
+        <v>-4.323088212779907</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.32114979376268</v>
+        <v>1.249870161100736</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.603287496195049</v>
+        <v>0.5760767986142645</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.341434368243475</v>
+        <v>3.325107949695005</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.024716047760548</v>
+        <v>-4.202915129415408</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.370364871548781</v>
+        <v>1.299085238886837</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7234605795595479</v>
+        <v>0.6962498819787635</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.414684062702476</v>
+        <v>3.398357644154006</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.889462686430571</v>
+        <v>-4.067661768085431</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.434554318642212</v>
+        <v>1.363274685980268</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.858713940889525</v>
+        <v>0.8315032433087406</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.505924182061903</v>
+        <v>3.489597763513432</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.949337513788263</v>
+        <v>-4.127536595443123</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.396641879100561</v>
+        <v>1.325362246438617</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7988391135318329</v>
+        <v>0.7716284159510485</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.456036777048713</v>
+        <v>3.439710358500243</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.829517282877426</v>
+        <v>-4.007716364532286</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.459859140699104</v>
+        <v>1.38857950803716</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7988391135318329</v>
+        <v>0.7716284159510485</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.471325946282922</v>
+        <v>3.454999527734451</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.831986989339232</v>
+        <v>-4.010186070994092</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.366515457436823</v>
+        <v>1.295235824774879</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7963694070700267</v>
+        <v>0.7691587094892423</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.37748832172828</v>
+        <v>3.361161903179809</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.900357175663242</v>
+        <v>-4.078556257318102</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.258429244392521</v>
+        <v>1.187149611730576</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8056451061062416</v>
+        <v>0.7784344085254572</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.30231560263531</v>
+        <v>3.285989184086839</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.914145228510288</v>
+        <v>-4.092344310165148</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.243350731885593</v>
+        <v>1.172071099223649</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8056451061062416</v>
+        <v>0.7784344085254572</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.292752311267201</v>
+        <v>3.276425892718731</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.969665304402878</v>
+        <v>-4.147864386057738</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.35817353822076</v>
+        <v>1.286893905558816</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8056451061062416</v>
+        <v>0.7784344085254572</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.429783147959404</v>
+        <v>3.413456729410933</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.794191044610409</v>
+        <v>-3.972390126265269</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.432930474129535</v>
+        <v>1.361650841467591</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8056451061062416</v>
+        <v>0.7784344085254572</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.434350379951192</v>
+        <v>3.418023961402721</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.905127297251657</v>
+        <v>-4.083326378906517</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.364298001834243</v>
+        <v>1.293018369172299</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8056451061062416</v>
+        <v>0.7784344085254572</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.410092408712399</v>
+        <v>3.393765990163928</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.871463751779376</v>
+        <v>-4.049662833434235</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.306301733424606</v>
+        <v>1.235022100762661</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8393086515785235</v>
+        <v>0.8120979539977391</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.358828849397217</v>
+        <v>3.342502430848747</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.811611132575652</v>
+        <v>-3.989810214230512</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.340415167538227</v>
+        <v>1.269135534876283</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8393086515785235</v>
+        <v>0.8120979539977391</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.36900123582935</v>
+        <v>3.352674817280879</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.725367669549275</v>
+        <v>-3.903566751204134</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.369858823322639</v>
+        <v>1.298579190660694</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8393086515785235</v>
+        <v>0.8120979539977391</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.36394750640321</v>
+        <v>3.34762108785474</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.770674488948255</v>
+        <v>-3.948873570603114</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.343511871007572</v>
+        <v>1.272232238345628</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7984984885692927</v>
+        <v>0.7712877909885083</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.331237184042197</v>
+        <v>3.314910765493726</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803193</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.799707593650556</v>
+        <v>-3.977906675305416</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.332450502159753</v>
+        <v>1.261170869497809</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7984984885692927</v>
+        <v>0.7712877909885083</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.331789057075299</v>
+        <v>3.315462638526828</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.706897112199697</v>
+        <v>-3.885096193854556</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.298847386631462</v>
+        <v>1.227567753969518</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8913089700201521</v>
+        <v>0.8640982724393677</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.31674803783718</v>
+        <v>3.300421619288709</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.751286581529125</v>
+        <v>-3.929485663183984</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.282965074824292</v>
+        <v>1.211685442162348</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8469195006907244</v>
+        <v>0.81970880310994</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.291987832164124</v>
+        <v>3.275661413615654</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.867828186634468</v>
+        <v>-4.046027268289326</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.231424141293878</v>
+        <v>1.160144508631934</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7303778955853817</v>
+        <v>0.7031671980045973</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.217138577612642</v>
+        <v>3.200812159064171</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.907752281217039</v>
+        <v>-4.085951362871898</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.220945799291516</v>
+        <v>1.149666166629573</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7303778955853817</v>
+        <v>0.7031671980045973</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.222629873443309</v>
+        <v>3.206303454894838</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.935532679118392</v>
+        <v>-4.113731760773251</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.221330841899514</v>
+        <v>1.150051209237571</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7025974976840286</v>
+        <v>0.6753868001032441</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.217458836471036</v>
+        <v>3.201132417922565</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.963841082329828</v>
+        <v>-4.23211243350339</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.048363200615594</v>
+        <v>0.9410546601461685</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.7053048553229899</v>
+        <v>0.6081689479522679</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.057438971055066</v>
+        <v>2.999157426632633</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.072455160773159</v>
+        <v>-4.340726511946721</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.125067229957467</v>
+        <v>1.017758689488042</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.7053048553229899</v>
+        <v>0.6081689479522679</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.177588631774272</v>
+        <v>3.119307087351839</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.037046122525016</v>
+        <v>-4.305317473698578</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.153743871359047</v>
+        <v>1.046435330889622</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.7053048553229899</v>
+        <v>0.6081689479522679</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.192101657876595</v>
+        <v>3.133820113454162</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.998662459966865</v>
+        <v>-4.266933811140427</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.166516777724676</v>
+        <v>1.059208237255251</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7436885178811411</v>
+        <v>0.6465526105104191</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.212551296753854</v>
+        <v>3.154269752331421</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.821546129931699</v>
+        <v>-4.089817481105261</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.234092338584044</v>
+        <v>1.126783798114619</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7436885178811411</v>
+        <v>0.6465526105104191</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.209280325599156</v>
+        <v>3.150998781176723</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793905</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.866638374765245</v>
+        <v>-4.134909725938806</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.216738832412539</v>
+        <v>1.109430291943114</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6817924747117513</v>
+        <v>0.5846565673410293</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.172826091459435</v>
+        <v>3.114544547037002</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.687262953526477</v>
+        <v>-3.955534304700039</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.282275976214461</v>
+        <v>1.174967435745035</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.83856923288247</v>
+        <v>0.741433325511748</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.260679121668281</v>
+        <v>3.202397577245848</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.732277167047083</v>
+        <v>-4.000548518220645</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.245077746137808</v>
+        <v>1.137769205668383</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.8082203375678654</v>
+        <v>0.7110844301971434</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.223277239811108</v>
+        <v>3.164995695388675</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.999281677319519</v>
+        <v>-4.267553028493081</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.143967504367779</v>
+        <v>1.036658963898354</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.6138572995249167</v>
+        <v>0.5167213921541949</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.112350979324285</v>
+        <v>3.054069434901851</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.100479458756691</v>
+        <v>-4.368750809930254</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.102692313689412</v>
+        <v>0.9953837732199866</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5454484859795976</v>
+        <v>0.4483125786088757</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.070509613093594</v>
+        <v>3.012228068671161</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.093968492142379</v>
+        <v>-4.362239843315941</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.102896661889454</v>
+        <v>0.9955881214200284</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5454484859795976</v>
+        <v>0.4483125786088757</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.068109574647911</v>
+        <v>3.009828030225478</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.074930364435081</v>
+        <v>-4.343201715608644</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.107036632180617</v>
+        <v>0.9997280917111924</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4872648746484031</v>
+        <v>0.3901289672776811</v>
       </c>
       <c r="G1962" t="n">
-        <v>3.029724127057439</v>
+        <v>2.971442582635006</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.127446166709902</v>
+        <v>-4.395717517883464</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.20532471290488</v>
+        <v>1.098016172435454</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4872648746484031</v>
+        <v>0.3901289672776811</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.149018528691629</v>
+        <v>3.090736984269197</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.14131292804382</v>
+        <v>-4.409584279217382</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.200611337357446</v>
+        <v>1.093302796888021</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4494069579145801</v>
+        <v>0.3522710505438582</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.127137107637469</v>
+        <v>3.068855563215036</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.09650875650389</v>
+        <v>-4.364780107677452</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.224541536370344</v>
+        <v>1.117232995900919</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4494069579145801</v>
+        <v>0.3522710505438582</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.133145638034395</v>
+        <v>3.074864093611962</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.948765786268888</v>
+        <v>-4.21703713744245</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.181588945741544</v>
+        <v>1.074280405272119</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6172143151494633</v>
+        <v>0.5200784077787414</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.131780273652525</v>
+        <v>3.073498729230092</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.032587007543586</v>
+        <v>-4.300858358717148</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.150854078763146</v>
+        <v>1.043545538293721</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6172143151494633</v>
+        <v>0.5200784077787414</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.134573895184006</v>
+        <v>3.076292350761573</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.026434301490801</v>
+        <v>-4.294705652664364</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.153977509575918</v>
+        <v>1.046668969106493</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6233670212022476</v>
+        <v>0.5262311138315257</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.138927867207335</v>
+        <v>3.080646322784902</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.043243599641303</v>
+        <v>-4.311514950814866</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.146334267055828</v>
+        <v>1.039025726586402</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.606557723051746</v>
+        <v>0.509421815681024</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.127922765057144</v>
+        <v>3.069641220634711</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.980945600865181</v>
+        <v>-4.249216952038743</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.237589020363097</v>
+        <v>1.130280479893672</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.6518519873261881</v>
+        <v>0.554716079955466</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.22143487741863</v>
+        <v>3.163153332996197</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.779155403200023</v>
+        <v>-4.047426754373586</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.120597101143287</v>
+        <v>1.013288560673863</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.8498701794953425</v>
+        <v>0.7527342721246204</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.14253779443425</v>
+        <v>3.084256250011816</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.830042115886218</v>
+        <v>-4.09831346705978</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.170532648390985</v>
+        <v>1.06322410792156</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.798983466809148</v>
+        <v>0.7018475594384259</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.182295999144708</v>
+        <v>3.124014454722275</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.743431373236411</v>
+        <v>-4.011702724409973</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.219804681566951</v>
+        <v>1.112496141097526</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8776091980143063</v>
+        <v>0.7804732906435842</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.244099173983847</v>
+        <v>3.185817629561414</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.803640671241695</v>
+        <v>-4.071912022415258</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.194256943189509</v>
+        <v>1.086948402720084</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.8173999000090217</v>
+        <v>0.7202639926382997</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.206509576005348</v>
+        <v>3.148228031582915</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.727218624809769</v>
+        <v>-3.995489975983332</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.223317379802209</v>
+        <v>1.116008839332783</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.8173999000090217</v>
+        <v>0.7202639926382997</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.205001194045277</v>
+        <v>3.146719649622843</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.6828454931712</v>
+        <v>-3.951116844344763</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.240929499893072</v>
+        <v>1.133620959423647</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8617730316475903</v>
+        <v>0.7646371242768683</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.231487940463854</v>
+        <v>3.173206396041421</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.705325844030085</v>
+        <v>-3.973597195203648</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.226331153688109</v>
+        <v>1.119022613218684</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8617730316475903</v>
+        <v>0.7646371242768683</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.225881734602444</v>
+        <v>3.167600190180011</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.657670113469029</v>
+        <v>-3.925941464642592</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.251775202940336</v>
+        <v>1.144466662470911</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.909428762208646</v>
+        <v>0.8122928548379239</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.260856929966883</v>
+        <v>3.202575385544449</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.557151954970275</v>
+        <v>-3.825423306143837</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.296874839714562</v>
+        <v>1.189566299245137</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.009946920707401</v>
+        <v>0.9128110133366785</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.32606019844086</v>
+        <v>3.267778654018427</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557295</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.541246625537922</v>
+        <v>-3.809517976711485</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.289991643963375</v>
+        <v>1.18268310349395</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.9308342599981616</v>
+        <v>0.8336983526274395</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.265347274491189</v>
+        <v>3.207065730068756</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81683703393277</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.496408223929524</v>
+        <v>-3.764679575103087</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.312024707217363</v>
+        <v>1.204716166747938</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.9353776929430311</v>
+        <v>0.838241785572309</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.272171036868739</v>
+        <v>3.213889492446306</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917053</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.515906680171532</v>
+        <v>-3.784178031345095</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.308386264351638</v>
+        <v>1.201077723882213</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8872930516631268</v>
+        <v>0.7901571442924047</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.247481191731874</v>
+        <v>3.189199647309441</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.471703843085632</v>
+        <v>-3.739975194259194</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.331947001713835</v>
+        <v>1.22463846124441</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.9314958887490272</v>
+        <v>0.8343599813783051</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.279882496511252</v>
+        <v>3.221600952088818</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265646</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.479263508922679</v>
+        <v>-3.747534860096241</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.327333135848264</v>
+        <v>1.220024595378839</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9862992927588465</v>
+        <v>0.8891633853881244</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.311174539386391</v>
+        <v>3.252892994963958</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.320972091383406</v>
+        <v>-3.589243442556969</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.441897468047013</v>
+        <v>1.334588927577588</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9862992927588465</v>
+        <v>0.8891633853881244</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.362422304569431</v>
+        <v>3.304140760146997</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321024</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.11333008774893</v>
+        <v>-3.381601438922493</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.523394974095056</v>
+        <v>1.416086433625631</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.193941296393323</v>
+        <v>1.096805389022601</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.485448211344369</v>
+        <v>3.427166666921936</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475141</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.062297995026402</v>
+        <v>-3.330569346199965</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.538756039422337</v>
+        <v>1.431447498952912</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.244973389115851</v>
+        <v>1.147837481745129</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.511015695216156</v>
+        <v>3.452734150793723</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404856</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.997073813899196</v>
+        <v>-3.265345165072759</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.582033115965925</v>
+        <v>1.4747245754965</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.310197570243056</v>
+        <v>1.213061662872334</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.567337607985185</v>
+        <v>3.509056063562751</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84006118688256</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.959646793828063</v>
+        <v>-3.227918145001625</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.592964896293659</v>
+        <v>1.485656355824233</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.315449108272238</v>
+        <v>1.218313200901516</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.566449503101974</v>
+        <v>3.508167958679541</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.979758449862771</v>
+        <v>-3.248029801036334</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.586177026211016</v>
+        <v>1.478868485741591</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.326476453269657</v>
+        <v>1.229340545898935</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.574322702431666</v>
+        <v>3.516041158009233</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636289</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.926013635435566</v>
+        <v>-3.194284986609129</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.768232723003108</v>
+        <v>1.660924182533683</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.336539762710119</v>
+        <v>1.239403855339397</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.740918459117154</v>
+        <v>3.68263691469472</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957628</v>
+        <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.851231374410554</v>
+        <v>-3.119502725584116</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.918258536630931</v>
+        <v>1.810949996161505</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.411322023735132</v>
+        <v>1.31418611636441</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.905900724949979</v>
+        <v>3.847619180527545</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998758</v>
+        <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.825147290146746</v>
+        <v>-3.093418641320308</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.920400146350313</v>
+        <v>1.813091605880888</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.411322023735132</v>
+        <v>1.31418611636441</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.897608700963838</v>
+        <v>3.839327156541404</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896931</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.737269377037625</v>
+        <v>-3.005540728211188</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.95374450717774</v>
+        <v>1.846435966708315</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.527247666158483</v>
+        <v>1.430111758787761</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.965357282001627</v>
+        <v>3.907075737579194</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959859</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.728376915644342</v>
+        <v>-2.996648266817904</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.974855897461845</v>
+        <v>1.86754735699242</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.527247666158483</v>
+        <v>1.430111758787761</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.982911687728419</v>
+        <v>3.924630143305986</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.896853032614219</v>
+        <v>-3.165124383787782</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.899320498078478</v>
+        <v>1.792011957609053</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.499299830441902</v>
+        <v>1.40216392307118</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.957998033703054</v>
+        <v>3.899716489280622</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.199053503752636</v>
+        <v>-2.467324854926199</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.159710006810973</v>
+        <v>2.052401466341548</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.428951771071492</v>
+        <v>1.33181586370077</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.89705889526867</v>
+        <v>3.838777350846237</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.176332400069484</v>
+        <v>-2.444603751243046</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.159462470781139</v>
+        <v>2.052153930311714</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.428951771071492</v>
+        <v>1.33181586370077</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.887722917765575</v>
+        <v>3.829441373343141</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777675</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.305534213363526</v>
+        <v>-2.573805564537089</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.266687871314691</v>
+        <v>2.159379330845265</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.299749957777449</v>
+        <v>1.202614050406728</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.969107955640318</v>
+        <v>3.910826411217885</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644415</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.460315220141782</v>
+        <v>-2.728586571315344</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.241853291097035</v>
+        <v>2.13454475062761</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.266382283722973</v>
+        <v>1.169246376352251</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.986165173701279</v>
+        <v>3.927883629278846</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799966</v>
+        <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.453260529926608</v>
+        <v>-2.721531881100171</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.24135052317265</v>
+        <v>2.134041982703224</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.273436973938147</v>
+        <v>1.176301066567425</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.987073343819929</v>
+        <v>3.928791799397495</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.42630930560012</v>
+        <v>-2.694580656773683</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.262137166547986</v>
+        <v>2.154828626078562</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.288317319965866</v>
+        <v>1.191181412595144</v>
       </c>
       <c r="G2002" t="n">
-        <v>4.006007705081301</v>
+        <v>3.947726160658869</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.76805206778411</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.562262313656436</v>
+        <v>-2.830533664829999</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.391859095470419</v>
+        <v>2.284550555000995</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.288317319965866</v>
+        <v>1.191181412595144</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.190110837226261</v>
+        <v>4.131829292803828</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714428</v>
+        <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.584670431461308</v>
+        <v>-2.852941782634871</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.375012543251464</v>
+        <v>2.267704002782039</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.288317319965866</v>
+        <v>1.191181412595144</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.182227532129255</v>
+        <v>4.123945987706821</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.612894667038909</v>
+        <v>-2.881166018212471</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.365776848570061</v>
+        <v>2.258468308100636</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.306294072417175</v>
+        <v>1.209158165046453</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.195067583149677</v>
+        <v>4.136786038727244</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516198</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.622335592927439</v>
+        <v>-2.890606944101001</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.418254195936496</v>
+        <v>2.310945655467071</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.428721189960566</v>
+        <v>1.331585282589844</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.32477757139756</v>
+        <v>4.266496026975126</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321637</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.67460920026308</v>
+        <v>-2.942880551436643</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.400235847547541</v>
+        <v>2.292927307078116</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.376447582624925</v>
+        <v>1.279311675254203</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.296304501541475</v>
+        <v>4.238022957119042</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347706</v>
+        <v>3.727898186347704</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.750939177863986</v>
+        <v>-3.019210529037549</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.367815669400954</v>
+        <v>2.260507128931528</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.376447582624925</v>
+        <v>1.279311675254203</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.29441631443525</v>
+        <v>4.236134770012817</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.71065410488775</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.953192898188339</v>
+        <v>-3.221464249361902</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.281734410874074</v>
+        <v>2.17442587040465</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.174193862300571</v>
+        <v>1.07705795492985</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.1678843118435</v>
+        <v>4.109602767421068</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343069</v>
+        <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.114761323715594</v>
+        <v>-3.383032674889157</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.215541050873325</v>
+        <v>2.1082325104039</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.047410938502692</v>
+        <v>0.9502750311319702</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.090248567774926</v>
+        <v>4.031967023352492</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389352</v>
+        <v>3.75459613538935</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.247062615813148</v>
+        <v>-3.51533396698671</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.175693940900222</v>
+        <v>2.068385400430797</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.047410938502692</v>
+        <v>0.9502750311319702</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.103321974640844</v>
+        <v>4.04504043021841</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378394</v>
+        <v>3.749882691378392</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.432930926652378</v>
+        <v>-3.70120227782594</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.09335181334747</v>
+        <v>1.986043272878045</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8888453451827445</v>
+        <v>0.7917094378120225</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.000187815431815</v>
+        <v>3.941906271009382</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006977</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.460831713761851</v>
+        <v>-3.729103064935413</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.080715539630683</v>
+        <v>1.973406999161258</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8542484210398097</v>
+        <v>0.7571125136690877</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.977953702073057</v>
+        <v>3.919672157650623</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787388</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.583357816464745</v>
+        <v>-3.851629167638307</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.028469542526724</v>
+        <v>1.921161002057299</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7317223183369158</v>
+        <v>0.6345864109661938</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.901202484428519</v>
+        <v>3.842920940006086</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585939</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.813872312650333</v>
+        <v>-4.082143663823896</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.002969703642992</v>
+        <v>1.895661163173567</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5012078221513271</v>
+        <v>0.4040719147806051</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.829599746307669</v>
+        <v>3.771318201885236</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814666</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.070593130645157</v>
+        <v>-4.338864481818719</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.040593095446909</v>
+        <v>1.933284554977485</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3927932480075123</v>
+        <v>0.2956573406367903</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.904862720823227</v>
+        <v>3.846581176400794</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237096</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.224579548421298</v>
+        <v>-4.49285089959486</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.047978797482093</v>
+        <v>1.940670257012669</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3927932480075123</v>
+        <v>0.2956573406367903</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.973842989968867</v>
+        <v>3.915561445546434</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423388</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.174057644593632</v>
+        <v>-4.442328995767194</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.054238761133281</v>
+        <v>1.946930220663856</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3927932480075123</v>
+        <v>0.2956573406367903</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.959894192088989</v>
+        <v>3.901612647666555</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609754</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.426532798601357</v>
+        <v>-4.694804149774918</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.965119188585605</v>
+        <v>1.85781064811618</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3927932480075123</v>
+        <v>0.2956573406367903</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.971764681144403</v>
+        <v>3.913483136721969</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973159</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.719428555080769</v>
+        <v>-4.98769990625433</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.849171420512784</v>
+        <v>1.741862880043359</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3927932480075123</v>
+        <v>0.2956573406367903</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.972975215663346</v>
+        <v>3.914693671240912</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251947</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.87697262681021</v>
+        <v>-5.145243977983772</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.790275534048328</v>
+        <v>1.682966993578904</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3258914428672378</v>
+        <v>0.2287555354965158</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.936955874806503</v>
+        <v>3.87867433038407</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916204</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.154937022393484</v>
+        <v>-5.423208373567046</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.674167628551208</v>
+        <v>1.566859088081784</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2362717085817535</v>
+        <v>0.1391358012110315</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.878261886971401</v>
+        <v>3.819980342548968</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.66796230683033</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.271904715032375</v>
+        <v>-5.540176066205937</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.789584608194696</v>
+        <v>1.682276067725271</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2362717085817535</v>
+        <v>0.1391358012110315</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.040465943670446</v>
+        <v>3.982184399248013</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071553</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.356622657253328</v>
+        <v>-5.62489400842689</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.750544069270129</v>
+        <v>1.643235528800704</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1511556796537071</v>
+        <v>0.05401977228298516</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.984242964277432</v>
+        <v>3.925961419854999</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868149</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.438557475522211</v>
+        <v>-5.706828826695773</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.727999559531067</v>
+        <v>1.620691019061642</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1412209340666269</v>
+        <v>0.04408502669590497</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.988511534493675</v>
+        <v>3.930229990071242</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332694</v>
+        <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.540533597770619</v>
+        <v>-5.80880494894418</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.696134749087606</v>
+        <v>1.588826208618181</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.03924481181821937</v>
+        <v>-0.0578910955525026</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.936251499600533</v>
+        <v>3.8779699551781</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231811</v>
+        <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.430527314293397</v>
+        <v>-5.698798665466959</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.73229014972267</v>
+        <v>1.624981609253246</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.06244938373549458</v>
+        <v>-0.0346865236352274</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.942327129995073</v>
+        <v>3.88404558557264</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818524</v>
+        <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.287467738552472</v>
+        <v>-5.555739089726034</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.793763990741015</v>
+        <v>1.68645545027159</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.07046281032547386</v>
+        <v>-0.02667309704524812</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.951385196671035</v>
+        <v>3.893103652248602</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77723741205179</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.986021013080634</v>
+        <v>-5.254292364254196</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.921603563812286</v>
+        <v>1.814295023342861</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3719095357973111</v>
+        <v>0.2747736284265891</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.139514114836674</v>
+        <v>4.08123257041424</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679626</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.010611257315818</v>
+        <v>-5.27888260848938</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.912738643870923</v>
+        <v>1.805430103401498</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3719095357973111</v>
+        <v>0.2747736284265891</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.140485292589384</v>
+        <v>4.082203748166951</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474161</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.764550193486752</v>
+        <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.959572881309298</v>
+        <v>-5.22784423248286</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.780364616649285</v>
+        <v>1.826688358183861</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3719095357973111</v>
+        <v>0.2747736284265891</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.987695914965139</v>
+        <v>4.083046652546706</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969545</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.783588292360897</v>
+        <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.918433586442667</v>
+        <v>-5.186704937616229</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.815858433470083</v>
+        <v>1.862182175004659</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4130488306639419</v>
+        <v>0.31591292329322</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.031417590759263</v>
+        <v>4.12676832834083</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700481</v>
+        <v>3.825752932700479</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.599772288484832</v>
+        <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.807827446363065</v>
+        <v>-5.076098797536627</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.676284885625858</v>
+        <v>1.722608627160434</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5236549707435439</v>
+        <v>0.426519063372822</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.913965270930959</v>
+        <v>4.009316008512526</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077643</v>
+        <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.603274332558795</v>
+        <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.938408180893908</v>
+        <v>-5.206679532067469</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.627554635887485</v>
+        <v>1.673878377422061</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3930742362127014</v>
+        <v>0.2959383288419795</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.839118874286417</v>
+        <v>3.934469611867984</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.77502886083346</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.587701151634878</v>
+        <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.773911846702946</v>
+        <v>-5.042183197876508</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.677779988639952</v>
+        <v>1.724103730174528</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3930742362127014</v>
+        <v>0.2959383288419795</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.823545693362499</v>
+        <v>3.918896430944066</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077629</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.586888862071308</v>
+        <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.801281779387378</v>
+        <v>-5.06955313056094</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.666019726002609</v>
+        <v>1.712343467537185</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3930742362127014</v>
+        <v>0.2959383288419795</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.822733403798929</v>
+        <v>3.918084141380496</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.59675764119638</v>
+        <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.811666974277268</v>
+        <v>-5.079938325450829</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.671734427171726</v>
+        <v>1.718058168706302</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3826890413228121</v>
+        <v>0.2855531339520901</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.826371065990068</v>
+        <v>3.921721803571635</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735285</v>
+        <v>3.834415493735283</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.667594646972805</v>
+        <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.830255132999492</v>
+        <v>-5.098526484173054</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.735136169459261</v>
+        <v>1.781459910993837</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3641008826005868</v>
+        <v>0.2669649752298648</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.886055176533158</v>
+        <v>3.981405914114725</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.664463657791104</v>
+        <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.830553679695528</v>
+        <v>-5.09882503086909</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.731885761599145</v>
+        <v>1.778209503133721</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3641008826005868</v>
+        <v>0.2669649752298648</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.882924187351456</v>
+        <v>3.978274924933023</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.81564321210886</v>
+        <v>3.815643212108858</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.668994552730495</v>
+        <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.729730546005101</v>
+        <v>-4.998001897178662</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.776745910014708</v>
+        <v>1.823069651549284</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3765650980849406</v>
+        <v>0.2794291907142186</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.89493361158146</v>
+        <v>3.990284349163027</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121469</v>
+        <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.669123806209039</v>
+        <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.538949185252694</v>
+        <v>-4.807220536426255</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.853187707794214</v>
+        <v>1.89951144932879</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.567346458837348</v>
+        <v>0.470210551466626</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.009531681511447</v>
+        <v>4.104882419093015</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906082</v>
+        <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.648960651946635</v>
+        <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.520432331210873</v>
+        <v>-4.788703682384435</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.840431295148538</v>
+        <v>1.886755036683114</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5802765882625562</v>
+        <v>0.4831406808918342</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.997126604904169</v>
+        <v>4.092477342485736</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912987</v>
+        <v>3.785761685912985</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.683927588558694</v>
+        <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.495239146709555</v>
+        <v>-4.763510497883117</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.885475505561124</v>
+        <v>1.9317992470957</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6054697727638746</v>
+        <v>0.5083338653931526</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.047209452217018</v>
+        <v>4.142560189798586</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539896</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.677614156460131</v>
+        <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.483185019796593</v>
+        <v>-4.751456370970154</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.883983724227747</v>
+        <v>1.930307465762323</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6175238996768374</v>
+        <v>0.5203879923061154</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.048128496266234</v>
+        <v>4.143479233847802</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811011</v>
+        <v>3.725010844811009</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.679494786644267</v>
+        <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.489808266486951</v>
+        <v>-4.758079617660512</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.883215055735739</v>
+        <v>1.929538797270316</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6109006529864791</v>
+        <v>0.513764745615757</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.046035178436155</v>
+        <v>4.141385916017722</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382921</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.69234581252215</v>
+        <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.386927676958358</v>
+        <v>-4.65519902813192</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.937218317425059</v>
+        <v>1.983542058959635</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.713781242515072</v>
+        <v>0.6166453351443499</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.120614558031193</v>
+        <v>4.215965295612761</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760317</v>
+        <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.712548482695744</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.410369716138445</v>
+        <v>-4.678641067312006</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.948044171926619</v>
+        <v>1.994367913461194</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.713781242515072</v>
+        <v>0.6166453351443499</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.140817228204787</v>
+        <v>4.236167965786355</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781707</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.712548482695744</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.428442224430056</v>
+        <v>-4.696713575603618</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.940815168609974</v>
+        <v>1.98713891014455</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.713781242515072</v>
+        <v>0.6166453351443499</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.140817228204787</v>
+        <v>4.236167965786355</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082836</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.67280039628921</v>
+        <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.659616018306688</v>
+        <v>-4.92788736948025</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.808597564652788</v>
+        <v>1.854921306187364</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.713781242515072</v>
+        <v>0.6166453351443499</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.101069141798254</v>
+        <v>4.196419879379821</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943587</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.67982301528615</v>
+        <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.628329997766233</v>
+        <v>-4.896601348939795</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.82813459186591</v>
+        <v>1.874458333400486</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.7450672630555274</v>
+        <v>0.6479313556848053</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.126863373119467</v>
+        <v>4.222214110701034</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677825</v>
+        <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.778994014859055</v>
+        <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.475304605652949</v>
+        <v>-4.74357595682651</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.988515748284128</v>
+        <v>2.034839489818704</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.8980926551688115</v>
+        <v>0.8009567477980895</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.317849607960342</v>
+        <v>4.413200345541909</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073885</v>
+        <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.966460239767347</v>
+        <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.503611919526219</v>
+        <v>-4.771883270699781</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.164659047643112</v>
+        <v>2.210982789177688</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.8980926551688115</v>
+        <v>0.8009567477980895</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.505315832868634</v>
+        <v>4.600666570450201</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.843336153821181</v>
+        <v>3.394447138332764</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.935863191121429</v>
+        <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.731651521224607</v>
+        <v>-4.933379694537205</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.042846158317839</v>
+        <v>2.115787170996801</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.6700530534704233</v>
+        <v>0.6394603239606648</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.337895023203684</v>
+        <v>4.473171667501829</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240812.xlsx
+++ b/tame_output/ON/bt/strategyON_20240812.xlsx
@@ -605,12 +605,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,37 +844,37 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>78.2%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.7%</t>
+          <t>109.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>124.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>427.4%</t>
+          <t>426.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-291.4%</t>
+          <t>-290.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-21.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-56.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2053"/>
+  <dimension ref="A1:G2054"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213492</v>
+        <v>3.223539378213493</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382324</v>
+        <v>3.235981977382325</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812098</v>
+        <v>3.684843823812099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784109</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714426</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161979</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321636</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347704</v>
+        <v>3.727898186347705</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887749</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.394447138332764</v>
+        <v>3.699135800903172</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
@@ -48780,6 +48780,29 @@
       </c>
       <c r="G2053" t="n">
         <v>4.473171667501829</v>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" s="2" t="n">
+        <v>45516</v>
+      </c>
+      <c r="B2054" t="n">
+        <v>3.38103515058143</v>
+      </c>
+      <c r="C2054" t="n">
+        <v>3.898426827050737</v>
+      </c>
+      <c r="D2054" t="n">
+        <v>-4.933379694537205</v>
+      </c>
+      <c r="E2054" t="n">
+        <v>2.115787170996801</v>
+      </c>
+      <c r="F2054" t="n">
+        <v>0.6394603239606648</v>
+      </c>
+      <c r="G2054" t="n">
+        <v>3.891490624037105</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240812.xlsx
+++ b/tame_output/ON/bt/strategyON_20240812.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>51.5%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>94.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,37 +844,37 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>31.9%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>69.0%</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>32.2%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>106.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-78.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.6%</t>
+          <t>110.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>426.8%</t>
+          <t>430.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-654.9%</t>
+          <t>-640.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-164.6%</t>
+          <t>-158.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-290.6%</t>
+          <t>-325.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-160.0%</t>
+          <t>-151.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.4%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-56.9%</t>
+          <t>-29.0%</t>
         </is>
       </c>
     </row>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213493</v>
+        <v>3.223539378213492</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382325</v>
+        <v>3.235981977382324</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.063275597136876</v>
+        <v>-8.885076515482016</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4469224730537209</v>
+        <v>-0.3756428403917771</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.42616506495983</v>
+        <v>-1.398954367379046</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.323045151138879</v>
+        <v>2.33937156968735</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.938696940799284</v>
+        <v>-8.760497859144424</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3959518659626253</v>
+        <v>-0.3246722333006811</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.42616506495983</v>
+        <v>-1.398954367379046</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.324184295694938</v>
+        <v>2.340510714243409</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.991592228843571</v>
+        <v>-8.813393147188711</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4144762070182324</v>
+        <v>-0.3431965743562881</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.421209718871384</v>
+        <v>-1.393999021290599</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.329791277510113</v>
+        <v>2.346117696058584</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.919459053555689</v>
+        <v>-8.741259971900829</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3798892326644432</v>
+        <v>-0.3086096000024994</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.421209718871384</v>
+        <v>-1.393999021290599</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.33552498174875</v>
+        <v>2.351851400297221</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.848092660946042</v>
+        <v>-8.669893579291182</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3610799380144494</v>
+        <v>-0.2898003053525056</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.349843326261736</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.368607554920673</v>
+        <v>2.384933973469144</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.754633626960818</v>
+        <v>-8.576434545305958</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3335798057332675</v>
+        <v>-0.2623001730713233</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.349843326261736</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.358724073607766</v>
+        <v>2.375050492156237</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.743980445407386</v>
+        <v>-8.565781363752526</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3311530936112685</v>
+        <v>-0.2598734609493243</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.349843326261736</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.356889513108392</v>
+        <v>2.373215931656863</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.646073406730896</v>
+        <v>-8.467874325076036</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2922905931141329</v>
+        <v>-0.221010960452189</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.28185757640118</v>
+        <v>-1.254646878820395</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.397380648051265</v>
+        <v>2.413707066599736</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.622119865754938</v>
+        <v>-8.443920784100078</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2820406705782563</v>
+        <v>-0.2107610379163121</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.257904035425222</v>
+        <v>-1.230693337844438</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.412421278782333</v>
+        <v>2.428747697330804</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.358059927432141</v>
+        <v>-8.179860845777281</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1896770114108897</v>
+        <v>-0.1183973787489458</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.9938440971024258</v>
+        <v>-0.9666333995216414</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.557596925614259</v>
+        <v>2.57392334416273</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.650980303927303</v>
+        <v>-7.472781222272443</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.09036780433074476</v>
+        <v>0.1616474369926886</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.9938440971024258</v>
+        <v>-0.9666333995216414</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.554809891953958</v>
+        <v>2.571136310502429</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.610796005561112</v>
+        <v>-7.432596923906252</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1067851475650623</v>
+        <v>0.1780647802270061</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9536597987362351</v>
+        <v>-0.9264491011554506</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.579264094861514</v>
+        <v>2.595590513409984</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.44739613462175</v>
+        <v>-7.26919705296689</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1715119171615642</v>
+        <v>0.242791549823508</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.7902599277968726</v>
+        <v>-0.7630492302160882</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.676670838645888</v>
+        <v>2.692997257194359</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.213914912392151</v>
+        <v>-7.035715830737291</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2728288348912562</v>
+        <v>0.3441084675532</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.556778705567274</v>
+        <v>-0.5295680079864896</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.8246840008215</v>
+        <v>2.841010419369971</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.064248521384636</v>
+        <v>-6.886049439729776</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3298031809813029</v>
+        <v>0.4010828136432467</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4638752143247381</v>
+        <v>-0.4366645167439537</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.877533885254062</v>
+        <v>2.893860303802533</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.93197304775375</v>
+        <v>-6.75377396609889</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3780808571806844</v>
+        <v>0.4493604898426287</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.3315997406938515</v>
+        <v>-0.304389043113067</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.952266656179621</v>
+        <v>2.968593074728092</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.776234715194008</v>
+        <v>-6.598035633539148</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4431912508922178</v>
+        <v>0.514470883554162</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1758614081341099</v>
+        <v>-0.1486507105533255</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.048524716403103</v>
+        <v>3.064851134951573</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.691270048464688</v>
+        <v>-6.513070966809828</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4900834588076046</v>
+        <v>0.5613630914695489</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.09089674140479032</v>
+        <v>-0.06368604382400589</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.112409857664353</v>
+        <v>3.128736276212824</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.796860038237792</v>
+        <v>-6.618660956582932</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3198715332991444</v>
+        <v>0.3911511659610882</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1964867311778947</v>
+        <v>-0.1692760335971102</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.921079934201272</v>
+        <v>2.937406352749742</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.728625453612365</v>
+        <v>-6.550426371957505</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3957097090264017</v>
+        <v>0.4669893416883455</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1780714083053587</v>
+        <v>-0.1508607107245742</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.98067346980188</v>
+        <v>2.99699988835035</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.580685412204765</v>
+        <v>-6.402486330549905</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3350068029012738</v>
+        <v>0.4062864355632176</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1577504923968011</v>
+        <v>-0.1305397948160167</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.872987096658847</v>
+        <v>2.889313515207317</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.527715889950777</v>
+        <v>-6.349516808295917</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.347480625549391</v>
+        <v>0.4187602582113348</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1047809701428122</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.896054823757762</v>
+        <v>2.912381242306233</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.361927693990486</v>
+        <v>-6.183728612335626</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4068352918384139</v>
+        <v>0.4781149245003582</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1047809701428122</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.889094211662669</v>
+        <v>2.90542063021114</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.328564487511717</v>
+        <v>-6.150365405856857</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4346429288110647</v>
+        <v>0.5059225614730085</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1047809701428122</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.903556566043812</v>
+        <v>2.919882984592283</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.220305350389196</v>
+        <v>-6.042106268734336</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4724787041192684</v>
+        <v>0.5437583367812122</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1047809701428122</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.898088686503007</v>
+        <v>2.914415105051478</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.097014215572065</v>
+        <v>-5.918815133917205</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5192932520566975</v>
+        <v>0.5905728847186418</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.01851016467431826</v>
+        <v>0.04572086225510269</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.969561461403862</v>
+        <v>2.985887879952333</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.044317348440774</v>
+        <v>-5.866118266785914</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5480729771465391</v>
+        <v>0.6193526098084834</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.07120703180560944</v>
+        <v>0.09841772938639387</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.008880559919962</v>
+        <v>3.025206978468433</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.800551906457329</v>
+        <v>-5.622352824802469</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6413598622869676</v>
+        <v>0.7126394949489119</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.07120703180560944</v>
+        <v>0.09841772938639387</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.004661268267013</v>
+        <v>3.020987686815483</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.710776234080857</v>
+        <v>-5.532577152425997</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6793944451575729</v>
+        <v>0.7506740778195167</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1328064767199195</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.043745249135615</v>
+        <v>3.060071667684086</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.460925840131782</v>
+        <v>-5.282726758476922</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7720766777209045</v>
+        <v>0.8433563103828488</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1328064767199195</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.036487324119317</v>
+        <v>3.052813742667788</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.28503374766435</v>
+        <v>-5.10683466600949</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8460326382285261</v>
+        <v>0.9173122708904704</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1328064767199195</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.040086447639966</v>
+        <v>3.056412866188436</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.113587284641887</v>
+        <v>-4.935388202987027</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9279387294920651</v>
+        <v>0.9992183621540094</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.3042529397423826</v>
+        <v>0.331463637323167</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.156281831507997</v>
+        <v>3.172608250056468</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.039297718903548</v>
+        <v>-4.861098637248688</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9566750334036977</v>
+        <v>1.027954666065642</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3785425054807219</v>
+        <v>0.4057532030615063</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.199876048567297</v>
+        <v>3.216202467115768</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.975661976669613</v>
+        <v>-4.797462895014753</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9868241313515891</v>
+        <v>1.058103764013533</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4421782477146564</v>
+        <v>0.4693889452954408</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.242752294961976</v>
+        <v>3.259078713510446</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.864235217343693</v>
+        <v>-4.686036135688833</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.012589093865753</v>
+        <v>1.083868726527697</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4421782477146564</v>
+        <v>0.4693889452954408</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.223946553745771</v>
+        <v>3.240272972294242</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.874737840408982</v>
+        <v>-4.696538758754122</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.010131121264515</v>
+        <v>1.081410753926459</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4316756246493675</v>
+        <v>0.458886322230152</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.219388056531475</v>
+        <v>3.235714475079946</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.802495272237787</v>
+        <v>-4.624296190582927</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.042957462367813</v>
+        <v>1.114237095029757</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4316756246493675</v>
+        <v>0.458886322230152</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.223317370366296</v>
+        <v>3.239643788914766</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.784781585359922</v>
+        <v>-4.606582503705062</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.050721521036299</v>
+        <v>1.122001153698243</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4348569535462843</v>
+        <v>0.4620676511270688</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.225904751621786</v>
+        <v>3.242231170170256</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.675976699880195</v>
+        <v>-4.497777618225335</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.091241546448183</v>
+        <v>1.162521179110127</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4348569535462843</v>
+        <v>0.4620676511270688</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.222902822841779</v>
+        <v>3.23922924139025</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.455955901843184</v>
+        <v>-4.277756820188324</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.180828902673601</v>
+        <v>1.252108535335545</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5760767986142645</v>
+        <v>0.603287496195049</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.309213766893182</v>
+        <v>3.325540185441652</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.323088212779907</v>
+        <v>-4.144889131125047</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.249870161100736</v>
+        <v>1.32114979376268</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5760767986142645</v>
+        <v>0.603287496195049</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.325107949695005</v>
+        <v>3.341434368243475</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.202915129415408</v>
+        <v>-4.024716047760548</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.299085238886837</v>
+        <v>1.370364871548781</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6962498819787635</v>
+        <v>0.7234605795595479</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.398357644154006</v>
+        <v>3.414684062702476</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.067661768085431</v>
+        <v>-3.889462686430571</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.363274685980268</v>
+        <v>1.434554318642212</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8315032433087406</v>
+        <v>0.858713940889525</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.489597763513432</v>
+        <v>3.505924182061903</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.127536595443123</v>
+        <v>-3.949337513788263</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.325362246438617</v>
+        <v>1.396641879100561</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7716284159510485</v>
+        <v>0.7988391135318329</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.439710358500243</v>
+        <v>3.456036777048713</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.007716364532286</v>
+        <v>-3.829517282877426</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.38857950803716</v>
+        <v>1.459859140699104</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7716284159510485</v>
+        <v>0.7988391135318329</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.454999527734451</v>
+        <v>3.471325946282922</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.010186070994092</v>
+        <v>-3.831986989339232</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.295235824774879</v>
+        <v>1.366515457436823</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7691587094892423</v>
+        <v>0.7963694070700267</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.361161903179809</v>
+        <v>3.37748832172828</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.078556257318102</v>
+        <v>-3.900357175663242</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.187149611730576</v>
+        <v>1.258429244392521</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7784344085254572</v>
+        <v>0.8056451061062416</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.285989184086839</v>
+        <v>3.30231560263531</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.092344310165148</v>
+        <v>-3.914145228510288</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.172071099223649</v>
+        <v>1.243350731885593</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7784344085254572</v>
+        <v>0.8056451061062416</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.276425892718731</v>
+        <v>3.292752311267201</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.147864386057738</v>
+        <v>-3.969665304402878</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.286893905558816</v>
+        <v>1.35817353822076</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7784344085254572</v>
+        <v>0.8056451061062416</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.413456729410933</v>
+        <v>3.429783147959404</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.972390126265269</v>
+        <v>-3.794191044610409</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.361650841467591</v>
+        <v>1.432930474129535</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7784344085254572</v>
+        <v>0.8056451061062416</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.418023961402721</v>
+        <v>3.434350379951192</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.083326378906517</v>
+        <v>-3.905127297251657</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.293018369172299</v>
+        <v>1.364298001834243</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7784344085254572</v>
+        <v>0.8056451061062416</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.393765990163928</v>
+        <v>3.410092408712399</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.049662833434235</v>
+        <v>-3.871463751779376</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.235022100762661</v>
+        <v>1.306301733424606</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8120979539977391</v>
+        <v>0.8393086515785235</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.342502430848747</v>
+        <v>3.358828849397217</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.989810214230512</v>
+        <v>-3.811611132575652</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.269135534876283</v>
+        <v>1.340415167538227</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8120979539977391</v>
+        <v>0.8393086515785235</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.352674817280879</v>
+        <v>3.36900123582935</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.903566751204134</v>
+        <v>-3.725367669549275</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.298579190660694</v>
+        <v>1.369858823322639</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8120979539977391</v>
+        <v>0.8393086515785235</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.34762108785474</v>
+        <v>3.36394750640321</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.948873570603114</v>
+        <v>-3.770674488948255</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.272232238345628</v>
+        <v>1.343511871007572</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7712877909885083</v>
+        <v>0.7984984885692927</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.314910765493726</v>
+        <v>3.331237184042197</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.977906675305416</v>
+        <v>-3.799707593650556</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.261170869497809</v>
+        <v>1.332450502159753</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7712877909885083</v>
+        <v>0.7984984885692927</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.315462638526828</v>
+        <v>3.331789057075299</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.885096193854556</v>
+        <v>-3.706897112199697</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.227567753969518</v>
+        <v>1.298847386631462</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8640982724393677</v>
+        <v>0.8913089700201521</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.300421619288709</v>
+        <v>3.31674803783718</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.929485663183984</v>
+        <v>-3.751286581529125</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.211685442162348</v>
+        <v>1.282965074824292</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.81970880310994</v>
+        <v>0.8469195006907244</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.275661413615654</v>
+        <v>3.291987832164124</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.046027268289326</v>
+        <v>-3.867828186634468</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.160144508631934</v>
+        <v>1.231424141293878</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7031671980045973</v>
+        <v>0.7303778955853817</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.200812159064171</v>
+        <v>3.217138577612642</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.085951362871898</v>
+        <v>-3.907752281217039</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.149666166629573</v>
+        <v>1.220945799291516</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7031671980045973</v>
+        <v>0.7303778955853817</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.206303454894838</v>
+        <v>3.222629873443309</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.113731760773251</v>
+        <v>-3.935532679118392</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.150051209237571</v>
+        <v>1.221330841899514</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6753868001032441</v>
+        <v>0.7025974976840286</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.201132417922565</v>
+        <v>3.217458836471036</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.23211243350339</v>
+        <v>-4.05391335184853</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9410546601461685</v>
+        <v>1.012334292808112</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6081689479522679</v>
+        <v>0.6353796455330524</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.999157426632633</v>
+        <v>3.015483845181103</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.340726511946721</v>
+        <v>-4.162527430291862</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.017758689488042</v>
+        <v>1.089038322149986</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6081689479522679</v>
+        <v>0.6353796455330524</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.119307087351839</v>
+        <v>3.135633505900309</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.305317473698578</v>
+        <v>-4.127118392043719</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.046435330889622</v>
+        <v>1.117714963551566</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6081689479522679</v>
+        <v>0.6353796455330524</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.133820113454162</v>
+        <v>3.150146532002632</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.266933811140427</v>
+        <v>-4.088734729485568</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.059208237255251</v>
+        <v>1.130487869917195</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6465526105104191</v>
+        <v>0.6737633080912035</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.154269752331421</v>
+        <v>3.170596170879892</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.089817481105261</v>
+        <v>-3.911618399450401</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.126783798114619</v>
+        <v>1.198063430776563</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6465526105104191</v>
+        <v>0.6737633080912035</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.150998781176723</v>
+        <v>3.167325199725194</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.134909725938806</v>
+        <v>-3.956710644283947</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.109430291943114</v>
+        <v>1.180709924605058</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5846565673410293</v>
+        <v>0.6118672649218138</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.114544547037002</v>
+        <v>3.130870965585473</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.955534304700039</v>
+        <v>-3.77733522304518</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.174967435745035</v>
+        <v>1.24624706840698</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.741433325511748</v>
+        <v>0.7686440230925324</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.202397577245848</v>
+        <v>3.218723995794318</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.000548518220645</v>
+        <v>-3.822349436565786</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.137769205668383</v>
+        <v>1.209048838330327</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7110844301971434</v>
+        <v>0.7382951277779278</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.164995695388675</v>
+        <v>3.181322113937145</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.267553028493081</v>
+        <v>-4.089353946838221</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.036658963898354</v>
+        <v>1.107938596560298</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5167213921541949</v>
+        <v>0.5439320897349793</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.054069434901851</v>
+        <v>3.070395853450322</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.368750809930254</v>
+        <v>-4.190551728275394</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9953837732199866</v>
+        <v>1.066663405881931</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4483125786088757</v>
+        <v>0.4755232761896601</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.012228068671161</v>
+        <v>3.028554487219632</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.362239843315941</v>
+        <v>-4.184040761661081</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9955881214200284</v>
+        <v>1.066867754081972</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4483125786088757</v>
+        <v>0.4755232761896601</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.009828030225478</v>
+        <v>3.026154448773949</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.343201715608644</v>
+        <v>-4.165002633953784</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9997280917111924</v>
+        <v>1.071007724373136</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3901289672776811</v>
+        <v>0.4173396648584656</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.971442582635006</v>
+        <v>2.987769001183477</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.395717517883464</v>
+        <v>-4.217518436228604</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.098016172435454</v>
+        <v>1.169295805097398</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3901289672776811</v>
+        <v>0.4173396648584656</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.090736984269197</v>
+        <v>3.107063402817667</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.409584279217382</v>
+        <v>-4.231385197562522</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.093302796888021</v>
+        <v>1.164582429549965</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3522710505438582</v>
+        <v>0.3794817481246426</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.068855563215036</v>
+        <v>3.085181981763507</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.364780107677452</v>
+        <v>-4.217390913282669</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.117232995900919</v>
+        <v>1.176188673658832</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3522710505438582</v>
+        <v>0.4376494367892281</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.074864093611962</v>
+        <v>3.126091125359184</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.21703713744245</v>
+        <v>-4.069647943047666</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.074280405272119</v>
+        <v>1.133236083030033</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5200784077787414</v>
+        <v>0.6054567940241112</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.073498729230092</v>
+        <v>3.124725760977313</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.300858358717148</v>
+        <v>-4.153469164322365</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.043545538293721</v>
+        <v>1.102501216051634</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5200784077787414</v>
+        <v>0.6054567940241112</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.076292350761573</v>
+        <v>3.127519382508794</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.294705652664364</v>
+        <v>-4.147316458269581</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.046668969106493</v>
+        <v>1.105624646864406</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5262311138315257</v>
+        <v>0.6116095000768955</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.080646322784902</v>
+        <v>3.131873354532123</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.311514950814866</v>
+        <v>-4.164125756420082</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.039025726586402</v>
+        <v>1.097981404344316</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.509421815681024</v>
+        <v>0.5948002019263938</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.069641220634711</v>
+        <v>3.120868252381933</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.249216952038743</v>
+        <v>-4.10182775764396</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.130280479893672</v>
+        <v>1.189236157651586</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.554716079955466</v>
+        <v>0.6400944662008359</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.163153332996197</v>
+        <v>3.214380364743419</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.047426754373586</v>
+        <v>-3.900037559978802</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.013288560673863</v>
+        <v>1.072244238431776</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7527342721246204</v>
+        <v>0.8381126583699903</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.084256250011816</v>
+        <v>3.135483281759039</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.09831346705978</v>
+        <v>-3.950924272664997</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.06322410792156</v>
+        <v>1.122179785679473</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7018475594384259</v>
+        <v>0.7872259456837958</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.124014454722275</v>
+        <v>3.175241486469497</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.011702724409973</v>
+        <v>-3.86431353001519</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.112496141097526</v>
+        <v>1.17145181885544</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7804732906435842</v>
+        <v>0.865851676888954</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.185817629561414</v>
+        <v>3.237044661308635</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.071912022415258</v>
+        <v>-3.924522828020474</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.086948402720084</v>
+        <v>1.145904080477998</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7202639926382997</v>
+        <v>0.8056423788836695</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.148228031582915</v>
+        <v>3.199455063330137</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.995489975983332</v>
+        <v>-3.848100781588547</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.116008839332783</v>
+        <v>1.174964517090697</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7202639926382997</v>
+        <v>0.8056423788836695</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.146719649622843</v>
+        <v>3.197946681370065</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.951116844344763</v>
+        <v>-3.803727649949979</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.133620959423647</v>
+        <v>1.192576637181561</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7646371242768683</v>
+        <v>0.8500155105222381</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.173206396041421</v>
+        <v>3.224433427788642</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.973597195203648</v>
+        <v>-3.826208000808863</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.119022613218684</v>
+        <v>1.177978290976597</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7646371242768683</v>
+        <v>0.8500155105222381</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.167600190180011</v>
+        <v>3.218827221927233</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.925941464642592</v>
+        <v>-3.778552270247808</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.144466662470911</v>
+        <v>1.203422340228824</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8122928548379239</v>
+        <v>0.8976712410832938</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.202575385544449</v>
+        <v>3.253802417291671</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.825423306143837</v>
+        <v>-3.678034111749053</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.189566299245137</v>
+        <v>1.248521977003051</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9128110133366785</v>
+        <v>0.9981893995820483</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.267778654018427</v>
+        <v>3.319005685765648</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.809517976711485</v>
+        <v>-3.6621287823167</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.18268310349395</v>
+        <v>1.241638781251864</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8336983526274395</v>
+        <v>0.9190767388728094</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.207065730068756</v>
+        <v>3.258292761815977</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.764679575103087</v>
+        <v>-3.617290380708302</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.204716166747938</v>
+        <v>1.263671844505852</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.838241785572309</v>
+        <v>0.9236201718176789</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.213889492446306</v>
+        <v>3.265116524193528</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.784178031345095</v>
+        <v>-3.636788836950311</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.201077723882213</v>
+        <v>1.260033401640127</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7901571442924047</v>
+        <v>0.8755355305377746</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.189199647309441</v>
+        <v>3.240426679056663</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.739975194259194</v>
+        <v>-3.59258599986441</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.22463846124441</v>
+        <v>1.283594139002324</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8343599813783051</v>
+        <v>0.919738367623675</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.221600952088818</v>
+        <v>3.272827983836041</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.747534860096241</v>
+        <v>-3.600145665701457</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.220024595378839</v>
+        <v>1.278980273136753</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8891633853881244</v>
+        <v>0.9745417716334943</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.252892994963958</v>
+        <v>3.30412002671118</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.589243442556969</v>
+        <v>-3.441854248162185</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.334588927577588</v>
+        <v>1.393544605335501</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8891633853881244</v>
+        <v>0.9745417716334943</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.304140760146997</v>
+        <v>3.355367791894219</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.381601438922493</v>
+        <v>-3.234212244527709</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.416086433625631</v>
+        <v>1.475042111383545</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.096805389022601</v>
+        <v>1.18218377526797</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.427166666921936</v>
+        <v>3.478393698669158</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.330569346199965</v>
+        <v>-3.183180151805181</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.431447498952912</v>
+        <v>1.490403176710826</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.147837481745129</v>
+        <v>1.233215867990499</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.452734150793723</v>
+        <v>3.503961182540945</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.265345165072759</v>
+        <v>-3.117955970677975</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.4747245754965</v>
+        <v>1.533680253254413</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.213061662872334</v>
+        <v>1.298440049117704</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.509056063562751</v>
+        <v>3.560283095309973</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.227918145001625</v>
+        <v>-3.080528950606841</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.485656355824233</v>
+        <v>1.544612033582147</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.218313200901516</v>
+        <v>1.303691587146886</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.508167958679541</v>
+        <v>3.559394990426763</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.248029801036334</v>
+        <v>-3.100640606641549</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.478868485741591</v>
+        <v>1.537824163499504</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.229340545898935</v>
+        <v>1.314718932144305</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.516041158009233</v>
+        <v>3.567268189756454</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.194284986609129</v>
+        <v>-3.046895792214344</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.660924182533683</v>
+        <v>1.719879860291597</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.239403855339397</v>
+        <v>1.324782241584767</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.68263691469472</v>
+        <v>3.733863946441943</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.119502725584116</v>
+        <v>-2.972113531189332</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.810949996161505</v>
+        <v>1.869905673919419</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.31418611636441</v>
+        <v>1.39956450260978</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.847619180527545</v>
+        <v>3.898846212274767</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.093418641320308</v>
+        <v>-2.946029446925524</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.813091605880888</v>
+        <v>1.872047283638801</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.31418611636441</v>
+        <v>1.39956450260978</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.839327156541404</v>
+        <v>3.890554188288626</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.005540728211188</v>
+        <v>-2.858151533816403</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.846435966708315</v>
+        <v>1.905391644466229</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.430111758787761</v>
+        <v>1.515490145033131</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.907075737579194</v>
+        <v>3.958302769326417</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.996648266817904</v>
+        <v>-2.84925907242312</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.86754735699242</v>
+        <v>1.926503034750334</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.430111758787761</v>
+        <v>1.515490145033131</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.924630143305986</v>
+        <v>3.975857175053208</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.165124383787782</v>
+        <v>-3.017735189392998</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.792011957609053</v>
+        <v>1.850967635366967</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.40216392307118</v>
+        <v>1.48754230931655</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.899716489280622</v>
+        <v>3.950943521027844</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.467324854926199</v>
+        <v>-2.319935660531415</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.052401466341548</v>
+        <v>2.111357144099462</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.33181586370077</v>
+        <v>1.41719424994614</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.838777350846237</v>
+        <v>3.890004382593459</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.444603751243046</v>
+        <v>-2.297214556848262</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.052153930311714</v>
+        <v>2.111109608069627</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.33181586370077</v>
+        <v>1.41719424994614</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.829441373343141</v>
+        <v>3.880668405090363</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.573805564537089</v>
+        <v>-2.426416370142304</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.159379330845265</v>
+        <v>2.218335008603179</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.202614050406728</v>
+        <v>1.287992436652097</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.910826411217885</v>
+        <v>3.962053442965107</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.728586571315344</v>
+        <v>-2.58119737692056</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.13454475062761</v>
+        <v>2.193500428385524</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.169246376352251</v>
+        <v>1.254624762597621</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.927883629278846</v>
+        <v>3.979110661026068</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.721531881100171</v>
+        <v>-2.574142686705386</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.134041982703224</v>
+        <v>2.192997660461138</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.176301066567425</v>
+        <v>1.261679452812795</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.928791799397495</v>
+        <v>3.980018831144717</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.694580656773683</v>
+        <v>-2.547191462378898</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.154828626078562</v>
+        <v>2.213784303836475</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.191181412595144</v>
+        <v>1.276559798840514</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.947726160658869</v>
+        <v>3.99895319240609</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.830533664829999</v>
+        <v>-2.683144470435215</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.284550555000995</v>
+        <v>2.343506232758908</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.191181412595144</v>
+        <v>1.276559798840514</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.131829292803828</v>
+        <v>4.18305632455105</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.852941782634871</v>
+        <v>-2.705552588240087</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.267704002782039</v>
+        <v>2.326659680539953</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.191181412595144</v>
+        <v>1.276559798840514</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.123945987706821</v>
+        <v>4.175173019454043</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.881166018212471</v>
+        <v>-2.733776823817687</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.258468308100636</v>
+        <v>2.31742398585855</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.209158165046453</v>
+        <v>1.294536551291823</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.136786038727244</v>
+        <v>4.188013070474466</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.890606944101001</v>
+        <v>-2.743217749706217</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.310945655467071</v>
+        <v>2.369901333224985</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.331585282589844</v>
+        <v>1.416963668835214</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.266496026975126</v>
+        <v>4.317723058722348</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.942880551436643</v>
+        <v>-2.795491357041858</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.292927307078116</v>
+        <v>2.351882984836029</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.279311675254203</v>
+        <v>1.364690061499573</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.238022957119042</v>
+        <v>4.289249988866264</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.019210529037549</v>
+        <v>-2.871821334642764</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.260507128931528</v>
+        <v>2.319462806689442</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.279311675254203</v>
+        <v>1.364690061499573</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.236134770012817</v>
+        <v>4.287361801760039</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.221464249361902</v>
+        <v>-3.074075054967118</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.17442587040465</v>
+        <v>2.233381548162563</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.07705795492985</v>
+        <v>1.162436341175219</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.109602767421068</v>
+        <v>4.160829799168289</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.383032674889157</v>
+        <v>-3.235643480494373</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.1082325104039</v>
+        <v>2.167188188161814</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9502750311319702</v>
+        <v>1.03565341737734</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.031967023352492</v>
+        <v>4.083194055099714</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.51533396698671</v>
+        <v>-3.367944772591926</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.068385400430797</v>
+        <v>2.127341078188711</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9502750311319702</v>
+        <v>1.03565341737734</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.04504043021841</v>
+        <v>4.096267461965633</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.70120227782594</v>
+        <v>-3.553813083431156</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.986043272878045</v>
+        <v>2.044998950635959</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7917094378120225</v>
+        <v>0.8770878240573925</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.941906271009382</v>
+        <v>3.993133302756604</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.729103064935413</v>
+        <v>-3.581713870540629</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.973406999161258</v>
+        <v>2.032362676919171</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7571125136690877</v>
+        <v>0.8424908999144577</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.919672157650623</v>
+        <v>3.970899189397845</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.851629167638307</v>
+        <v>-3.704239973243523</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.921161002057299</v>
+        <v>1.980116679815213</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6345864109661938</v>
+        <v>0.7199647972115638</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.842920940006086</v>
+        <v>3.894147971753308</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.082143663823896</v>
+        <v>-3.934754469429111</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.895661163173567</v>
+        <v>1.954616840931481</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4040719147806051</v>
+        <v>0.4894503010259751</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.771318201885236</v>
+        <v>3.822545233632458</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.338864481818719</v>
+        <v>-4.191475287423936</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.933284554977485</v>
+        <v>1.992240232735398</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2956573406367903</v>
+        <v>0.3810357268821603</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.846581176400794</v>
+        <v>3.897808208148017</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.49285089959486</v>
+        <v>-4.345461705200076</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.940670257012669</v>
+        <v>1.999625934770582</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2956573406367903</v>
+        <v>0.3810357268821603</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.915561445546434</v>
+        <v>3.966788477293656</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.442328995767194</v>
+        <v>-4.29493980137241</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.946930220663856</v>
+        <v>2.005885898421769</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2956573406367903</v>
+        <v>0.3810357268821603</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.901612647666555</v>
+        <v>3.952839679413777</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.694804149774918</v>
+        <v>-4.547414955380135</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.85781064811618</v>
+        <v>1.916766325874093</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2956573406367903</v>
+        <v>0.3810357268821603</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.913483136721969</v>
+        <v>3.964710168469191</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.98769990625433</v>
+        <v>-4.840310711859547</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.741862880043359</v>
+        <v>1.800818557801272</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2956573406367903</v>
+        <v>0.3810357268821603</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.914693671240912</v>
+        <v>3.965920702988135</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.145243977983772</v>
+        <v>-4.997854783588989</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.682966993578904</v>
+        <v>1.741922671336817</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2287555354965158</v>
+        <v>0.3141339217418858</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.87867433038407</v>
+        <v>3.929901362131291</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.423208373567046</v>
+        <v>-5.275819179172262</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.566859088081784</v>
+        <v>1.625814765839697</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1391358012110315</v>
+        <v>0.2245141874564015</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.819980342548968</v>
+        <v>3.87120737429619</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.540176066205937</v>
+        <v>-5.392786871811153</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.682276067725271</v>
+        <v>1.741231745483185</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1391358012110315</v>
+        <v>0.2245141874564015</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.982184399248013</v>
+        <v>4.033411430995234</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.62489400842689</v>
+        <v>-5.477504814032106</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.643235528800704</v>
+        <v>1.702191206558618</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.05401977228298516</v>
+        <v>0.1393981585283551</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.925961419854999</v>
+        <v>3.97718845160222</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.706828826695773</v>
+        <v>-5.55943963230099</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.620691019061642</v>
+        <v>1.679646696819555</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.04408502669590497</v>
+        <v>0.1294634129412749</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.930229990071242</v>
+        <v>3.981457021818464</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.80880494894418</v>
+        <v>-5.661415754549397</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.588826208618181</v>
+        <v>1.647781886376095</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.0578910955525026</v>
+        <v>0.02748729069286737</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.8779699551781</v>
+        <v>3.929196986925322</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.698798665466959</v>
+        <v>-5.551409471072176</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.624981609253246</v>
+        <v>1.683937287011159</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.0346865236352274</v>
+        <v>0.05069186261014258</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.88404558557264</v>
+        <v>3.935272617319862</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.555739089726034</v>
+        <v>-5.40834989533125</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.68645545027159</v>
+        <v>1.745411128029503</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.02667309704524812</v>
+        <v>0.05870528920012186</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.893103652248602</v>
+        <v>3.944330683995824</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.254292364254196</v>
+        <v>-5.106903169859413</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.814295023342861</v>
+        <v>1.873250701100774</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2747736284265891</v>
+        <v>0.3601520146719591</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.08123257041424</v>
+        <v>4.132459602161463</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.27888260848938</v>
+        <v>-5.131493414094597</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.805430103401498</v>
+        <v>1.864385781159411</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2747736284265891</v>
+        <v>0.3601520146719591</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.082203748166951</v>
+        <v>4.133430779914173</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.22784423248286</v>
+        <v>-5.080455038088076</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.826688358183861</v>
+        <v>1.885644035941775</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2747736284265891</v>
+        <v>0.3601520146719591</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.083046652546706</v>
+        <v>4.134273684293928</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.186704937616229</v>
+        <v>-5.039315743221445</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.862182175004659</v>
+        <v>1.921137852762572</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.31591292329322</v>
+        <v>0.4012913095385899</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.12676832834083</v>
+        <v>4.177995360088052</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.076098797536627</v>
+        <v>-4.928709603141844</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.722608627160434</v>
+        <v>1.781564304918348</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.426519063372822</v>
+        <v>0.5118974496181919</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.009316008512526</v>
+        <v>4.060543040259748</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.206679532067469</v>
+        <v>-5.059290337672686</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.673878377422061</v>
+        <v>1.732834055179974</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2959383288419795</v>
+        <v>0.3813167150873494</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.934469611867984</v>
+        <v>3.985696643615206</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.042183197876508</v>
+        <v>-4.894794003481724</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.724103730174528</v>
+        <v>1.783059407932442</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.2959383288419795</v>
+        <v>0.3813167150873494</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.918896430944066</v>
+        <v>3.970123462691289</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.06955313056094</v>
+        <v>-4.922163936166156</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.712343467537185</v>
+        <v>1.771299145295099</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.2959383288419795</v>
+        <v>0.3813167150873494</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.918084141380496</v>
+        <v>3.969311173127719</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.079938325450829</v>
+        <v>-4.932549131056046</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.718058168706302</v>
+        <v>1.777013846464215</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.2855531339520901</v>
+        <v>0.3709315201974601</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.921721803571635</v>
+        <v>3.972948835318857</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.098526484173054</v>
+        <v>-4.951137289778271</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.781459910993837</v>
+        <v>1.84041558875175</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.2669649752298648</v>
+        <v>0.3523433614752348</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.981405914114725</v>
+        <v>4.032632945861947</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.09882503086909</v>
+        <v>-4.951435836474307</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.778209503133721</v>
+        <v>1.837165180891634</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.2669649752298648</v>
+        <v>0.3523433614752348</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.978274924933023</v>
+        <v>4.029501956680246</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.998001897178662</v>
+        <v>-4.850612702783879</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.823069651549284</v>
+        <v>1.882025329307197</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2794291907142186</v>
+        <v>0.3648075769595886</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.990284349163027</v>
+        <v>4.041511380910249</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.807220536426255</v>
+        <v>-4.659831342031472</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.89951144932879</v>
+        <v>1.958467127086703</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.470210551466626</v>
+        <v>0.555588937711996</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.104882419093015</v>
+        <v>4.156109450840237</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.788703682384435</v>
+        <v>-4.641314487989652</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.886755036683114</v>
+        <v>1.945710714441028</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.4831406808918342</v>
+        <v>0.5685190671372042</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.092477342485736</v>
+        <v>4.143704374232959</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.763510497883117</v>
+        <v>-4.616121303488334</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.9317992470957</v>
+        <v>1.990754924853613</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.5083338653931526</v>
+        <v>0.5937122516385226</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.142560189798586</v>
+        <v>4.193787221545808</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.751456370970154</v>
+        <v>-4.604067176575371</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.930307465762323</v>
+        <v>1.989263143520236</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.5203879923061154</v>
+        <v>0.6057663785514854</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.143479233847802</v>
+        <v>4.194706265595023</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.758079617660512</v>
+        <v>-4.610690423265729</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.929538797270316</v>
+        <v>1.988494475028229</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.513764745615757</v>
+        <v>0.5991431318611271</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.141385916017722</v>
+        <v>4.192612947764944</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.65519902813192</v>
+        <v>-4.507809833737136</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.983542058959635</v>
+        <v>2.042497736717548</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6166453351443499</v>
+        <v>0.70202372138972</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.215965295612761</v>
+        <v>4.267192327359982</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.678641067312006</v>
+        <v>-4.531251872917223</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.994367913461194</v>
+        <v>2.053323591219108</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6166453351443499</v>
+        <v>0.70202372138972</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.236167965786355</v>
+        <v>4.287394997533577</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.696713575603618</v>
+        <v>-4.549324381208835</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.98713891014455</v>
+        <v>2.046094587902463</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6166453351443499</v>
+        <v>0.70202372138972</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.236167965786355</v>
+        <v>4.287394997533577</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.92788736948025</v>
+        <v>-4.780498175085467</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.854921306187364</v>
+        <v>1.913876983945277</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6166453351443499</v>
+        <v>0.70202372138972</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.196419879379821</v>
+        <v>4.247646911127044</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.896601348939795</v>
+        <v>-4.749212154545011</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.874458333400486</v>
+        <v>1.933414011158399</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.6479313556848053</v>
+        <v>0.7333097419301754</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.222214110701034</v>
+        <v>4.273441142448257</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.74357595682651</v>
+        <v>-4.596186762431727</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.034839489818704</v>
+        <v>2.093795167576617</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.8009567477980895</v>
+        <v>0.8863351340434595</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.413200345541909</v>
+        <v>4.464427377289131</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.771883270699781</v>
+        <v>-4.624494076304997</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.210982789177688</v>
+        <v>2.269938466935601</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.8009567477980895</v>
+        <v>0.8863351340434595</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.600666570450201</v>
+        <v>4.651893602197424</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903172</v>
+        <v>3.699135800903171</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.933379694537205</v>
+        <v>-4.785990500142422</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.115787170996801</v>
+        <v>2.174742848754714</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.6394603239606648</v>
+        <v>0.7248387102060349</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.473171667501829</v>
+        <v>4.524398699249051</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.38103515058143</v>
+        <v>3.795428881514012</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.898426827050737</v>
+        <v>4.177154815453494</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.933379694537205</v>
+        <v>-4.785990500142422</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.115787170996801</v>
+        <v>2.174742848754714</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.6394603239606648</v>
+        <v>0.7248387102060349</v>
       </c>
       <c r="G2054" t="n">
-        <v>3.891490624037105</v>
+        <v>4.170218612439862</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240812.xlsx
+++ b/tame_output/ON/bt/strategyON_20240812.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-640.2%</t>
+          <t>-639.1%</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-158.7%</t>
+          <t>-158.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.1%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-325.5%</t>
+          <t>-314.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-151.5%</t>
+          <t>-157.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.217390913282669</v>
+        <v>-4.207060613035992</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.176188673658832</v>
+        <v>1.180320793757503</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4376494367892281</v>
+        <v>0.3794817481246426</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.126091125359184</v>
+        <v>3.091190512160433</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.069647943047666</v>
+        <v>-4.059317642800989</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.133236083030033</v>
+        <v>1.137368203128704</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6054567940241112</v>
+        <v>0.5472891053595258</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.124725760977313</v>
+        <v>3.089825147778562</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.153469164322365</v>
+        <v>-4.143138864075688</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.102501216051634</v>
+        <v>1.106633336150305</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6054567940241112</v>
+        <v>0.5472891053595258</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.127519382508794</v>
+        <v>3.092618769310043</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.147316458269581</v>
+        <v>-4.136986158022903</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.105624646864406</v>
+        <v>1.109756766963077</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6116095000768955</v>
+        <v>0.5534418114123101</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.131873354532123</v>
+        <v>3.096972741333372</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.164125756420082</v>
+        <v>-4.153795456173405</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.097981404344316</v>
+        <v>1.102113524442987</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5948002019263938</v>
+        <v>0.5366325132618084</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.120868252381933</v>
+        <v>3.085967639183181</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.10182775764396</v>
+        <v>-4.091497457397283</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.189236157651586</v>
+        <v>1.193368277750257</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.6400944662008359</v>
+        <v>0.5819267775362504</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.214380364743419</v>
+        <v>3.179479751544668</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.900037559978802</v>
+        <v>-3.889707259732125</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.072244238431776</v>
+        <v>1.076376358530447</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.8381126583699903</v>
+        <v>0.7799449697054048</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.135483281759039</v>
+        <v>3.100582668560287</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.950924272664997</v>
+        <v>-3.94059397241832</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.122179785679473</v>
+        <v>1.126311905778144</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7872259456837958</v>
+        <v>0.7290582570192103</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.175241486469497</v>
+        <v>3.140340873270746</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.86431353001519</v>
+        <v>-3.853983229768513</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.17145181885544</v>
+        <v>1.175583938954111</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.865851676888954</v>
+        <v>0.8076839882243686</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.237044661308635</v>
+        <v>3.202144048109884</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.924522828020474</v>
+        <v>-3.914192527773797</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.145904080477998</v>
+        <v>1.150036200576668</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.8056423788836695</v>
+        <v>0.7474746902190841</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.199455063330137</v>
+        <v>3.164554450131385</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.848100781588547</v>
+        <v>-3.83777048134187</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.174964517090697</v>
+        <v>1.179096637189368</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.8056423788836695</v>
+        <v>0.7474746902190841</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.197946681370065</v>
+        <v>3.163046068171314</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.803727649949979</v>
+        <v>-3.793397349703302</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.192576637181561</v>
+        <v>1.196708757280232</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8500155105222381</v>
+        <v>0.7918478218576527</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.224433427788642</v>
+        <v>3.189532814589891</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.826208000808863</v>
+        <v>-3.815877700562186</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.177978290976597</v>
+        <v>1.182110411075268</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8500155105222381</v>
+        <v>0.7918478218576527</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.218827221927233</v>
+        <v>3.183926608728482</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.778552270247808</v>
+        <v>-3.768221970001131</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.203422340228824</v>
+        <v>1.207554460327495</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8976712410832938</v>
+        <v>0.8395035524187083</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.253802417291671</v>
+        <v>3.21890180409292</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.678034111749053</v>
+        <v>-3.667703811502376</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.248521977003051</v>
+        <v>1.252654097101722</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9981893995820483</v>
+        <v>0.9400217109174629</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.319005685765648</v>
+        <v>3.284105072566897</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.6621287823167</v>
+        <v>-3.651798482070023</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.241638781251864</v>
+        <v>1.245770901350535</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.9190767388728094</v>
+        <v>0.8609090502082239</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.258292761815977</v>
+        <v>3.223392148617226</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.617290380708302</v>
+        <v>-3.606960080461625</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.263671844505852</v>
+        <v>1.267803964604523</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.9236201718176789</v>
+        <v>0.8654524831530934</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.265116524193528</v>
+        <v>3.230215910994776</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.636788836950311</v>
+        <v>-3.626458536703633</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.260033401640127</v>
+        <v>1.264165521738797</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8755355305377746</v>
+        <v>0.8173678418731891</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.240426679056663</v>
+        <v>3.205526065857912</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.59258599986441</v>
+        <v>-3.582255699617733</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.283594139002324</v>
+        <v>1.287726259100995</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.919738367623675</v>
+        <v>0.8615706789590896</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.272827983836041</v>
+        <v>3.237927370637289</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.600145665701457</v>
+        <v>-3.58981536545478</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.278980273136753</v>
+        <v>1.283112393235424</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9745417716334943</v>
+        <v>0.9163740829689089</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.30412002671118</v>
+        <v>3.269219413512428</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.441854248162185</v>
+        <v>-3.431523947915508</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.393544605335501</v>
+        <v>1.397676725434172</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9745417716334943</v>
+        <v>0.9163740829689089</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.355367791894219</v>
+        <v>3.320467178695468</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.234212244527709</v>
+        <v>-3.223881944281032</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.475042111383545</v>
+        <v>1.479174231482216</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.18218377526797</v>
+        <v>1.124016086603385</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.478393698669158</v>
+        <v>3.443493085470407</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.183180151805181</v>
+        <v>-3.172849851558504</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.490403176710826</v>
+        <v>1.494535296809497</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.233215867990499</v>
+        <v>1.175048179325913</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.503961182540945</v>
+        <v>3.469060569342194</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.117955970677975</v>
+        <v>-3.107625670431298</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.533680253254413</v>
+        <v>1.537812373353084</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.298440049117704</v>
+        <v>1.240272360453119</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.560283095309973</v>
+        <v>3.525382482111222</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.080528950606841</v>
+        <v>-3.070198650360164</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.544612033582147</v>
+        <v>1.548744153680818</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.303691587146886</v>
+        <v>1.2455238984823</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.559394990426763</v>
+        <v>3.524494377228011</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.100640606641549</v>
+        <v>-3.090310306394872</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.537824163499504</v>
+        <v>1.541956283598175</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.314718932144305</v>
+        <v>1.25655124347972</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.567268189756454</v>
+        <v>3.532367576557703</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.046895792214344</v>
+        <v>-3.036565491967667</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.719879860291597</v>
+        <v>1.724011980390268</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.324782241584767</v>
+        <v>1.266614552920182</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.733863946441943</v>
+        <v>3.698963333243191</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.972113531189332</v>
+        <v>-2.961783230942655</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.869905673919419</v>
+        <v>1.87403779401809</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.39956450260978</v>
+        <v>1.341396813945194</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.898846212274767</v>
+        <v>3.863945599076016</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.946029446925524</v>
+        <v>-2.935699146678847</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.872047283638801</v>
+        <v>1.876179403737472</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.39956450260978</v>
+        <v>1.341396813945194</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.890554188288626</v>
+        <v>3.855653575089875</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.858151533816403</v>
+        <v>-2.847821233569726</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.905391644466229</v>
+        <v>1.9095237645649</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.515490145033131</v>
+        <v>1.457322456368546</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.958302769326417</v>
+        <v>3.923402156127665</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.84925907242312</v>
+        <v>-2.838928772176443</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.926503034750334</v>
+        <v>1.930635154849004</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.515490145033131</v>
+        <v>1.457322456368546</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.975857175053208</v>
+        <v>3.940956561854456</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.017735189392998</v>
+        <v>-3.007404889146321</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.850967635366967</v>
+        <v>1.855099755465637</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.48754230931655</v>
+        <v>1.429374620651965</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.950943521027844</v>
+        <v>3.916042907829092</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.319935660531415</v>
+        <v>-2.309605360284738</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.111357144099462</v>
+        <v>2.115489264198132</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.41719424994614</v>
+        <v>1.359026561281554</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.890004382593459</v>
+        <v>3.855103769394708</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.297214556848262</v>
+        <v>-2.286884256601585</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.111109608069627</v>
+        <v>2.115241728168298</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.41719424994614</v>
+        <v>1.359026561281554</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.880668405090363</v>
+        <v>3.845767791891612</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.426416370142304</v>
+        <v>-2.416086069895627</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.218335008603179</v>
+        <v>2.22246712870185</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.287992436652097</v>
+        <v>1.229824747987512</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.962053442965107</v>
+        <v>3.927152829766356</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.58119737692056</v>
+        <v>-2.570867076673883</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.193500428385524</v>
+        <v>2.197632548484195</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.254624762597621</v>
+        <v>1.196457073933036</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.979110661026068</v>
+        <v>3.944210047827316</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.574142686705386</v>
+        <v>-2.563812386458709</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.192997660461138</v>
+        <v>2.197129780559809</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.261679452812795</v>
+        <v>1.20351176414821</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.980018831144717</v>
+        <v>3.945118217945966</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.547191462378898</v>
+        <v>-2.536861162132221</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.213784303836475</v>
+        <v>2.217916423935146</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.276559798840514</v>
+        <v>1.218392110175929</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.99895319240609</v>
+        <v>3.964052579207339</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.683144470435215</v>
+        <v>-2.672814170188538</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.343506232758908</v>
+        <v>2.347638352857579</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.276559798840514</v>
+        <v>1.218392110175929</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.18305632455105</v>
+        <v>4.148155711352299</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.705552588240087</v>
+        <v>-2.69522228799341</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.326659680539953</v>
+        <v>2.330791800638623</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.276559798840514</v>
+        <v>1.218392110175929</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.175173019454043</v>
+        <v>4.140272406255292</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.733776823817687</v>
+        <v>-2.72344652357101</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.31742398585855</v>
+        <v>2.321556105957221</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.294536551291823</v>
+        <v>1.236368862627237</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.188013070474466</v>
+        <v>4.153112457275714</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.743217749706217</v>
+        <v>-2.73288744945954</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.369901333224985</v>
+        <v>2.374033453323656</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.416963668835214</v>
+        <v>1.358795980170629</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.317723058722348</v>
+        <v>4.282822445523597</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.795491357041858</v>
+        <v>-2.785161056795181</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.351882984836029</v>
+        <v>2.3560151049347</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.364690061499573</v>
+        <v>1.306522372834988</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.289249988866264</v>
+        <v>4.254349375667513</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.871821334642764</v>
+        <v>-2.861491034396087</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.319462806689442</v>
+        <v>2.323594926788113</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.364690061499573</v>
+        <v>1.306522372834988</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.287361801760039</v>
+        <v>4.252461188561288</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.074075054967118</v>
+        <v>-3.063744754720441</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.233381548162563</v>
+        <v>2.237513668261234</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.162436341175219</v>
+        <v>1.104268652510634</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.160829799168289</v>
+        <v>4.125929185969538</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.235643480494373</v>
+        <v>-3.225313180247696</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.167188188161814</v>
+        <v>2.171320308260484</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.03565341737734</v>
+        <v>0.9774857287127546</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.083194055099714</v>
+        <v>4.048293441900963</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.367944772591926</v>
+        <v>-3.357614472345249</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.127341078188711</v>
+        <v>2.131473198287382</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.03565341737734</v>
+        <v>0.9774857287127546</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.096267461965633</v>
+        <v>4.061366848766881</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.553813083431156</v>
+        <v>-3.543482783184479</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.044998950635959</v>
+        <v>2.04913107073463</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8770878240573925</v>
+        <v>0.8189201353928069</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.993133302756604</v>
+        <v>3.958232689557853</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.581713870540629</v>
+        <v>-3.571383570293952</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.032362676919171</v>
+        <v>2.036494797017842</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8424908999144577</v>
+        <v>0.7843232112498721</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.970899189397845</v>
+        <v>3.935998576199093</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.704239973243523</v>
+        <v>-3.693909672996846</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.980116679815213</v>
+        <v>1.984248799913884</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7199647972115638</v>
+        <v>0.6617971085469783</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.894147971753308</v>
+        <v>3.859247358554557</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.934754469429111</v>
+        <v>-3.924424169182434</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.954616840931481</v>
+        <v>1.958748961030152</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4894503010259751</v>
+        <v>0.4312826123613895</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.822545233632458</v>
+        <v>3.787644620433707</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.191475287423936</v>
+        <v>-4.181144987177259</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.992240232735398</v>
+        <v>1.996372352834069</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3810357268821603</v>
+        <v>0.3228680382175747</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.897808208148017</v>
+        <v>3.862907594949265</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.345461705200076</v>
+        <v>-4.335131404953399</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.999625934770582</v>
+        <v>2.003758054869253</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3810357268821603</v>
+        <v>0.3228680382175747</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.966788477293656</v>
+        <v>3.931887864094905</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.29493980137241</v>
+        <v>-4.284609501125733</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.005885898421769</v>
+        <v>2.01001801852044</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3810357268821603</v>
+        <v>0.3228680382175747</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.952839679413777</v>
+        <v>3.917939066215026</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.547414955380135</v>
+        <v>-4.537084655133458</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.916766325874093</v>
+        <v>1.920898445972764</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3810357268821603</v>
+        <v>0.3228680382175747</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.964710168469191</v>
+        <v>3.92980955527044</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.840310711859547</v>
+        <v>-4.82998041161287</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.800818557801272</v>
+        <v>1.804950677899943</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3810357268821603</v>
+        <v>0.3228680382175747</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.965920702988135</v>
+        <v>3.931020089789383</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.997854783588989</v>
+        <v>-4.987524483342312</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.741922671336817</v>
+        <v>1.746054791435488</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3141339217418858</v>
+        <v>0.2559662330773002</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.929901362131291</v>
+        <v>3.89500074893254</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.275819179172262</v>
+        <v>-5.265488878925585</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.625814765839697</v>
+        <v>1.629946885938368</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2245141874564015</v>
+        <v>0.166346498791816</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.87120737429619</v>
+        <v>3.836306761097439</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.392786871811153</v>
+        <v>-5.382456571564476</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.741231745483185</v>
+        <v>1.745363865581856</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2245141874564015</v>
+        <v>0.166346498791816</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.033411430995234</v>
+        <v>3.998510817796483</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.477504814032106</v>
+        <v>-5.467174513785429</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.702191206558618</v>
+        <v>1.706323326657289</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1393981585283551</v>
+        <v>0.08123046986376958</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.97718845160222</v>
+        <v>3.94228783840347</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.55943963230099</v>
+        <v>-5.549109332054313</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.679646696819555</v>
+        <v>1.683778816918226</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1294634129412749</v>
+        <v>0.0712957242766894</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.981457021818464</v>
+        <v>3.946556408619712</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.661415754549397</v>
+        <v>-5.65108545430272</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.647781886376095</v>
+        <v>1.651914006474766</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.02748729069286737</v>
+        <v>-0.03068039797171818</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.929196986925322</v>
+        <v>3.89429637372657</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.551409471072176</v>
+        <v>-5.541079170825499</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.683937287011159</v>
+        <v>1.68806940710983</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.05069186261014258</v>
+        <v>-0.007475826054442969</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.935272617319862</v>
+        <v>3.900372004121111</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.40834989533125</v>
+        <v>-5.398019595084573</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.745411128029503</v>
+        <v>1.749543248128174</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.05870528920012186</v>
+        <v>0.0005376005355363089</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.944330683995824</v>
+        <v>3.909430070797073</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.106903169859413</v>
+        <v>-5.096572869612736</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.873250701100774</v>
+        <v>1.877382821199445</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3601520146719591</v>
+        <v>0.3019843260073736</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.132459602161463</v>
+        <v>4.097558988962711</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.131493414094597</v>
+        <v>-5.12116311384792</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.864385781159411</v>
+        <v>1.868517901258082</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3601520146719591</v>
+        <v>0.3019843260073736</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.133430779914173</v>
+        <v>4.098530166715422</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.080455038088076</v>
+        <v>-5.070124737841399</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.885644035941775</v>
+        <v>1.889776156040445</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3601520146719591</v>
+        <v>0.3019843260073736</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.134273684293928</v>
+        <v>4.099373071095177</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.039315743221445</v>
+        <v>-5.028985442974768</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.921137852762572</v>
+        <v>1.925269972861243</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4012913095385899</v>
+        <v>0.3431236208740044</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.177995360088052</v>
+        <v>4.143094746889301</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.928709603141844</v>
+        <v>-4.918379302895167</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.781564304918348</v>
+        <v>1.785696425017018</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5118974496181919</v>
+        <v>0.4537297609536064</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.060543040259748</v>
+        <v>4.025642427060997</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.059290337672686</v>
+        <v>-5.048960037426009</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.732834055179974</v>
+        <v>1.736966175278645</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3813167150873494</v>
+        <v>0.3231490264227639</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.985696643615206</v>
+        <v>3.950796030416455</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.894794003481724</v>
+        <v>-4.884463703235047</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.783059407932442</v>
+        <v>1.787191528031112</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3813167150873494</v>
+        <v>0.3231490264227639</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.970123462691289</v>
+        <v>3.935222849492537</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.922163936166156</v>
+        <v>-4.911833635919479</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.771299145295099</v>
+        <v>1.775431265393769</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3813167150873494</v>
+        <v>0.3231490264227639</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.969311173127719</v>
+        <v>3.934410559928967</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.932549131056046</v>
+        <v>-4.922218830809369</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.777013846464215</v>
+        <v>1.781145966562886</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3709315201974601</v>
+        <v>0.3127638315328746</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.972948835318857</v>
+        <v>3.938048222120106</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.951137289778271</v>
+        <v>-4.940806989531594</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.84041558875175</v>
+        <v>1.844547708850421</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3523433614752348</v>
+        <v>0.2941756728106492</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.032632945861947</v>
+        <v>3.997732332663196</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.951435836474307</v>
+        <v>-4.94110553622763</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.837165180891634</v>
+        <v>1.841297300990305</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3523433614752348</v>
+        <v>0.2941756728106492</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.029501956680246</v>
+        <v>3.994601343481494</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.850612702783879</v>
+        <v>-4.840282402537202</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.882025329307197</v>
+        <v>1.886157449405868</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3648075769595886</v>
+        <v>0.306639888295003</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.041511380910249</v>
+        <v>4.006610767711498</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.659831342031472</v>
+        <v>-4.649501041784795</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.958467127086703</v>
+        <v>1.962599247185374</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.555588937711996</v>
+        <v>0.4974212490474104</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.156109450840237</v>
+        <v>4.121208837641485</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.641314487989652</v>
+        <v>-4.630984187742975</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.945710714441028</v>
+        <v>1.949842834539699</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5685190671372042</v>
+        <v>0.5103513784726186</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.143704374232959</v>
+        <v>4.108803761034207</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.616121303488334</v>
+        <v>-4.605791003241657</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.990754924853613</v>
+        <v>1.994887044952284</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.5937122516385226</v>
+        <v>0.5355445629739369</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.193787221545808</v>
+        <v>4.158886608347056</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.604067176575371</v>
+        <v>-4.593736876328694</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.989263143520236</v>
+        <v>1.993395263618907</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6057663785514854</v>
+        <v>0.5475986898868997</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.194706265595023</v>
+        <v>4.159805652396272</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.610690423265729</v>
+        <v>-4.600360123019052</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.988494475028229</v>
+        <v>1.992626595126899</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5991431318611271</v>
+        <v>0.5409754431965415</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.192612947764944</v>
+        <v>4.157712334566193</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.507809833737136</v>
+        <v>-4.497479533490459</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.042497736717548</v>
+        <v>2.046629856816219</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.70202372138972</v>
+        <v>0.6438560327251344</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.267192327359982</v>
+        <v>4.232291714161231</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.531251872917223</v>
+        <v>-4.520921572670546</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.053323591219108</v>
+        <v>2.057455711317779</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.70202372138972</v>
+        <v>0.6438560327251344</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.287394997533577</v>
+        <v>4.252494384334825</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.549324381208835</v>
+        <v>-4.538994080962158</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.046094587902463</v>
+        <v>2.050226708001134</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.70202372138972</v>
+        <v>0.6438560327251344</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.287394997533577</v>
+        <v>4.252494384334825</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.780498175085467</v>
+        <v>-4.77016787483879</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.913876983945277</v>
+        <v>1.918009104043948</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.70202372138972</v>
+        <v>0.6438560327251344</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.247646911127044</v>
+        <v>4.212746297928292</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.749212154545011</v>
+        <v>-4.738881854298334</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.933414011158399</v>
+        <v>1.93754613125707</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.7333097419301754</v>
+        <v>0.6751420532655897</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.273441142448257</v>
+        <v>4.238540529249505</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.596186762431727</v>
+        <v>-4.58585646218505</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.093795167576617</v>
+        <v>2.097927287675287</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.8863351340434595</v>
+        <v>0.8281674453788739</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.464427377289131</v>
+        <v>4.429526764090379</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.624494076304997</v>
+        <v>-4.61416377605832</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.269938466935601</v>
+        <v>2.274070587034272</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.8863351340434595</v>
+        <v>0.8281674453788739</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.651893602197424</v>
+        <v>4.616992988998672</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.785990500142422</v>
+        <v>-4.775660199895745</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.174742848754714</v>
+        <v>2.178874968853385</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7248387102060349</v>
+        <v>0.6666710215414492</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.524398699249051</v>
+        <v>4.4894980860503</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,13 +48793,13 @@
         <v>4.177154815453494</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.785990500142422</v>
+        <v>-4.775660199895745</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.174742848754714</v>
+        <v>2.178874968853385</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7248387102060349</v>
+        <v>0.6666710215414492</v>
       </c>
       <c r="G2054" t="n">
         <v>4.170218612439862</v>

--- a/tame_output/ON/bt/strategyON_20240812.xlsx
+++ b/tame_output/ON/bt/strategyON_20240812.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>50.9%</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94.5%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>80.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>106.1%</t>
+          <t>118.4%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.0%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-597.3%</t>
+          <t>-581.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.5%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-74.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.8%</t>
+          <t>430.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-639.1%</t>
+          <t>-645.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-239.3%</t>
+          <t>-233.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-158.3%</t>
+          <t>-164.6%</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-314.0%</t>
+          <t>-314.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>83.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-29.0%</t>
+          <t>-16.6%</t>
         </is>
       </c>
     </row>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382324</v>
+        <v>3.235981977382325</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.960208298997795</v>
+        <v>-2.803099376914839</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.953650793839381</v>
+        <v>2.016494362672563</v>
       </c>
       <c r="F1855" t="n">
         <v>0.2070821474982212</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.210078979012376</v>
+        <v>-3.052970056929421</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.855471645288164</v>
+        <v>1.918315214121346</v>
       </c>
       <c r="F1856" t="n">
         <v>0.2433448673286845</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130012</v>
+        <v>3.287377576130013</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.416590755899398</v>
+        <v>-3.259481833816443</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.768972993189614</v>
+        <v>1.831816562022796</v>
       </c>
       <c r="F1857" t="n">
         <v>0.036833090441663</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178238</v>
+        <v>3.315884374178239</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.735934830979899</v>
+        <v>-3.578825908896944</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.643008289857673</v>
+        <v>1.705851858690854</v>
       </c>
       <c r="F1858" t="n">
         <v>0.036833090441663</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.122144662255674</v>
+        <v>-3.965035740172719</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.474857244814767</v>
+        <v>1.537700813647949</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.05393984927578033</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.356838656388226</v>
+        <v>-4.199729734305272</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.369264422163837</v>
+        <v>1.432107990997018</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.04760358204652515</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.692501303618679</v>
+        <v>-4.535392381535725</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.233579954927621</v>
+        <v>1.296423523760803</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.11553456753543</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.76894563382155</v>
+        <v>-4.611836711738596</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.209489783080714</v>
+        <v>1.272333351913896</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.03508905844176807</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.134073016460297</v>
+        <v>-4.976964094377343</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.062693345031047</v>
+        <v>1.125536913864228</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.3313998427407806</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.542661793640976</v>
+        <v>-5.385552871558021</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8980193781735339</v>
+        <v>0.9608629470067158</v>
       </c>
       <c r="F1864" t="n">
         <v>-0.739988619921459</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.656422205663841</v>
+        <v>-5.499313283580886</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.8477006458358489</v>
+        <v>0.9105442146690308</v>
       </c>
       <c r="F1865" t="n">
         <v>-0.739988619921459</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.072814079950838</v>
+        <v>-5.915705157867883</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6791379467299272</v>
+        <v>0.7419815155631091</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.739988619921459</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.433987709767826</v>
+        <v>-6.276878787684871</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5449271854718107</v>
+        <v>0.6077707543049931</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.739988619921459</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.777246229410845</v>
+        <v>-6.62013730732789</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.4037233427602986</v>
+        <v>0.4665669115934805</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.739988619921459</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.825449046653189</v>
+        <v>-6.668340124570234</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3828471359183618</v>
+        <v>0.4456907047515437</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.739988619921459</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.122110388463386</v>
+        <v>-6.965001466380431</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2679615751234912</v>
+        <v>0.330805143956673</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.8087317556553376</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.308830096772689</v>
+        <v>-7.151721174689734</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1892473872653668</v>
+        <v>0.2520909560985487</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.8087317556553376</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.69183148551532</v>
+        <v>-7.534722563432365</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.03594473044673041</v>
+        <v>0.09878829927991228</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.8087317556553376</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.696317930716709</v>
+        <v>-7.539209008633754</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.03672166833760526</v>
+        <v>0.09956523717078714</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.8132182008567264</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.055848253220711</v>
+        <v>-7.898739331137755</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1017401573659455</v>
+        <v>-0.03889658853276323</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.8132182008567264</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.106197316674933</v>
+        <v>-7.949088394591977</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1139637627904571</v>
+        <v>-0.05112019395727474</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.8635672643109484</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.203816594096329</v>
+        <v>-8.046707672013374</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1499697231372465</v>
+        <v>-0.08712615430406467</v>
       </c>
       <c r="F1876" t="n">
         <v>-0.9611865417323451</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.257888093604688</v>
+        <v>-8.100779171521733</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.168704766619018</v>
+        <v>-0.1058611977858361</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.015258041240704</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.462146268934552</v>
+        <v>-8.305037346851597</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2448948396323209</v>
+        <v>-0.1820512707991391</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.142896985854693</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.495799107443025</v>
+        <v>-8.33869018536007</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2538734205512743</v>
+        <v>-0.1910298517180924</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.243310353771731</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.422329275775576</v>
+        <v>-8.265220353692621</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2091137863908736</v>
+        <v>-0.1462702175576918</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.169840522104282</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.597453693162119</v>
+        <v>-8.440344771079165</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.264608332597974</v>
+        <v>-0.2017647637647921</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.344964939490826</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.831905787176609</v>
+        <v>-8.674796865093654</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3656083351053661</v>
+        <v>-0.3027647662721842</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.344964939490826</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.936280518203056</v>
+        <v>-8.779171596120101</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4140304182899208</v>
+        <v>-0.3511868494567389</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.449339670517272</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.09879398390164</v>
+        <v>-8.941685061818685</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.477920014730798</v>
+        <v>-0.4150764458976162</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.546973100935959</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.224830777269929</v>
+        <v>-9.067721855186974</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5256410034489991</v>
+        <v>-0.4627974346158172</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.521721478126216</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.167759005373998</v>
+        <v>-9.010650083291043</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4988219590042262</v>
+        <v>-0.4359783901710443</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.521721478126216</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.309430847098119</v>
+        <v>-9.152321925015164</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.556965922592616</v>
+        <v>-0.4941223537594341</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.521721478126216</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.259840002673284</v>
+        <v>-9.102731080590329</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5220761746578098</v>
+        <v>-0.4592326058246279</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.472130633701382</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.110921668201428</v>
+        <v>-8.953812746118473</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4755599745157504</v>
+        <v>-0.4127164056825685</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.440881042966209</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615279</v>
+        <v>3.68516138161528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.885076515482016</v>
+        <v>-8.727967593399061</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3756428403917771</v>
+        <v>-0.3127992715585948</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.398954367379046</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.760497859144424</v>
+        <v>-8.603388937061469</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3246722333006811</v>
+        <v>-0.2618286644674992</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.398954367379046</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646213</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.813393147188711</v>
+        <v>-8.656284225105756</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3431965743562881</v>
+        <v>-0.2803530055231063</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.393999021290599</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611564</v>
+        <v>3.768951674611565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.741259971900829</v>
+        <v>-8.584151049817875</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3086096000024994</v>
+        <v>-0.2457660311693175</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.393999021290599</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.669893579291182</v>
+        <v>-8.512784657208227</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2898003053525056</v>
+        <v>-0.2269567365193237</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.322632628680952</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.576434545305958</v>
+        <v>-8.419325623223003</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2623001730713233</v>
+        <v>-0.1994566042381414</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.322632628680952</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.565781363752526</v>
+        <v>-8.408672441669571</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2598734609493243</v>
+        <v>-0.1970298921161424</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.322632628680952</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.467874325076036</v>
+        <v>-8.310765402993081</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.221010960452189</v>
+        <v>-0.1581673916190072</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.254646878820395</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.443920784100078</v>
+        <v>-8.286811862017123</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2107610379163121</v>
+        <v>-0.1479174690831302</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.230693337844438</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.179860845777281</v>
+        <v>-8.022751923694326</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1183973787489458</v>
+        <v>-0.05555380991576353</v>
       </c>
       <c r="F1899" t="n">
         <v>-0.9666333995216414</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.472781222272443</v>
+        <v>-7.315672300189488</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1616474369926886</v>
+        <v>0.2244910058258709</v>
       </c>
       <c r="F1900" t="n">
         <v>-0.9666333995216414</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.432596923906252</v>
+        <v>-7.275488001823297</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1780647802270061</v>
+        <v>0.2409083490601884</v>
       </c>
       <c r="F1901" t="n">
         <v>-0.9264491011554506</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.26919705296689</v>
+        <v>-7.112088130883935</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.242791549823508</v>
+        <v>0.3056351186566904</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.7630492302160882</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.035715830737291</v>
+        <v>-6.878606908654336</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3441084675532</v>
+        <v>0.4069520363863819</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.5295680079864896</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.886049439729776</v>
+        <v>-6.728940517646821</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4010828136432467</v>
+        <v>0.463926382476429</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.4366645167439537</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.75377396609889</v>
+        <v>-6.596665044015935</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4493604898426287</v>
+        <v>0.5122040586758105</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.304389043113067</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.598035633539148</v>
+        <v>-6.440926711456193</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.514470883554162</v>
+        <v>0.5773144523873439</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.1486507105533255</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.513070966809828</v>
+        <v>-6.355962044726873</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5613630914695489</v>
+        <v>0.6242066603027308</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.06368604382400589</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.618660956582932</v>
+        <v>-6.461552034499977</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3911511659610882</v>
+        <v>0.4539947347942701</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.1692760335971102</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987899</v>
+        <v>3.7704225839879</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.550426371957505</v>
+        <v>-6.39331744987455</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4669893416883455</v>
+        <v>0.5298329105215274</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.1508607107245742</v>
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>2.931454839754883</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.402486330549905</v>
+        <v>-6.24537740846695</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4062864355632176</v>
+        <v>0.4329474520543553</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.1305397948160167</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.889313515207317</v>
+        <v>2.853130962865273</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409203</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>2.922740853501405</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.349516808295917</v>
+        <v>-6.192407886212962</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4187602582113348</v>
+        <v>0.4454212747024728</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.07757027256202781</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.912381242306233</v>
+        <v>2.876198689964188</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>2.915780241406312</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.183728612335626</v>
+        <v>-6.026619690252671</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4781149245003582</v>
+        <v>0.5047759409914958</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.07757027256202781</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.90542063021114</v>
+        <v>2.869238077869095</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>2.930242595787455</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.150365405856857</v>
+        <v>-5.993256483773902</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5059225614730085</v>
+        <v>0.5325835779641466</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.07757027256202781</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.919882984592283</v>
+        <v>2.883700432250238</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>2.92477471624665</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.042106268734336</v>
+        <v>-5.884997346651381</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5437583367812122</v>
+        <v>0.5704193532723503</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.07757027256202781</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.914415105051478</v>
+        <v>2.878232552709433</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>2.922272810257227</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.918815133917205</v>
+        <v>-5.76170621183425</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5905728847186418</v>
+        <v>0.6172339012097794</v>
       </c>
       <c r="F1915" t="n">
         <v>0.04572086225510269</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.985887879952333</v>
+        <v>2.949705327610288</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>2.929973788494552</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.866118266785914</v>
+        <v>-5.709009344702959</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6193526098084834</v>
+        <v>0.646013626299621</v>
       </c>
       <c r="F1916" t="n">
         <v>0.09841772938639387</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.025206978468433</v>
+        <v>2.989024426126389</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>2.925754496841602</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.622352824802469</v>
+        <v>-5.465243902719514</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7126394949489119</v>
+        <v>0.7393005114400495</v>
       </c>
       <c r="F1917" t="n">
         <v>0.09841772938639387</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.020987686815483</v>
+        <v>2.984805134473439</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>2.927878810761618</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.532577152425997</v>
+        <v>-5.375468230343042</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7506740778195167</v>
+        <v>0.7773350943106543</v>
       </c>
       <c r="F1918" t="n">
         <v>0.1600171743007039</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.060071667684086</v>
+        <v>3.023889115342041</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>2.920620885745321</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.282726758476922</v>
+        <v>-5.125617836393968</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8433563103828488</v>
+        <v>0.8700173268739864</v>
       </c>
       <c r="F1919" t="n">
         <v>0.1600171743007039</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.052813742667788</v>
+        <v>3.016631190325743</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011494</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>2.924220009265969</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.10683466600949</v>
+        <v>-4.949725743926535</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9173122708904704</v>
+        <v>0.943973287381608</v>
       </c>
       <c r="F1920" t="n">
         <v>0.1600171743007039</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.056412866188436</v>
+        <v>3.020230313846392</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>2.937547515320523</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.935388202987027</v>
+        <v>-4.778279280904072</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9992183621540094</v>
+        <v>1.025879378645147</v>
       </c>
       <c r="F1921" t="n">
         <v>0.331463637323167</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.172608250056468</v>
+        <v>3.136425697714424</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632777</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>2.93656799293682</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.861098637248688</v>
+        <v>-4.703989715165733</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.027954666065642</v>
+        <v>1.05461568255678</v>
       </c>
       <c r="F1922" t="n">
         <v>0.4057532030615063</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.216202467115768</v>
+        <v>3.180019914773724</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>2.941262793991137</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.797462895014753</v>
+        <v>-4.640353972931798</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.058103764013533</v>
+        <v>1.084764780504671</v>
       </c>
       <c r="F1923" t="n">
         <v>0.4693889452954408</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.259078713510446</v>
+        <v>3.222896161168402</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>2.922457052774933</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.686036135688833</v>
+        <v>-4.528927213605878</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.083868726527697</v>
+        <v>1.110529743018834</v>
       </c>
       <c r="F1924" t="n">
         <v>0.4693889452954408</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.240272972294242</v>
+        <v>3.204090419952198</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>2.92420012939981</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.696538758754122</v>
+        <v>-4.539429836671167</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.081410753926459</v>
+        <v>1.108071770417596</v>
       </c>
       <c r="F1925" t="n">
         <v>0.458886322230152</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.235714475079946</v>
+        <v>3.199531922737902</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>2.928129443234631</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.624296190582927</v>
+        <v>-4.467187268499972</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.114237095029757</v>
+        <v>1.140898111520894</v>
       </c>
       <c r="F1926" t="n">
         <v>0.458886322230152</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.239643788914766</v>
+        <v>3.203461236572722</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>2.928808027151971</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.606582503705062</v>
+        <v>-4.449473581622107</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.122001153698243</v>
+        <v>1.14866217018938</v>
       </c>
       <c r="F1927" t="n">
         <v>0.4620676511270688</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.242231170170256</v>
+        <v>3.206048617828212</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>2.925806098371964</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.497777618225335</v>
+        <v>-4.34066869614238</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.162521179110127</v>
+        <v>1.189182195601265</v>
       </c>
       <c r="F1928" t="n">
         <v>0.4620676511270688</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.23922924139025</v>
+        <v>3.203046689048206</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>2.927385135382578</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.277756820188324</v>
+        <v>-4.12064789810537</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.252108535335545</v>
+        <v>1.278769551826683</v>
       </c>
       <c r="F1929" t="n">
         <v>0.603287496195049</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.325540185441652</v>
+        <v>3.289357633099608</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>2.943279318184401</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.144889131125047</v>
+        <v>-3.987780209042092</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.32114979376268</v>
+        <v>1.347810810253818</v>
       </c>
       <c r="F1930" t="n">
         <v>0.603287496195049</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.341434368243475</v>
+        <v>3.305251815901431</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>2.944425162624703</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.024716047760548</v>
+        <v>-3.867607125677592</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.370364871548781</v>
+        <v>1.397025888039919</v>
       </c>
       <c r="F1931" t="n">
         <v>0.7234605795595479</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.414684062702476</v>
+        <v>3.378501510360432</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>2.954513265186143</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.889462686430571</v>
+        <v>-3.732353764347615</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.434554318642212</v>
+        <v>1.46121533513335</v>
       </c>
       <c r="F1932" t="n">
         <v>0.858713940889525</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.505924182061903</v>
+        <v>3.469741629719858</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>2.940550756587569</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.949337513788263</v>
+        <v>-3.792228591705308</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.396641879100561</v>
+        <v>1.423302895591699</v>
       </c>
       <c r="F1933" t="n">
         <v>0.7988391135318329</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.456036777048713</v>
+        <v>3.419854224706669</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.992022478163822</v>
+        <v>2.955839925821778</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.829517282877426</v>
+        <v>-3.67240836079447</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.459859140699104</v>
+        <v>1.486520157190242</v>
       </c>
       <c r="F1934" t="n">
         <v>0.7988391135318329</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.471325946282922</v>
+        <v>3.435143393940877</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.899666677486263</v>
+        <v>2.863484125144219</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.831986989339232</v>
+        <v>-3.674878067256276</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.366515457436823</v>
+        <v>1.393176473927961</v>
       </c>
       <c r="F1935" t="n">
         <v>0.7963694070700267</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.37748832172828</v>
+        <v>3.341305769386235</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.818928538971565</v>
+        <v>2.782745986629521</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.900357175663242</v>
+        <v>-3.743248253580286</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.258429244392521</v>
+        <v>1.285090260883659</v>
       </c>
       <c r="F1936" t="n">
         <v>0.8056451061062416</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.30231560263531</v>
+        <v>3.266133050293266</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.809365247603456</v>
+        <v>2.773182695261412</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.914145228510288</v>
+        <v>-3.757036306427333</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.243350731885593</v>
+        <v>1.270011748376731</v>
       </c>
       <c r="F1937" t="n">
         <v>0.8056451061062416</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.292752311267201</v>
+        <v>3.256569758925157</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.946396084295658</v>
+        <v>2.910213531953614</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.969665304402878</v>
+        <v>-3.812556382319922</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.35817353822076</v>
+        <v>1.384834554711898</v>
       </c>
       <c r="F1938" t="n">
         <v>0.8056451061062416</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.429783147959404</v>
+        <v>3.39360059561736</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.950963316287446</v>
+        <v>2.914780763945402</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.794191044610409</v>
+        <v>-3.637082122527453</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.432930474129535</v>
+        <v>1.459591490620674</v>
       </c>
       <c r="F1939" t="n">
         <v>0.8056451061062416</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.434350379951192</v>
+        <v>3.398167827609147</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.926705345048653</v>
+        <v>2.890522792706609</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.905127297251657</v>
+        <v>-3.748018375168702</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.364298001834243</v>
+        <v>1.390959018325381</v>
       </c>
       <c r="F1940" t="n">
         <v>0.8056451061062416</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.410092408712399</v>
+        <v>3.373909856370354</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.855243658450103</v>
+        <v>2.819061106108059</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.871463751779376</v>
+        <v>-3.71435482969642</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.306301733424606</v>
+        <v>1.332962749915744</v>
       </c>
       <c r="F1941" t="n">
         <v>0.8393086515785235</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.358828849397217</v>
+        <v>3.322646297055173</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.865416044882235</v>
+        <v>2.829233492540191</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.811611132575652</v>
+        <v>-3.654502210492697</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.340415167538227</v>
+        <v>1.367076184029365</v>
       </c>
       <c r="F1942" t="n">
         <v>0.8393086515785235</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.36900123582935</v>
+        <v>3.332818683487305</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.860362315456096</v>
+        <v>2.824179763114052</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.725367669549275</v>
+        <v>-3.568258747466319</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.369858823322639</v>
+        <v>1.396519839813777</v>
       </c>
       <c r="F1943" t="n">
         <v>0.8393086515785235</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.36394750640321</v>
+        <v>3.327764954061166</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.852138090900621</v>
+        <v>2.815955538558577</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.770674488948255</v>
+        <v>-3.613565566865299</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.343511871007572</v>
+        <v>1.37017288749871</v>
       </c>
       <c r="F1944" t="n">
         <v>0.7984984885692927</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.331237184042197</v>
+        <v>3.295054631700153</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.852689963933723</v>
+        <v>2.816507411591679</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.799707593650556</v>
+        <v>-3.642598671567601</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.332450502159753</v>
+        <v>1.359111518650891</v>
       </c>
       <c r="F1945" t="n">
         <v>0.7984984885692927</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.331789057075299</v>
+        <v>3.295606504733255</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.781962655825089</v>
+        <v>2.745780103483044</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.706897112199697</v>
+        <v>-3.549788190116741</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.298847386631462</v>
+        <v>1.3255084031226</v>
       </c>
       <c r="F1946" t="n">
         <v>0.8913089700201521</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.31674803783718</v>
+        <v>3.280565485495136</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.783836131749689</v>
+        <v>2.747653579407645</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.751286581529125</v>
+        <v>-3.594177659446169</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.282965074824292</v>
+        <v>1.30962609131543</v>
       </c>
       <c r="F1947" t="n">
         <v>0.8469195006907244</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.291987832164124</v>
+        <v>3.25580527982208</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.778911840261412</v>
+        <v>2.742729287919368</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.867828186634468</v>
+        <v>-3.710719264551512</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.231424141293878</v>
+        <v>1.258085157785016</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7303778955853817</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.217138577612642</v>
+        <v>3.180956025270597</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.78440313609208</v>
+        <v>2.748220583750035</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.907752281217039</v>
+        <v>-3.750643359134084</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.220945799291516</v>
+        <v>1.247606815782655</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7303778955853817</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.222629873443309</v>
+        <v>3.186447321101264</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.795900337860619</v>
+        <v>2.759717785518574</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.935532679118392</v>
+        <v>-3.778423757035437</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.221330841899514</v>
+        <v>1.247991858390652</v>
       </c>
       <c r="F1950" t="n">
         <v>0.7025974976840286</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.217458836471036</v>
+        <v>3.181276284128992</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.634256057861272</v>
+        <v>2.598073505519228</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.05391335184853</v>
+        <v>-3.896804429765575</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.012334292808112</v>
+        <v>1.03899530929925</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6353796455330524</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.015483845181103</v>
+        <v>2.979301292839059</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.754405718580478</v>
+        <v>2.718223166238433</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.162527430291862</v>
+        <v>-4.005418508208907</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.089038322149986</v>
+        <v>1.115699338641124</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6353796455330524</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.135633505900309</v>
+        <v>3.099450953558265</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.768918744682801</v>
+        <v>2.732736192340756</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.127118392043719</v>
+        <v>-3.970009469960764</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.117714963551566</v>
+        <v>1.144375980042704</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6353796455330524</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.150146532002632</v>
+        <v>3.113963979660588</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.766338186025169</v>
+        <v>2.730155633683125</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.088734729485568</v>
+        <v>-3.931625807402613</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.130487869917195</v>
+        <v>1.157148886408333</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6737633080912035</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.170596170879892</v>
+        <v>3.134413618537848</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.763067214870471</v>
+        <v>2.726884662528427</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.911618399450401</v>
+        <v>-3.754509477367447</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.198063430776563</v>
+        <v>1.224724447267701</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6737633080912035</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.167325199725194</v>
+        <v>3.131142647383149</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.763750606632384</v>
+        <v>2.72756805429034</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.956710644283947</v>
+        <v>-3.799601722200992</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.180709924605058</v>
+        <v>1.207370941096196</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6118672649218138</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.130870965585473</v>
+        <v>3.094688413243428</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.757537581938799</v>
+        <v>2.721355029596754</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.77733522304518</v>
+        <v>-3.620226300962224</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.24624706840698</v>
+        <v>1.272908084898118</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7686440230925324</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.218723995794318</v>
+        <v>3.182541443452274</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.738345037270388</v>
+        <v>2.702162484928344</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.822349436565786</v>
+        <v>-3.66524051448283</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.209048838330327</v>
+        <v>1.235709854821465</v>
       </c>
       <c r="F1958" t="n">
         <v>0.7382951277779278</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.181322113937145</v>
+        <v>3.145139561595101</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.744036599609334</v>
+        <v>2.70785404726729</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.089353946838221</v>
+        <v>-3.932245024755266</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.107938596560298</v>
+        <v>1.134599613051436</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5439320897349793</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.070395853450322</v>
+        <v>3.034213301108278</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.743240521505836</v>
+        <v>2.707057969163791</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.190551728275394</v>
+        <v>-4.033442806192438</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.066663405881931</v>
+        <v>1.093324422373069</v>
       </c>
       <c r="F1960" t="n">
         <v>0.4755232761896601</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.028554487219632</v>
+        <v>2.992371934877588</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.740840483060152</v>
+        <v>2.704657930718108</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.184040761661081</v>
+        <v>-4.026931839578126</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.066867754081972</v>
+        <v>1.09352877057311</v>
       </c>
       <c r="F1961" t="n">
         <v>0.4755232761896601</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.026154448773949</v>
+        <v>2.989971896431904</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.737365202268397</v>
+        <v>2.701182649926353</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.165002633953784</v>
+        <v>-4.007893711870828</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.071007724373136</v>
+        <v>1.097668740864274</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4173396648584656</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.987769001183477</v>
+        <v>2.951586448841432</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.856659603902588</v>
+        <v>2.820477051560543</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.217518436228604</v>
+        <v>-4.060409514145649</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.169295805097398</v>
+        <v>1.195956821588537</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4173396648584656</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.107063402817667</v>
+        <v>3.070880850475623</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.857492932888721</v>
+        <v>2.821310380546677</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.231385197562522</v>
+        <v>-4.074276275479567</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.164582429549965</v>
+        <v>1.191243446041103</v>
       </c>
       <c r="F1964" t="n">
         <v>0.3794817481246426</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.085181981763507</v>
+        <v>3.048999429421463</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.863501463285647</v>
+        <v>2.827318910943603</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.207060613035992</v>
+        <v>-4.049951690953036</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.180320793757503</v>
+        <v>1.206981810248641</v>
       </c>
       <c r="F1965" t="n">
         <v>0.3794817481246426</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.091190512160433</v>
+        <v>3.055007959818389</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.761451684562847</v>
+        <v>2.725269132220802</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.059317642800989</v>
+        <v>-3.902208720718034</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.137368203128704</v>
+        <v>1.164029219619841</v>
       </c>
       <c r="F1966" t="n">
         <v>0.5472891053595258</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.089825147778562</v>
+        <v>3.053642595436518</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.764245306094328</v>
+        <v>2.728062753752283</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.143138864075688</v>
+        <v>-3.986029941992732</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.106633336150305</v>
+        <v>1.133294352641443</v>
       </c>
       <c r="F1967" t="n">
         <v>0.5472891053595258</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.092618769310043</v>
+        <v>3.056436216967999</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.764907654485986</v>
+        <v>2.728725102143942</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.136986158022903</v>
+        <v>-3.979877235939948</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.109756766963077</v>
+        <v>1.136417783454215</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5534418114123101</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.096972741333372</v>
+        <v>3.060790188991328</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.763988131226096</v>
+        <v>2.727805578884052</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.153795456173405</v>
+        <v>-3.996686534090449</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.102113524442987</v>
+        <v>1.128774540934125</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5366325132618084</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.085967639183181</v>
+        <v>3.049785086841137</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.830323685022917</v>
+        <v>2.794141132680873</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.091497457397283</v>
+        <v>-3.934388535314327</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.193368277750257</v>
+        <v>1.220029294241395</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5819267775362504</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.179479751544668</v>
+        <v>3.143297199202623</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.632615686737044</v>
+        <v>2.596433134395</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.889707259732125</v>
+        <v>-3.732598337649169</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.076376358530447</v>
+        <v>1.103037375021585</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7799449697054048</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.100582668560287</v>
+        <v>3.064400116218243</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.702905919059219</v>
+        <v>2.666723366717175</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.94059397241832</v>
+        <v>-3.783485050335364</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.126311905778144</v>
+        <v>1.152972922269282</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7290582570192103</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.140340873270746</v>
+        <v>3.104158320928701</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.717533655175263</v>
+        <v>2.681351102833219</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.853983229768513</v>
+        <v>-3.696874307685557</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.175583938954111</v>
+        <v>1.202244955445249</v>
       </c>
       <c r="F1973" t="n">
         <v>0.8076839882243686</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.202144048109884</v>
+        <v>3.16596149576784</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.716069635999935</v>
+        <v>2.67988708365789</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.914192527773797</v>
+        <v>-3.757083605690841</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.150036200576668</v>
+        <v>1.176697217067807</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7474746902190841</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.164554450131385</v>
+        <v>3.128371897789341</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.714561254039863</v>
+        <v>2.678378701697819</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.83777048134187</v>
+        <v>-3.680661559258914</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.179096637189368</v>
+        <v>1.205757653680506</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7474746902190841</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.163046068171314</v>
+        <v>3.12686351582927</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.714424121475299</v>
+        <v>2.678241569133255</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.793397349703302</v>
+        <v>-3.636288427620346</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.196708757280232</v>
+        <v>1.22336977377137</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7918478218576527</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.189532814589891</v>
+        <v>3.153350262247847</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.70881791561389</v>
+        <v>2.672635363271846</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.815877700562186</v>
+        <v>-3.658768778479231</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.182110411075268</v>
+        <v>1.208771427566406</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7918478218576527</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.183926608728482</v>
+        <v>3.147744056386438</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.715199672641694</v>
+        <v>2.67901712029965</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.768221970001131</v>
+        <v>-3.611113047918175</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.207554460327495</v>
+        <v>1.234215476818633</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8395035524187083</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.21890180409292</v>
+        <v>3.182719251750875</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.720092046016419</v>
+        <v>2.683909493674375</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.667703811502376</v>
+        <v>-3.51059488941942</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.252654097101722</v>
+        <v>1.27931511359286</v>
       </c>
       <c r="F1979" t="n">
         <v>0.9400217109174629</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.284105072566897</v>
+        <v>3.247922520224853</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.706846718492292</v>
+        <v>2.670664166150247</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.651798482070023</v>
+        <v>-3.494689559987068</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.245770901350535</v>
+        <v>1.272431917841673</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8609090502082239</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.223392148617226</v>
+        <v>3.187209596275182</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.71094442110292</v>
+        <v>2.674761868760876</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.606960080461625</v>
+        <v>-3.44985115837867</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.267803964604523</v>
+        <v>1.294464981095661</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8654524831530934</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.230215910994776</v>
+        <v>3.194033358652732</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.715105360733998</v>
+        <v>2.678922808391954</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.626458536703633</v>
+        <v>-3.469349614620678</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.264165521738797</v>
+        <v>1.290826538229936</v>
       </c>
       <c r="F1982" t="n">
         <v>0.8173678418731891</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.205526065857912</v>
+        <v>3.169343513515868</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.720984963261835</v>
+        <v>2.684802410919791</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.582255699617733</v>
+        <v>-3.425146777534777</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.287726259100995</v>
+        <v>1.314387275592133</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8615706789590896</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.237927370637289</v>
+        <v>3.201744818295245</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.719394963731083</v>
+        <v>2.683212411389039</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.58981536545478</v>
+        <v>-3.432706443371824</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.283112393235424</v>
+        <v>1.309773409726562</v>
       </c>
       <c r="F1984" t="n">
         <v>0.9163740829689089</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.269219413512428</v>
+        <v>3.233036861170384</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.770642728914122</v>
+        <v>2.734460176572078</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.431523947915508</v>
+        <v>-3.274415025832552</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.397676725434172</v>
+        <v>1.42433774192531</v>
       </c>
       <c r="F1985" t="n">
         <v>0.9163740829689089</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.320467178695468</v>
+        <v>3.284284626353424</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.769083433508376</v>
+        <v>2.732900881166331</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.223881944281032</v>
+        <v>-3.066773022198076</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.479174231482216</v>
+        <v>1.505835247973354</v>
       </c>
       <c r="F1986" t="n">
         <v>1.124016086603385</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.443493085470407</v>
+        <v>3.407310533128363</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.764031661746646</v>
+        <v>2.727849109404601</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.172849851558504</v>
+        <v>-3.015740929475548</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.494535296809497</v>
+        <v>1.521196313300635</v>
       </c>
       <c r="F1987" t="n">
         <v>1.175048179325913</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.469060569342194</v>
+        <v>3.432878017000149</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404853</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.781219065839351</v>
+        <v>2.745036513497306</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.107625670431298</v>
+        <v>-2.950516748348342</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.537812373353084</v>
+        <v>1.564473389844222</v>
       </c>
       <c r="F1988" t="n">
         <v>1.240272360453119</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.525382482111222</v>
+        <v>3.489199929769178</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.777180038138631</v>
+        <v>2.740997485796587</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.070198650360164</v>
+        <v>-2.913089728277208</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.548744153680818</v>
+        <v>1.575405170171956</v>
       </c>
       <c r="F1989" t="n">
         <v>1.2455238984823</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.524494377228011</v>
+        <v>3.488311824885967</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.778436830469871</v>
+        <v>2.742254278127827</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.090310306394872</v>
+        <v>-2.933201384311916</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.541956283598175</v>
+        <v>1.568617300089313</v>
       </c>
       <c r="F1990" t="n">
         <v>1.25655124347972</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.532367576557703</v>
+        <v>3.496185024215659</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.938994601491082</v>
+        <v>2.902812049149038</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.036565491967667</v>
+        <v>-2.879456569884712</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.724011980390268</v>
+        <v>1.750672996881406</v>
       </c>
       <c r="F1991" t="n">
         <v>1.266614552920182</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.698963333243191</v>
+        <v>3.662780780901147</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.059107510708899</v>
+        <v>3.022924958366855</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.961783230942655</v>
+        <v>-2.804674308859699</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.87403779401809</v>
+        <v>1.900698810509228</v>
       </c>
       <c r="F1992" t="n">
         <v>1.341396813945194</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.863945599076016</v>
+        <v>3.827763046733972</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.050815486722758</v>
+        <v>3.014632934380714</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.935699146678847</v>
+        <v>-2.778590224595891</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.876179403737472</v>
+        <v>1.90284042022861</v>
       </c>
       <c r="F1993" t="n">
         <v>1.341396813945194</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.855653575089875</v>
+        <v>3.819471022747831</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.049008682306538</v>
+        <v>3.012826129964493</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.847821233569726</v>
+        <v>-2.690712311486771</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.9095237645649</v>
+        <v>1.936184781056038</v>
       </c>
       <c r="F1994" t="n">
         <v>1.457322456368546</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.923402156127665</v>
+        <v>3.887219603785621</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.066563088033329</v>
+        <v>3.030380535691285</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.838928772176443</v>
+        <v>-2.681819850093487</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.930635154849004</v>
+        <v>1.957296171340142</v>
       </c>
       <c r="F1995" t="n">
         <v>1.457322456368546</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.940956561854456</v>
+        <v>3.904774009512412</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.058418135437913</v>
+        <v>3.022235583095869</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.007404889146321</v>
+        <v>-2.850295967063365</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.855099755465637</v>
+        <v>1.881760771956775</v>
       </c>
       <c r="F1996" t="n">
         <v>1.429374620651965</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.916042907829092</v>
+        <v>3.879860355487048</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.039687832625775</v>
+        <v>3.003505280283731</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.309605360284738</v>
+        <v>-2.152496438201782</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.115489264198132</v>
+        <v>2.14215028068927</v>
       </c>
       <c r="F1997" t="n">
         <v>1.359026561281554</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.855103769394708</v>
+        <v>3.818921217052663</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.030351855122679</v>
+        <v>2.994169302780635</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.286884256601585</v>
+        <v>-2.129775334518629</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.115241728168298</v>
+        <v>2.141902744659436</v>
       </c>
       <c r="F1998" t="n">
         <v>1.359026561281554</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.845767791891612</v>
+        <v>3.809585239549568</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.189257980973848</v>
+        <v>3.153075428631804</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.416086069895627</v>
+        <v>-2.258977147812672</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.22246712870185</v>
+        <v>2.249128145192988</v>
       </c>
       <c r="F1999" t="n">
         <v>1.229824747987512</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.927152829766356</v>
+        <v>3.890970277424311</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.226335803467495</v>
+        <v>3.190153251125451</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.570867076673883</v>
+        <v>-2.413758154590927</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.197632548484195</v>
+        <v>2.224293564975333</v>
       </c>
       <c r="F2000" t="n">
         <v>1.196457073933036</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.944210047827316</v>
+        <v>3.908027495485273</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.22301115945704</v>
+        <v>3.186828607114996</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.563812386458709</v>
+        <v>-2.406703464375754</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.197129780559809</v>
+        <v>2.223790797050947</v>
       </c>
       <c r="F2001" t="n">
         <v>1.20351176414821</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.945118217945966</v>
+        <v>3.908935665603922</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.233017313101782</v>
+        <v>3.196834760759737</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.536861162132221</v>
+        <v>-2.379752240049266</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.217916423935146</v>
+        <v>2.244577440426284</v>
       </c>
       <c r="F2002" t="n">
         <v>1.218392110175929</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.964052579207339</v>
+        <v>3.927870026865294</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784109</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.417120445246741</v>
+        <v>3.380937892904697</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.672814170188538</v>
+        <v>-2.515705248105582</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.347638352857579</v>
+        <v>2.374299369348717</v>
       </c>
       <c r="F2003" t="n">
         <v>1.218392110175929</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.148155711352299</v>
+        <v>4.111973159010255</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.409237140149735</v>
+        <v>3.37305458780769</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.69522228799341</v>
+        <v>-2.538113365910454</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.330791800638623</v>
+        <v>2.357452817129762</v>
       </c>
       <c r="F2004" t="n">
         <v>1.218392110175929</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.140272406255292</v>
+        <v>4.104089853913248</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.411291139699372</v>
+        <v>3.375108587357328</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.72344652357101</v>
+        <v>-2.566337601488054</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.321556105957221</v>
+        <v>2.348217122448359</v>
       </c>
       <c r="F2005" t="n">
         <v>1.236368862627237</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.153112457275714</v>
+        <v>4.11692990493367</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161979</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.467544857421219</v>
+        <v>3.431362305079175</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.73288744945954</v>
+        <v>-2.575778527376584</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.374033453323656</v>
+        <v>2.400694469814794</v>
       </c>
       <c r="F2006" t="n">
         <v>1.358795980170629</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.282822445523597</v>
+        <v>4.246639893181553</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321636</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.47043595196652</v>
+        <v>3.434253399624476</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.785161056795181</v>
+        <v>-2.628052134712226</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.3560151049347</v>
+        <v>2.382676121425838</v>
       </c>
       <c r="F2007" t="n">
         <v>1.306522372834988</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.254349375667513</v>
+        <v>4.218166823325468</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347705</v>
+        <v>3.727898186347704</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.468547764860295</v>
+        <v>3.432365212518251</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.861491034396087</v>
+        <v>-2.704382112313132</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.323594926788113</v>
+        <v>2.350255943279251</v>
       </c>
       <c r="F2008" t="n">
         <v>1.306522372834988</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.252461188561288</v>
+        <v>4.216278636219243</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887749</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.463367994463157</v>
+        <v>3.427185442121113</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.063744754720441</v>
+        <v>-2.906635832637485</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.237513668261234</v>
+        <v>2.264174684752372</v>
       </c>
       <c r="F2009" t="n">
         <v>1.104268652510634</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.125929185969538</v>
+        <v>4.089746633627493</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.46180200467331</v>
+        <v>3.425619452331266</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.225313180247696</v>
+        <v>-3.06820425816474</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.171320308260484</v>
+        <v>2.197981324751622</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9774857287127546</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.048293441900963</v>
+        <v>4.012110889558919</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.75459613538935</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.474875411539228</v>
+        <v>3.438692859197184</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.357614472345249</v>
+        <v>-3.200505550262293</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.131473198287382</v>
+        <v>2.15813421477852</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9774857287127546</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.061366848766881</v>
+        <v>4.025184296424837</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749882691378392</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.466880608322168</v>
+        <v>3.430698055980124</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.543482783184479</v>
+        <v>-3.386373861101523</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.04913107073463</v>
+        <v>2.075792087225768</v>
       </c>
       <c r="F2012" t="n">
         <v>0.8189201353928069</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.958232689557853</v>
+        <v>3.922050137215809</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.46540464944917</v>
+        <v>3.429222097107126</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.571383570293952</v>
+        <v>-3.414274648210996</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.036494797017842</v>
+        <v>2.06315581350898</v>
       </c>
       <c r="F2013" t="n">
         <v>0.7843232112498721</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.935998576199093</v>
+        <v>3.89981602385705</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.462169093426369</v>
+        <v>3.425986541084325</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.693909672996846</v>
+        <v>-3.53680075091389</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.984248799913884</v>
+        <v>2.010909816405022</v>
       </c>
       <c r="F2014" t="n">
         <v>0.6617971085469783</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.859247358554557</v>
+        <v>3.823064806212512</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.528875053016873</v>
+        <v>3.492692500674829</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.924424169182434</v>
+        <v>-3.767315247099479</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.958748961030152</v>
+        <v>1.98540997752129</v>
       </c>
       <c r="F2015" t="n">
         <v>0.4312826123613895</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.787644620433707</v>
+        <v>3.751462068091663</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.66918677201872</v>
+        <v>3.633004219676676</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.181144987177259</v>
+        <v>-4.024036065094302</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.996372352834069</v>
+        <v>2.023033369325208</v>
       </c>
       <c r="F2016" t="n">
         <v>0.3228680382175747</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.862907594949265</v>
+        <v>3.826725042607221</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.73816704116436</v>
+        <v>3.701984488822315</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.335131404953399</v>
+        <v>-4.178022482870443</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.003758054869253</v>
+        <v>2.030419071360391</v>
       </c>
       <c r="F2017" t="n">
         <v>0.3228680382175747</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.931887864094905</v>
+        <v>3.89570531175286</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.724218243284481</v>
+        <v>3.688035690942436</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.284609501125733</v>
+        <v>-4.350889399065061</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.01001801852044</v>
+        <v>1.947323507002665</v>
       </c>
       <c r="F2018" t="n">
         <v>0.3228680382175747</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.917939066215026</v>
+        <v>3.881756513872981</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.736088732339895</v>
+        <v>3.69990617999785</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.537084655133458</v>
+        <v>-4.603364553072786</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.920898445972764</v>
+        <v>1.858203934454989</v>
       </c>
       <c r="F2019" t="n">
         <v>0.3228680382175747</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.92980955527044</v>
+        <v>3.893627002928395</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.737299266858838</v>
+        <v>3.701116714516794</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.82998041161287</v>
+        <v>-4.896260309552198</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.804950677899943</v>
+        <v>1.742256166382168</v>
       </c>
       <c r="F2020" t="n">
         <v>0.3228680382175747</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.931020089789383</v>
+        <v>3.894837537447339</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.74142100908616</v>
+        <v>3.705238456744115</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.987524483342312</v>
+        <v>-5.05380438128164</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.746054791435488</v>
+        <v>1.683360279917713</v>
       </c>
       <c r="F2021" t="n">
         <v>0.2559662330773002</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.89500074893254</v>
+        <v>3.858818196590496</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.736498861822349</v>
+        <v>3.700316309480305</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.265488878925585</v>
+        <v>-5.331768776864913</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.629946885938368</v>
+        <v>1.567252374420592</v>
       </c>
       <c r="F2022" t="n">
         <v>0.166346498791816</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.836306761097439</v>
+        <v>3.800124208755395</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.898702918521393</v>
+        <v>3.862520366179349</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.382456571564476</v>
+        <v>-5.448736469503804</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.745363865581856</v>
+        <v>1.68266935406408</v>
       </c>
       <c r="F2023" t="n">
         <v>0.166346498791816</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.998510817796483</v>
+        <v>3.962328265454439</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.893549556485207</v>
+        <v>3.857367004143163</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.467174513785429</v>
+        <v>-5.533454411724757</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.706323326657289</v>
+        <v>1.643628815139513</v>
       </c>
       <c r="F2024" t="n">
         <v>0.08123046986376958</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.94228783840347</v>
+        <v>3.906105286061425</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.903778974053699</v>
+        <v>3.867596421711654</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.549109332054313</v>
+        <v>-5.615389229993641</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.683778816918226</v>
+        <v>1.621084305400451</v>
       </c>
       <c r="F2025" t="n">
         <v>0.0712957242766894</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.946556408619712</v>
+        <v>3.910373856277668</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.912704612509601</v>
+        <v>3.876522060167557</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.65108545430272</v>
+        <v>-5.717365352242048</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.651914006474766</v>
+        <v>1.58921949495699</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.03068039797171818</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.89429637372657</v>
+        <v>3.858113821384526</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.904857499753776</v>
+        <v>3.868674947411732</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.541079170825499</v>
+        <v>-5.607359068764826</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.68806940710983</v>
+        <v>1.625374895592054</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.007475826054442969</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.900372004121111</v>
+        <v>3.864189451779067</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.909107510475751</v>
+        <v>3.872924958133706</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.398019595084573</v>
+        <v>-5.464299493023901</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.749543248128174</v>
+        <v>1.686848736610399</v>
       </c>
       <c r="F2028" t="n">
         <v>0.0005376005355363089</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.909430070797073</v>
+        <v>3.873247518455028</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.916368393358287</v>
+        <v>3.880185841016242</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.096572869612736</v>
+        <v>-5.162852767552064</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.877382821199445</v>
+        <v>1.814688309681669</v>
       </c>
       <c r="F2029" t="n">
         <v>0.3019843260073736</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.097558988962711</v>
+        <v>4.061376436620667</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.917339571110997</v>
+        <v>3.881157018768953</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.12116311384792</v>
+        <v>-5.187443011787248</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.868517901258082</v>
+        <v>1.805823389740307</v>
       </c>
       <c r="F2030" t="n">
         <v>0.3019843260073736</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.098530166715422</v>
+        <v>4.062347614373378</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.918182475490752</v>
+        <v>3.881999923148709</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.070124737841399</v>
+        <v>-5.136404635780727</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.889776156040445</v>
+        <v>1.827081644522671</v>
       </c>
       <c r="F2031" t="n">
         <v>0.3019843260073736</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.099373071095177</v>
+        <v>4.063190518753133</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.937220574364898</v>
+        <v>3.901038022022854</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.028985442974768</v>
+        <v>-5.095265340914096</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.925269972861243</v>
+        <v>1.862575461343468</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3431236208740044</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.143094746889301</v>
+        <v>4.106912194547257</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700479</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.753404570488832</v>
+        <v>3.717222018146789</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.918379302895167</v>
+        <v>-4.984659200834495</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.785696425017018</v>
+        <v>1.723001913499243</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4537297609536064</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.025642427060997</v>
+        <v>3.989459874718952</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.756906614562796</v>
+        <v>3.720724062220753</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.048960037426009</v>
+        <v>-5.115239935365337</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.736966175278645</v>
+        <v>1.674271663760871</v>
       </c>
       <c r="F2034" t="n">
         <v>0.3231490264227639</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.950796030416455</v>
+        <v>3.914613478074411</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.741333433638879</v>
+        <v>3.705150881296835</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.884463703235047</v>
+        <v>-4.950743601174375</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.787191528031112</v>
+        <v>1.724497016513338</v>
       </c>
       <c r="F2035" t="n">
         <v>0.3231490264227639</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.935222849492537</v>
+        <v>3.899040297150494</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.740521144075308</v>
+        <v>3.704338591733265</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.911833635919479</v>
+        <v>-4.978113533858807</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.775431265393769</v>
+        <v>1.712736753875995</v>
       </c>
       <c r="F2036" t="n">
         <v>0.3231490264227639</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.934410559928967</v>
+        <v>3.898228007586924</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.750389923200381</v>
+        <v>3.714207370858337</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.922218830809369</v>
+        <v>-4.988498728748697</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.781145966562886</v>
+        <v>1.718451455045111</v>
       </c>
       <c r="F2037" t="n">
         <v>0.3127638315328746</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.938048222120106</v>
+        <v>3.901865669778062</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735283</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.821226928976806</v>
+        <v>3.785044376634763</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.940806989531594</v>
+        <v>-5.007086887470922</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.844547708850421</v>
+        <v>1.781853197332647</v>
       </c>
       <c r="F2038" t="n">
         <v>0.2941756728106492</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.997732332663196</v>
+        <v>3.961549780321152</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.818095939795104</v>
+        <v>3.781913387453061</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.94110553622763</v>
+        <v>-5.007385434166958</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.841297300990305</v>
+        <v>1.778602789472531</v>
       </c>
       <c r="F2039" t="n">
         <v>0.2941756728106492</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.994601343481494</v>
+        <v>3.958418791139451</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108858</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.822626834734496</v>
+        <v>3.786444282392452</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.840282402537202</v>
+        <v>-4.90656230047653</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.886157449405868</v>
+        <v>1.823462937888093</v>
       </c>
       <c r="F2040" t="n">
         <v>0.306639888295003</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.006610767711498</v>
+        <v>3.970428215369455</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.822756088213039</v>
+        <v>3.786573535870996</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.649501041784795</v>
+        <v>-4.715780939724123</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.962599247185374</v>
+        <v>1.899904735667599</v>
       </c>
       <c r="F2041" t="n">
         <v>0.4974212490474104</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.121208837641485</v>
+        <v>4.085026285299442</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.802592933950636</v>
+        <v>3.766410381608592</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.630984187742975</v>
+        <v>-4.697264085682303</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.949842834539699</v>
+        <v>1.887148323021924</v>
       </c>
       <c r="F2042" t="n">
         <v>0.5103513784726186</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.108803761034207</v>
+        <v>4.072621208692164</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912985</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.837559870562694</v>
+        <v>3.801377318220651</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.605791003241657</v>
+        <v>-4.672070901180985</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.994887044952284</v>
+        <v>1.93219253343451</v>
       </c>
       <c r="F2043" t="n">
         <v>0.5355445629739369</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.158886608347056</v>
+        <v>4.122704056005013</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.831246438464132</v>
+        <v>3.795063886122088</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.593736876328694</v>
+        <v>-4.660016774268022</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.993395263618907</v>
+        <v>1.930700752101132</v>
       </c>
       <c r="F2044" t="n">
         <v>0.5475986898868997</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.159805652396272</v>
+        <v>4.123623100054228</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811009</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.833127068648268</v>
+        <v>3.796944516306224</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.600360123019052</v>
+        <v>-4.66664002095838</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.992626595126899</v>
+        <v>1.929932083609125</v>
       </c>
       <c r="F2045" t="n">
         <v>0.5409754431965415</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.157712334566193</v>
+        <v>4.121529782224149</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.84597809452615</v>
+        <v>3.809795542184107</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.497479533490459</v>
+        <v>-4.563759431429787</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.046629856816219</v>
+        <v>1.983935345298445</v>
       </c>
       <c r="F2046" t="n">
         <v>0.6438560327251344</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.232291714161231</v>
+        <v>4.196109161819187</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.866180764699744</v>
+        <v>3.829998212357701</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.520921572670546</v>
+        <v>-4.587201470609874</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.057455711317779</v>
+        <v>1.994761199800004</v>
       </c>
       <c r="F2047" t="n">
         <v>0.6438560327251344</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.252494384334825</v>
+        <v>4.216311831992781</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.866180764699744</v>
+        <v>3.829998212357701</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.538994080962158</v>
+        <v>-4.605273978901486</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.050226708001134</v>
+        <v>1.987532196483359</v>
       </c>
       <c r="F2048" t="n">
         <v>0.6438560327251344</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.252494384334825</v>
+        <v>4.216311831992781</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.826432678293211</v>
+        <v>3.790250125951168</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.77016787483879</v>
+        <v>-4.836447772778118</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.918009104043948</v>
+        <v>1.855314592526173</v>
       </c>
       <c r="F2049" t="n">
         <v>0.6438560327251344</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.212746297928292</v>
+        <v>4.176563745586249</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.833455297290151</v>
+        <v>3.797272744948108</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.738881854298334</v>
+        <v>-4.805161752237662</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.93754613125707</v>
+        <v>1.874851619739295</v>
       </c>
       <c r="F2050" t="n">
         <v>0.6751420532655897</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.238540529249505</v>
+        <v>4.202357976907462</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.932626296863055</v>
+        <v>3.896443744521012</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.58585646218505</v>
+        <v>-4.652136360124378</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.097927287675287</v>
+        <v>2.035232776157514</v>
       </c>
       <c r="F2051" t="n">
         <v>0.8281674453788739</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.429526764090379</v>
+        <v>4.393344211748337</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.120092521771348</v>
+        <v>4.083909969429304</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.61416377605832</v>
+        <v>-4.680443673997648</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.274070587034272</v>
+        <v>2.211376075516498</v>
       </c>
       <c r="F2052" t="n">
         <v>0.8281674453788739</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.616992988998672</v>
+        <v>4.580810436656629</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699135800903171</v>
       </c>
       <c r="C2053" t="n">
-        <v>4.08949547312543</v>
+        <v>4.053312920783386</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.775660199895745</v>
+        <v>-4.841940097835073</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.178874968853385</v>
+        <v>2.11618045733561</v>
       </c>
       <c r="F2053" t="n">
         <v>0.6666710215414492</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.4894980860503</v>
+        <v>4.453315533708256</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.795428881514012</v>
+        <v>3.789444212357721</v>
       </c>
       <c r="C2054" t="n">
-        <v>4.177154815453494</v>
+        <v>4.300754571337287</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.775660199895745</v>
+        <v>-4.841940097835073</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.178874968853385</v>
+        <v>2.11618045733561</v>
       </c>
       <c r="F2054" t="n">
         <v>0.6666710215414492</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.170218612439862</v>
+        <v>4.293818368323655</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240812.xlsx
+++ b/tame_output/ON/bt/strategyON_20240812.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>51.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>80.1%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>118.4%</t>
+          <t>97.7%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>110.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-581.5%</t>
+          <t>-597.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.3%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.1%</t>
+          <t>430.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-645.8%</t>
+          <t>-639.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-233.0%</t>
+          <t>-239.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.5%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-164.6%</t>
+          <t>-158.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-314.1%</t>
+          <t>-338.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-157.3%</t>
+          <t>-146.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>83.4%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>83.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>9.6%</t>
         </is>
       </c>
     </row>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382325</v>
+        <v>3.235981977382324</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.803099376914839</v>
+        <v>-2.960208298997795</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.016494362672563</v>
+        <v>1.953650793839381</v>
       </c>
       <c r="F1855" t="n">
         <v>0.2070821474982212</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.052970056929421</v>
+        <v>-3.210078979012376</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.918315214121346</v>
+        <v>1.855471645288164</v>
       </c>
       <c r="F1856" t="n">
         <v>0.2433448673286845</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130013</v>
+        <v>3.287377576130012</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.259481833816443</v>
+        <v>-3.416590755899398</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.831816562022796</v>
+        <v>1.768972993189614</v>
       </c>
       <c r="F1857" t="n">
         <v>0.036833090441663</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178239</v>
+        <v>3.315884374178238</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.578825908896944</v>
+        <v>-3.735934830979899</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.705851858690854</v>
+        <v>1.643008289857673</v>
       </c>
       <c r="F1858" t="n">
         <v>0.036833090441663</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.305316798207808</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.965035740172719</v>
+        <v>-4.122144662255674</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.537700813647949</v>
+        <v>1.474857244814767</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.05393984927578033</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.199729734305272</v>
+        <v>-4.356838656388226</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.432107990997018</v>
+        <v>1.369264422163837</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.04760358204652515</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.535392381535725</v>
+        <v>-4.692501303618679</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.296423523760803</v>
+        <v>1.233579954927621</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.11553456753543</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.611836711738596</v>
+        <v>-4.76894563382155</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.272333351913896</v>
+        <v>1.209489783080714</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.03508905844176807</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.976964094377343</v>
+        <v>-5.134073016460297</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.125536913864228</v>
+        <v>1.062693345031047</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.3313998427407806</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.385552871558021</v>
+        <v>-5.542661793640976</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.9608629470067158</v>
+        <v>0.8980193781735339</v>
       </c>
       <c r="F1864" t="n">
         <v>-0.739988619921459</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.499313283580886</v>
+        <v>-5.656422205663841</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.9105442146690308</v>
+        <v>0.8477006458358489</v>
       </c>
       <c r="F1865" t="n">
         <v>-0.739988619921459</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.915705157867883</v>
+        <v>-6.072814079950838</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.7419815155631091</v>
+        <v>0.6791379467299272</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.739988619921459</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.276878787684871</v>
+        <v>-6.433987709767826</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.6077707543049931</v>
+        <v>0.5449271854718107</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.739988619921459</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.62013730732789</v>
+        <v>-6.777246229410845</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.4665669115934805</v>
+        <v>0.4037233427602986</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.739988619921459</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.668340124570234</v>
+        <v>-6.825449046653189</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.4456907047515437</v>
+        <v>0.3828471359183618</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.739988619921459</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.965001466380431</v>
+        <v>-7.122110388463386</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.330805143956673</v>
+        <v>0.2679615751234912</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.8087317556553376</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.151721174689734</v>
+        <v>-7.308830096772689</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2520909560985487</v>
+        <v>0.1892473872653668</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.8087317556553376</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.534722563432365</v>
+        <v>-7.69183148551532</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.09878829927991228</v>
+        <v>0.03594473044673041</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.8087317556553376</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.539209008633754</v>
+        <v>-7.696317930716709</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.09956523717078714</v>
+        <v>0.03672166833760526</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.8132182008567264</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.898739331137755</v>
+        <v>-8.055848253220711</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.03889658853276323</v>
+        <v>-0.1017401573659455</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.8132182008567264</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.949088394591977</v>
+        <v>-8.106197316674933</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.05112019395727474</v>
+        <v>-0.1139637627904571</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.8635672643109484</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.046707672013374</v>
+        <v>-8.203816594096329</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.08712615430406467</v>
+        <v>-0.1499697231372465</v>
       </c>
       <c r="F1876" t="n">
         <v>-0.9611865417323451</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.100779171521733</v>
+        <v>-8.257888093604688</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1058611977858361</v>
+        <v>-0.168704766619018</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.015258041240704</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.305037346851597</v>
+        <v>-8.462146268934552</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1820512707991391</v>
+        <v>-0.2448948396323209</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.142896985854693</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.33869018536007</v>
+        <v>-8.495799107443025</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1910298517180924</v>
+        <v>-0.2538734205512743</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.243310353771731</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.265220353692621</v>
+        <v>-8.422329275775576</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1462702175576918</v>
+        <v>-0.2091137863908736</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.169840522104282</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.440344771079165</v>
+        <v>-8.597453693162119</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2017647637647921</v>
+        <v>-0.264608332597974</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.344964939490826</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.674796865093654</v>
+        <v>-8.831905787176609</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3027647662721842</v>
+        <v>-0.3656083351053661</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.344964939490826</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.779171596120101</v>
+        <v>-8.936280518203056</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.3511868494567389</v>
+        <v>-0.4140304182899208</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.449339670517272</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.941685061818685</v>
+        <v>-9.09879398390164</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4150764458976162</v>
+        <v>-0.477920014730798</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.546973100935959</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.067721855186974</v>
+        <v>-9.224830777269929</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.4627974346158172</v>
+        <v>-0.5256410034489991</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.521721478126216</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.010650083291043</v>
+        <v>-9.167759005373998</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4359783901710443</v>
+        <v>-0.4988219590042262</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.521721478126216</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.152321925015164</v>
+        <v>-9.309430847098119</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.4941223537594341</v>
+        <v>-0.556965922592616</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.521721478126216</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.102731080590329</v>
+        <v>-9.259840002673284</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.4592326058246279</v>
+        <v>-0.5220761746578098</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.472130633701382</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.953812746118473</v>
+        <v>-9.110921668201428</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4127164056825685</v>
+        <v>-0.4755599745157504</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.440881042966209</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68516138161528</v>
+        <v>3.685161381615279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.727967593399061</v>
+        <v>-8.885076515482016</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3127992715585948</v>
+        <v>-0.3756428403917771</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.398954367379046</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.603388937061469</v>
+        <v>-8.760497859144424</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.2618286644674992</v>
+        <v>-0.3246722333006811</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.398954367379046</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.656284225105756</v>
+        <v>-8.813393147188711</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2803530055231063</v>
+        <v>-0.3431965743562881</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.393999021290599</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611565</v>
+        <v>3.768951674611564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.584151049817875</v>
+        <v>-8.741259971900829</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2457660311693175</v>
+        <v>-0.3086096000024994</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.393999021290599</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.512784657208227</v>
+        <v>-8.669893579291182</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2269567365193237</v>
+        <v>-0.2898003053525056</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.322632628680952</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.419325623223003</v>
+        <v>-8.576434545305958</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.1994566042381414</v>
+        <v>-0.2623001730713233</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.322632628680952</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.408672441669571</v>
+        <v>-8.565781363752526</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.1970298921161424</v>
+        <v>-0.2598734609493243</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.322632628680952</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.310765402993081</v>
+        <v>-8.467874325076036</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1581673916190072</v>
+        <v>-0.221010960452189</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.254646878820395</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.80082935409724</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.286811862017123</v>
+        <v>-8.443920784100078</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1479174690831302</v>
+        <v>-0.2107610379163121</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.230693337844438</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017768</v>
+        <v>3.789311112017767</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.022751923694326</v>
+        <v>-8.179860845777281</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.05555380991576353</v>
+        <v>-0.1183973787489458</v>
       </c>
       <c r="F1899" t="n">
         <v>-0.9666333995216414</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.315672300189488</v>
+        <v>-7.472781222272443</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2244910058258709</v>
+        <v>0.1616474369926886</v>
       </c>
       <c r="F1900" t="n">
         <v>-0.9666333995216414</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.275488001823297</v>
+        <v>-7.432596923906252</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2409083490601884</v>
+        <v>0.1780647802270061</v>
       </c>
       <c r="F1901" t="n">
         <v>-0.9264491011554506</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.112088130883935</v>
+        <v>-7.26919705296689</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.3056351186566904</v>
+        <v>0.242791549823508</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.7630492302160882</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.878606908654336</v>
+        <v>-7.035715830737291</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4069520363863819</v>
+        <v>0.3441084675532</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.5295680079864896</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.728940517646821</v>
+        <v>-6.886049439729776</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.463926382476429</v>
+        <v>0.4010828136432467</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.4366645167439537</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.596665044015935</v>
+        <v>-6.75377396609889</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5122040586758105</v>
+        <v>0.4493604898426287</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.304389043113067</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.440926711456193</v>
+        <v>-6.598035633539148</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5773144523873439</v>
+        <v>0.514470883554162</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.1486507105533255</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.355962044726873</v>
+        <v>-6.513070966809828</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6242066603027308</v>
+        <v>0.5613630914695489</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.06368604382400589</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.461552034499977</v>
+        <v>-6.618660956582932</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4539947347942701</v>
+        <v>0.3911511659610882</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.1692760335971102</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704225839879</v>
+        <v>3.770422583987899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.39331744987455</v>
+        <v>-6.550426371957505</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5298329105215274</v>
+        <v>0.4669893416883455</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.1508607107245742</v>
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.931454839754883</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.24537740846695</v>
+        <v>-6.419499039716699</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4329474520543553</v>
+        <v>0.3994813518965001</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1305397948160167</v>
+        <v>-0.09846630795886496</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.853130962865273</v>
+        <v>2.908557607321609</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409203</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.922740853501405</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.192407886212962</v>
+        <v>-6.366529517462711</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4454212747024728</v>
+        <v>0.4119551745446173</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.04549678570487609</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.876198689964188</v>
+        <v>2.931625334420524</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.915780241406312</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.026619690252671</v>
+        <v>-6.20074132150242</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5047759409914958</v>
+        <v>0.4713098408336407</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.04549678570487609</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.869238077869095</v>
+        <v>2.924664722325431</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.930242595787455</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.993256483773902</v>
+        <v>-6.167378115023651</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5325835779641466</v>
+        <v>0.499117477806291</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.04549678570487609</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.883700432250238</v>
+        <v>2.939127076706574</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.92477471624665</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.884997346651381</v>
+        <v>-6.05911897790113</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5704193532723503</v>
+        <v>0.5369532531144947</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.04549678570487609</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.878232552709433</v>
+        <v>2.933659197165769</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.922272810257227</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.76170621183425</v>
+        <v>-5.935827843083999</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6172339012097794</v>
+        <v>0.5837678010519243</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.04572086225510269</v>
+        <v>0.07779434911225441</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.949705327610288</v>
+        <v>3.005131972066624</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.929973788494552</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.709009344702959</v>
+        <v>-5.883130975952708</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.646013626299621</v>
+        <v>0.6125475261417659</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.09841772938639387</v>
+        <v>0.1304912162435456</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.989024426126389</v>
+        <v>3.044451070582724</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.925754496841602</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.465243902719514</v>
+        <v>-5.639365533969263</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7393005114400495</v>
+        <v>0.7058344112821944</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.09841772938639387</v>
+        <v>0.1304912162435456</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.984805134473439</v>
+        <v>3.040231778929774</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.927878810761618</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.375468230343042</v>
+        <v>-5.549589861592791</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7773350943106543</v>
+        <v>0.7438689941527992</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.1920906611578556</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.023889115342041</v>
+        <v>3.079315759798376</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.920620885745321</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.125617836393968</v>
+        <v>-5.299739467643716</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8700173268739864</v>
+        <v>0.8365512267161312</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.1920906611578556</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.016631190325743</v>
+        <v>3.072057834782079</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011494</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.924220009265969</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.949725743926535</v>
+        <v>-5.123847375176284</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.943973287381608</v>
+        <v>0.9105071872237525</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.1920906611578556</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.020230313846392</v>
+        <v>3.075656958302727</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.937547515320523</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.778279280904072</v>
+        <v>-4.952400912153821</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.025879378645147</v>
+        <v>0.9924132784872917</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.331463637323167</v>
+        <v>0.3635371241803187</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.136425697714424</v>
+        <v>3.191852342170759</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632777</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.93656799293682</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.703989715165733</v>
+        <v>-4.878111346415482</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.05461568255678</v>
+        <v>1.021149582398924</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.4057532030615063</v>
+        <v>0.437826689918658</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.180019914773724</v>
+        <v>3.235446559230059</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.941262793991137</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.640353972931798</v>
+        <v>-4.814475604181547</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.084764780504671</v>
+        <v>1.051298680346815</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4693889452954408</v>
+        <v>0.5014624321525926</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.222896161168402</v>
+        <v>3.278322805624737</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.922457052774933</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.528927213605878</v>
+        <v>-4.703048844855627</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.110529743018834</v>
+        <v>1.077063642860979</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4693889452954408</v>
+        <v>0.5014624321525926</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.204090419952198</v>
+        <v>3.259517064408533</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.92420012939981</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.539429836671167</v>
+        <v>-4.713551467920916</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.108071770417596</v>
+        <v>1.074605670259741</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.458886322230152</v>
+        <v>0.4909598090873037</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.199531922737902</v>
+        <v>3.254958567194237</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.928129443234631</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.467187268499972</v>
+        <v>-4.641308899749721</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.140898111520894</v>
+        <v>1.107432011363039</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.458886322230152</v>
+        <v>0.4909598090873037</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.203461236572722</v>
+        <v>3.258887881029057</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.928808027151971</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.449473581622107</v>
+        <v>-4.623595212871856</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.14866217018938</v>
+        <v>1.115196070031525</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4620676511270688</v>
+        <v>0.4941411379842205</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.206048617828212</v>
+        <v>3.261475262284547</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.925806098371964</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.34066869614238</v>
+        <v>-4.514790327392129</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.189182195601265</v>
+        <v>1.155716095443409</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4620676511270688</v>
+        <v>0.4941411379842205</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.203046689048206</v>
+        <v>3.258473333504541</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.927385135382578</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.12064789810537</v>
+        <v>-4.294769529355118</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.278769551826683</v>
+        <v>1.245303451668828</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.603287496195049</v>
+        <v>0.6353609830522008</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.289357633099608</v>
+        <v>3.344784277555943</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.943279318184401</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.987780209042092</v>
+        <v>-4.161901840291841</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.347810810253818</v>
+        <v>1.314344710095962</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.603287496195049</v>
+        <v>0.6353609830522008</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.305251815901431</v>
+        <v>3.360678460357767</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.944425162624703</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.867607125677592</v>
+        <v>-4.041728756927342</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.397025888039919</v>
+        <v>1.363559787882064</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7234605795595479</v>
+        <v>0.7555340664166997</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.378501510360432</v>
+        <v>3.433928154816768</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.954513265186143</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.732353764347615</v>
+        <v>-3.906475395597365</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.46121533513335</v>
+        <v>1.427749234975494</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.858713940889525</v>
+        <v>0.8907874277466769</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.469741629719858</v>
+        <v>3.525168274176194</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.940550756587569</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.792228591705308</v>
+        <v>-3.966350222955057</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.423302895591699</v>
+        <v>1.389836795433843</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7988391135318329</v>
+        <v>0.8309126003889847</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.419854224706669</v>
+        <v>3.475280869163004</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.955839925821778</v>
+        <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.67240836079447</v>
+        <v>-3.84652999204422</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.486520157190242</v>
+        <v>1.453054057032387</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7988391135318329</v>
+        <v>0.8309126003889847</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.435143393940877</v>
+        <v>3.490570038397213</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.863484125144219</v>
+        <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.674878067256276</v>
+        <v>-3.848999698506026</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.393176473927961</v>
+        <v>1.359710373770106</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7963694070700267</v>
+        <v>0.8284428939271786</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.341305769386235</v>
+        <v>3.396732413842571</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.782745986629521</v>
+        <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.743248253580286</v>
+        <v>-3.917369884830036</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.285090260883659</v>
+        <v>1.251624160725803</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8056451061062416</v>
+        <v>0.8377185929633936</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.266133050293266</v>
+        <v>3.321559694749601</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.773182695261412</v>
+        <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.757036306427333</v>
+        <v>-3.969840912514969</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.270011748376731</v>
+        <v>1.221072458283721</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8056451061062416</v>
+        <v>0.8377185929633936</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.256569758925157</v>
+        <v>3.311996403381492</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.910213531953614</v>
+        <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.812556382319922</v>
+        <v>-4.025360988407558</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.384834554711898</v>
+        <v>1.335895264618888</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8056451061062416</v>
+        <v>0.8377185929633936</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.39360059561736</v>
+        <v>3.449027240073695</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.914780763945402</v>
+        <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.637082122527453</v>
+        <v>-3.849886728615088</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.459591490620674</v>
+        <v>1.410652200527664</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8056451061062416</v>
+        <v>0.8377185929633936</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.398167827609147</v>
+        <v>3.453594472065483</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.890522792706609</v>
+        <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.748018375168702</v>
+        <v>-3.960822981256337</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.390959018325381</v>
+        <v>1.342019728232371</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8056451061062416</v>
+        <v>0.8377185929633936</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.373909856370354</v>
+        <v>3.42933650082669</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.819061106108059</v>
+        <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.71435482969642</v>
+        <v>-3.927159435784055</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.332962749915744</v>
+        <v>1.284023459822734</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8393086515785235</v>
+        <v>0.8713821384356755</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.322646297055173</v>
+        <v>3.378072941511509</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.829233492540191</v>
+        <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.654502210492697</v>
+        <v>-3.867306816580332</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.367076184029365</v>
+        <v>1.318136893936355</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8393086515785235</v>
+        <v>0.8713821384356755</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.332818683487305</v>
+        <v>3.388245327943641</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.824179763114052</v>
+        <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.568258747466319</v>
+        <v>-3.781063353553955</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.396519839813777</v>
+        <v>1.347580549720767</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8393086515785235</v>
+        <v>0.8713821384356755</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.327764954061166</v>
+        <v>3.383191598517501</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.815955538558577</v>
+        <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.613565566865299</v>
+        <v>-3.826370172952934</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.37017288749871</v>
+        <v>1.3212335974057</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7984984885692927</v>
+        <v>0.8305719754264447</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.295054631700153</v>
+        <v>3.350481276156488</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.816507411591679</v>
+        <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.642598671567601</v>
+        <v>-3.855403277655236</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.359111518650891</v>
+        <v>1.310172228557881</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7984984885692927</v>
+        <v>0.8305719754264447</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.295606504733255</v>
+        <v>3.35103314918959</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.745780103483044</v>
+        <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.549788190116741</v>
+        <v>-3.762592796204377</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.3255084031226</v>
+        <v>1.27656911302959</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8913089700201521</v>
+        <v>0.923382456877304</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.280565485495136</v>
+        <v>3.335992129951471</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.747653579407645</v>
+        <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.594177659446169</v>
+        <v>-3.806982265533804</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.30962609131543</v>
+        <v>1.26068680122242</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8469195006907244</v>
+        <v>0.8789929875478764</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.25580527982208</v>
+        <v>3.311231924278415</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.742729287919368</v>
+        <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.710719264551512</v>
+        <v>-3.923523870639147</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.258085157785016</v>
+        <v>1.209145867692006</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7303778955853817</v>
+        <v>0.7624513824425336</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.180956025270597</v>
+        <v>3.236382669726933</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.748220583750035</v>
+        <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.750643359134084</v>
+        <v>-3.963447965221719</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.247606815782655</v>
+        <v>1.198667525689645</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7303778955853817</v>
+        <v>0.7624513824425336</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.186447321101264</v>
+        <v>3.2418739655576</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.759717785518574</v>
+        <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.778423757035437</v>
+        <v>-3.991228363123072</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.247991858390652</v>
+        <v>1.199052568297643</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7025974976840286</v>
+        <v>0.7346709845411805</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.181276284128992</v>
+        <v>3.236702928585327</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.598073505519228</v>
+        <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.896804429765575</v>
+        <v>-4.10960903585321</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.03899530929925</v>
+        <v>0.9900560192062406</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6353796455330524</v>
+        <v>0.6674531323902043</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.979301292839059</v>
+        <v>3.034727937295395</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.718223166238433</v>
+        <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.005418508208907</v>
+        <v>-4.218223114296541</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.115699338641124</v>
+        <v>1.066760048548114</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6353796455330524</v>
+        <v>0.6674531323902043</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.099450953558265</v>
+        <v>3.1548775980146</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.732736192340756</v>
+        <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.970009469960764</v>
+        <v>-4.182814076048398</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.144375980042704</v>
+        <v>1.095436689949694</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6353796455330524</v>
+        <v>0.6674531323902043</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.113963979660588</v>
+        <v>3.169390624116923</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.730155633683125</v>
+        <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.931625807402613</v>
+        <v>-4.144430413490247</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.157148886408333</v>
+        <v>1.108209596315323</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6737633080912035</v>
+        <v>0.7058367949483555</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.134413618537848</v>
+        <v>3.189840262994183</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.726884662528427</v>
+        <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.754509477367447</v>
+        <v>-3.967314083455081</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.224724447267701</v>
+        <v>1.175785157174691</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6737633080912035</v>
+        <v>0.7058367949483555</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.131142647383149</v>
+        <v>3.186569291839485</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.72756805429034</v>
+        <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.799601722200992</v>
+        <v>-4.012406328288627</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.207370941096196</v>
+        <v>1.158431651003186</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6118672649218138</v>
+        <v>0.6439407517789657</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.094688413243428</v>
+        <v>3.150115057699764</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.721355029596754</v>
+        <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.620226300962224</v>
+        <v>-3.833030907049859</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.272908084898118</v>
+        <v>1.223968794805108</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7686440230925324</v>
+        <v>0.8007175099496844</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.182541443452274</v>
+        <v>3.23796808790861</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.702162484928344</v>
+        <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.66524051448283</v>
+        <v>-3.878045120570465</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.235709854821465</v>
+        <v>1.186770564728455</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7382951277779278</v>
+        <v>0.7703686146350798</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.145139561595101</v>
+        <v>3.200566206051437</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.70785404726729</v>
+        <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.932245024755266</v>
+        <v>-4.145049630842901</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.134599613051436</v>
+        <v>1.085660322958427</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5439320897349793</v>
+        <v>0.5760055765921313</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.034213301108278</v>
+        <v>3.089639945564613</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.707057969163791</v>
+        <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.033442806192438</v>
+        <v>-4.246247412280074</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.093324422373069</v>
+        <v>1.044385132280059</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4755232761896601</v>
+        <v>0.5075967630468121</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.992371934877588</v>
+        <v>3.047798579333923</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.704657930718108</v>
+        <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.026931839578126</v>
+        <v>-4.239736445665761</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.09352877057311</v>
+        <v>1.044589480480101</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4755232761896601</v>
+        <v>0.5075967630468121</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.989971896431904</v>
+        <v>3.04539854088824</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.701182649926353</v>
+        <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.007893711870828</v>
+        <v>-4.220698317958464</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.097668740864274</v>
+        <v>1.048729450771265</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4173396648584656</v>
+        <v>0.4494131517156176</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.951586448841432</v>
+        <v>3.007013093297768</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.820477051560543</v>
+        <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.060409514145649</v>
+        <v>-4.273214120233284</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.195956821588537</v>
+        <v>1.147017531495527</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4173396648584656</v>
+        <v>0.4494131517156176</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.070880850475623</v>
+        <v>3.126307494931958</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.821310380546677</v>
+        <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.074276275479567</v>
+        <v>-4.287080881567202</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.191243446041103</v>
+        <v>1.142304155948093</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3794817481246426</v>
+        <v>0.4115552349817946</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.048999429421463</v>
+        <v>3.104426073877798</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.827318910943603</v>
+        <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.049951690953036</v>
+        <v>-4.242276710027272</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.206981810248641</v>
+        <v>1.166234354960991</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3794817481246426</v>
+        <v>0.4115552349817946</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.055007959818389</v>
+        <v>3.110434604274724</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.725269132220802</v>
+        <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.902208720718034</v>
+        <v>-4.094533739792269</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.164029219619841</v>
+        <v>1.123281764332192</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5472891053595258</v>
+        <v>0.5793625922166779</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.053642595436518</v>
+        <v>3.109069239892853</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.728062753752283</v>
+        <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.986029941992732</v>
+        <v>-4.178354961066968</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.133294352641443</v>
+        <v>1.092546897353793</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5472891053595258</v>
+        <v>0.5793625922166779</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.056436216967999</v>
+        <v>3.111862861424334</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.728725102143942</v>
+        <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.979877235939948</v>
+        <v>-4.172202255014184</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.136417783454215</v>
+        <v>1.095670328166565</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5534418114123101</v>
+        <v>0.5855152982694621</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.060790188991328</v>
+        <v>3.116216833447663</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.727805578884052</v>
+        <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.996686534090449</v>
+        <v>-4.189011553164685</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.128774540934125</v>
+        <v>1.088027085646475</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5366325132618084</v>
+        <v>0.5687060001189606</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.049785086841137</v>
+        <v>3.105211731297473</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.794141132680873</v>
+        <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.934388535314327</v>
+        <v>-4.126713554388563</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.220029294241395</v>
+        <v>1.179281838953744</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5819267775362504</v>
+        <v>0.6140002643934026</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.143297199202623</v>
+        <v>3.198723843658959</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.596433134395</v>
+        <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.732598337649169</v>
+        <v>-3.924923356723405</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.103037375021585</v>
+        <v>1.062289919733935</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7799449697054048</v>
+        <v>0.812018456562557</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.064400116218243</v>
+        <v>3.119826760674579</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.666723366717175</v>
+        <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.783485050335364</v>
+        <v>-3.9758100694096</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.152972922269282</v>
+        <v>1.112225466981632</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7290582570192103</v>
+        <v>0.7611317438763625</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.104158320928701</v>
+        <v>3.159584965385037</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.681351102833219</v>
+        <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.696874307685557</v>
+        <v>-3.889199326759793</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.202244955445249</v>
+        <v>1.161497500157599</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8076839882243686</v>
+        <v>0.8397574750815208</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.16596149576784</v>
+        <v>3.221388140224176</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.67988708365789</v>
+        <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.757083605690841</v>
+        <v>-3.949408624765077</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.176697217067807</v>
+        <v>1.135949761780156</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7474746902190841</v>
+        <v>0.7795481770762362</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.128371897789341</v>
+        <v>3.183798542245677</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.678378701697819</v>
+        <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.680661559258914</v>
+        <v>-3.87298657833315</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.205757653680506</v>
+        <v>1.165010198392856</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7474746902190841</v>
+        <v>0.7795481770762362</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.12686351582927</v>
+        <v>3.182290160285605</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.678241569133255</v>
+        <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.636288427620346</v>
+        <v>-3.828613446694582</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.22336977377137</v>
+        <v>1.182622318483719</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7918478218576527</v>
+        <v>0.8239213087148048</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.153350262247847</v>
+        <v>3.208776906704182</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.672635363271846</v>
+        <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.658768778479231</v>
+        <v>-3.851093797553466</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.208771427566406</v>
+        <v>1.168023972278756</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7918478218576527</v>
+        <v>0.8239213087148048</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.147744056386438</v>
+        <v>3.203170700842773</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.67901712029965</v>
+        <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.611113047918175</v>
+        <v>-3.803438066992411</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.234215476818633</v>
+        <v>1.193468021530983</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8395035524187083</v>
+        <v>0.8715770392758605</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.182719251750875</v>
+        <v>3.238145896207211</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.683909493674375</v>
+        <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.51059488941942</v>
+        <v>-3.702919908493656</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.27931511359286</v>
+        <v>1.23856765830521</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9400217109174629</v>
+        <v>0.9720951977746151</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.247922520224853</v>
+        <v>3.303349164681189</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.670664166150247</v>
+        <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.494689559987068</v>
+        <v>-3.687014579061303</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.272431917841673</v>
+        <v>1.231684462554023</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8609090502082239</v>
+        <v>0.8929825370653761</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.187209596275182</v>
+        <v>3.242636240731517</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.674761868760876</v>
+        <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.44985115837867</v>
+        <v>-3.642176177452905</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.294464981095661</v>
+        <v>1.253717525808011</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8654524831530934</v>
+        <v>0.8975259700102456</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.194033358652732</v>
+        <v>3.249460003109068</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.678922808391954</v>
+        <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.469349614620678</v>
+        <v>-3.661674633694914</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.290826538229936</v>
+        <v>1.250079082942285</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8173678418731891</v>
+        <v>0.8494413287303413</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.169343513515868</v>
+        <v>3.224770157972203</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.684802410919791</v>
+        <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.425146777534777</v>
+        <v>-3.617471796609013</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.314387275592133</v>
+        <v>1.273639820304483</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8615706789590896</v>
+        <v>0.8936441658162417</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.201744818295245</v>
+        <v>3.257171462751581</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.683212411389039</v>
+        <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.432706443371824</v>
+        <v>-3.62503146244606</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.309773409726562</v>
+        <v>1.269025954438912</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9163740829689089</v>
+        <v>0.948447569826061</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.233036861170384</v>
+        <v>3.28846350562672</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.734460176572078</v>
+        <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.274415025832552</v>
+        <v>-3.466740044906788</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.42433774192531</v>
+        <v>1.38359028663766</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9163740829689089</v>
+        <v>0.948447569826061</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.284284626353424</v>
+        <v>3.339711270809759</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.732900881166331</v>
+        <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.066773022198076</v>
+        <v>-3.259098041272312</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.505835247973354</v>
+        <v>1.465087792685704</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.124016086603385</v>
+        <v>1.156089573460537</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.407310533128363</v>
+        <v>3.462737177584698</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.727849109404601</v>
+        <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.015740929475548</v>
+        <v>-3.208065948549784</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.521196313300635</v>
+        <v>1.480448858012985</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.175048179325913</v>
+        <v>1.207121666183065</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.432878017000149</v>
+        <v>3.488304661456485</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.745036513497306</v>
+        <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.950516748348342</v>
+        <v>-3.142841767422578</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.564473389844222</v>
+        <v>1.523725934556572</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.240272360453119</v>
+        <v>1.272345847310271</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.489199929769178</v>
+        <v>3.544626574225513</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.740997485796587</v>
+        <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.913089728277208</v>
+        <v>-3.105414747351444</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.575405170171956</v>
+        <v>1.534657714884306</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.2455238984823</v>
+        <v>1.277597385339452</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.488311824885967</v>
+        <v>3.543738469342303</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.742254278127827</v>
+        <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.933201384311916</v>
+        <v>-3.125526403386152</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.568617300089313</v>
+        <v>1.527869844801663</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.25655124347972</v>
+        <v>1.288624730336872</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.496185024215659</v>
+        <v>3.551611668671995</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.902812049149038</v>
+        <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.879456569884712</v>
+        <v>-3.071781588958947</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.750672996881406</v>
+        <v>1.709925541593756</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.266614552920182</v>
+        <v>1.298688039777334</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.662780780901147</v>
+        <v>3.718207425357482</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.022924958366855</v>
+        <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.804674308859699</v>
+        <v>-2.996999327933935</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.900698810509228</v>
+        <v>1.859951355221578</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.341396813945194</v>
+        <v>1.373470300802346</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.827763046733972</v>
+        <v>3.883189691190307</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.014632934380714</v>
+        <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.778590224595891</v>
+        <v>-2.970915243670127</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.90284042022861</v>
+        <v>1.86209296494096</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.341396813945194</v>
+        <v>1.373470300802346</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.819471022747831</v>
+        <v>3.874897667204166</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.012826129964493</v>
+        <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.690712311486771</v>
+        <v>-2.883037330561006</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.936184781056038</v>
+        <v>1.895437325768388</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.457322456368546</v>
+        <v>1.489395943225698</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.887219603785621</v>
+        <v>3.942646248241957</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.030380535691285</v>
+        <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.681819850093487</v>
+        <v>-2.874144869167723</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.957296171340142</v>
+        <v>1.916548716052493</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.457322456368546</v>
+        <v>1.489395943225698</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.904774009512412</v>
+        <v>3.960200653968748</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.022235583095869</v>
+        <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.850295967063365</v>
+        <v>-3.042620986137601</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.881760771956775</v>
+        <v>1.841013316669125</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.429374620651965</v>
+        <v>1.461448107509117</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.879860355487048</v>
+        <v>3.935286999943383</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.003505280283731</v>
+        <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.152496438201782</v>
+        <v>-2.344821457276018</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.14215028068927</v>
+        <v>2.101402825401621</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.359026561281554</v>
+        <v>1.391100048138706</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.818921217052663</v>
+        <v>3.874347861508999</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.994169302780635</v>
+        <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.129775334518629</v>
+        <v>-2.322100353592865</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.141902744659436</v>
+        <v>2.101155289371786</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.359026561281554</v>
+        <v>1.391100048138706</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.809585239549568</v>
+        <v>3.865011884005903</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.153075428631804</v>
+        <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.258977147812672</v>
+        <v>-2.451302166886907</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.249128145192988</v>
+        <v>2.208380689905338</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.229824747987512</v>
+        <v>1.261898234844664</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.890970277424311</v>
+        <v>3.946396921880647</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.190153251125451</v>
+        <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.413758154590927</v>
+        <v>-2.606083173665163</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.224293564975333</v>
+        <v>2.183546109687683</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.196457073933036</v>
+        <v>1.228530560790188</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.908027495485273</v>
+        <v>3.963454139941608</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.186828607114996</v>
+        <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.406703464375754</v>
+        <v>-2.599028483449989</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.223790797050947</v>
+        <v>2.183043341763297</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.20351176414821</v>
+        <v>1.235585251005362</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.908935665603922</v>
+        <v>3.964362310060257</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.196834760759737</v>
+        <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.379752240049266</v>
+        <v>-2.572077259123501</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.244577440426284</v>
+        <v>2.203829985138634</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.218392110175929</v>
+        <v>1.250465597033081</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.927870026865294</v>
+        <v>3.98329667132163</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.380937892904697</v>
+        <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.515705248105582</v>
+        <v>-2.708030267179818</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.374299369348717</v>
+        <v>2.333551914061067</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.218392110175929</v>
+        <v>1.250465597033081</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.111973159010255</v>
+        <v>4.16739980346659</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.37305458780769</v>
+        <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.538113365910454</v>
+        <v>-2.73043838498469</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.357452817129762</v>
+        <v>2.316705361842112</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.218392110175929</v>
+        <v>1.250465597033081</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.104089853913248</v>
+        <v>4.159516498369583</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.375108587357328</v>
+        <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.566337601488054</v>
+        <v>-2.75866262056229</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.348217122448359</v>
+        <v>2.307469667160709</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.236368862627237</v>
+        <v>1.268442349484389</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.11692990493367</v>
+        <v>4.172356549390006</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.431362305079175</v>
+        <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.575778527376584</v>
+        <v>-2.76810354645082</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.400694469814794</v>
+        <v>2.359947014527144</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.358795980170629</v>
+        <v>1.390869467027781</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.246639893181553</v>
+        <v>4.302066537637888</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.434253399624476</v>
+        <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.628052134712226</v>
+        <v>-2.820377153786461</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.382676121425838</v>
+        <v>2.341928666138188</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.306522372834988</v>
+        <v>1.338595859692139</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.218166823325468</v>
+        <v>4.273593467781804</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347704</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.432365212518251</v>
+        <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.704382112313132</v>
+        <v>-2.896707131387367</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.350255943279251</v>
+        <v>2.309508487991601</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.306522372834988</v>
+        <v>1.338595859692139</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.216278636219243</v>
+        <v>4.27170528067558</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.427185442121113</v>
+        <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.906635832637485</v>
+        <v>-3.098960851711721</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.264174684752372</v>
+        <v>2.223427229464722</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.104268652510634</v>
+        <v>1.136342139367786</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.089746633627493</v>
+        <v>4.14517327808383</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.425619452331266</v>
+        <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.06820425816474</v>
+        <v>-3.260529277238976</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.197981324751622</v>
+        <v>2.157233869463972</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9774857287127546</v>
+        <v>1.009559215569907</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.012110889558919</v>
+        <v>4.067537534015254</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.75459613538935</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.438692859197184</v>
+        <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.200505550262293</v>
+        <v>-3.392830569336529</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.15813421477852</v>
+        <v>2.11738675949087</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9774857287127546</v>
+        <v>1.009559215569907</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.025184296424837</v>
+        <v>4.080610940881173</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749882691378392</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.430698055980124</v>
+        <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.386373861101523</v>
+        <v>-3.578698880175759</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.075792087225768</v>
+        <v>2.035044631938117</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8189201353928069</v>
+        <v>0.850993622249959</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.922050137215809</v>
+        <v>3.977476781672144</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.429222097107126</v>
+        <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.414274648210996</v>
+        <v>-3.606599667285232</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.06315581350898</v>
+        <v>2.02240835822133</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7843232112498721</v>
+        <v>0.8163966981070242</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.89981602385705</v>
+        <v>3.955242668313385</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.425986541084325</v>
+        <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.53680075091389</v>
+        <v>-3.729125769988126</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.010909816405022</v>
+        <v>1.970162361117372</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6617971085469783</v>
+        <v>0.6938705954041303</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.823064806212512</v>
+        <v>3.878491450668847</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.492692500674829</v>
+        <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.767315247099479</v>
+        <v>-3.959640266173714</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.98540997752129</v>
+        <v>1.94466252223364</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4312826123613895</v>
+        <v>0.4633560992185416</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.751462068091663</v>
+        <v>3.806888712547998</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.633004219676676</v>
+        <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.024036065094302</v>
+        <v>-4.216361084168538</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.023033369325208</v>
+        <v>1.982285914037558</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3228680382175747</v>
+        <v>0.3549415250747268</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.826725042607221</v>
+        <v>3.882151687063556</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.701984488822315</v>
+        <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.178022482870443</v>
+        <v>-4.370347501944678</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.030419071360391</v>
+        <v>1.989671616072741</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3228680382175747</v>
+        <v>0.3549415250747268</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.89570531175286</v>
+        <v>3.951131956209196</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.688035690942436</v>
+        <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.350889399065061</v>
+        <v>-4.319825598117013</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.947323507002665</v>
+        <v>1.995931579723928</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3228680382175747</v>
+        <v>0.3549415250747268</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.881756513872981</v>
+        <v>3.937183158329317</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.69990617999785</v>
+        <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.603364553072786</v>
+        <v>-4.572300752124737</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.858203934454989</v>
+        <v>1.906812007176252</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3228680382175747</v>
+        <v>0.3549415250747268</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.893627002928395</v>
+        <v>3.949053647384731</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.701116714516794</v>
+        <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.896260309552198</v>
+        <v>-4.865196508604149</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.742256166382168</v>
+        <v>1.790864239103431</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3228680382175747</v>
+        <v>0.3549415250747268</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.894837537447339</v>
+        <v>3.950264181903675</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.705238456744115</v>
+        <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.05380438128164</v>
+        <v>-5.022740580333591</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.683360279917713</v>
+        <v>1.731968352638976</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2559662330773002</v>
+        <v>0.2880397199344523</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.858818196590496</v>
+        <v>3.914244841046831</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.700316309480305</v>
+        <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.331768776864913</v>
+        <v>-5.300704975916864</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.567252374420592</v>
+        <v>1.615860447141856</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.166346498791816</v>
+        <v>0.198419985648968</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.800124208755395</v>
+        <v>3.85555085321173</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.862520366179349</v>
+        <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.448736469503804</v>
+        <v>-5.417672668555755</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.68266935406408</v>
+        <v>1.731277426785344</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.166346498791816</v>
+        <v>0.198419985648968</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.962328265454439</v>
+        <v>4.017754909910774</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.857367004143163</v>
+        <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.533454411724757</v>
+        <v>-5.502390610776708</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.643628815139513</v>
+        <v>1.692236887860777</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.08123046986376958</v>
+        <v>0.1133039567209216</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.906105286061425</v>
+        <v>3.961531930517761</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.867596421711654</v>
+        <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.615389229993641</v>
+        <v>-5.584325429045592</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.621084305400451</v>
+        <v>1.669692378121715</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.0712957242766894</v>
+        <v>0.1033692111338415</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.910373856277668</v>
+        <v>3.965800500734003</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.876522060167557</v>
+        <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.717365352242048</v>
+        <v>-5.686301551293999</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.58921949495699</v>
+        <v>1.637827567678254</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.03068039797171818</v>
+        <v>0.00139308888543388</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.858113821384526</v>
+        <v>3.913540465840861</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.868674947411732</v>
+        <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.607359068764826</v>
+        <v>-5.576295267816778</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.625374895592054</v>
+        <v>1.673982968313318</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.007475826054442969</v>
+        <v>0.02459766080270909</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.864189451779067</v>
+        <v>3.919616096235402</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.872924958133706</v>
+        <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.464299493023901</v>
+        <v>-5.433235692075852</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.686848736610399</v>
+        <v>1.735456809331662</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.0005376005355363089</v>
+        <v>0.03261108739268836</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.873247518455028</v>
+        <v>3.928674162911364</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.880185841016242</v>
+        <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.162852767552064</v>
+        <v>-5.131788966604015</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.814688309681669</v>
+        <v>1.863296382402933</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3019843260073736</v>
+        <v>0.3340578128645256</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.061376436620667</v>
+        <v>4.116803081077002</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.881157018768953</v>
+        <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.187443011787248</v>
+        <v>-5.156379210839199</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.805823389740307</v>
+        <v>1.85443146246157</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3019843260073736</v>
+        <v>0.3340578128645256</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.062347614373378</v>
+        <v>4.117774258829713</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.881999923148709</v>
+        <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.136404635780727</v>
+        <v>-5.105340834832679</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.827081644522671</v>
+        <v>1.875689717243934</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3019843260073736</v>
+        <v>0.3340578128645256</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.063190518753133</v>
+        <v>4.118617163209468</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.901038022022854</v>
+        <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.095265340914096</v>
+        <v>-5.064201539966048</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.862575461343468</v>
+        <v>1.911183534064731</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3431236208740044</v>
+        <v>0.3751971077311564</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.106912194547257</v>
+        <v>4.162338839003592</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700479</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.717222018146789</v>
+        <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.984659200834495</v>
+        <v>-4.953595399886446</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.723001913499243</v>
+        <v>1.771609986220507</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4537297609536064</v>
+        <v>0.4858032478107585</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.989459874718952</v>
+        <v>4.044886519175288</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.720724062220753</v>
+        <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.115239935365337</v>
+        <v>-5.084176134417288</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.674271663760871</v>
+        <v>1.722879736482133</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3231490264227639</v>
+        <v>0.3552225132799159</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.914613478074411</v>
+        <v>3.970040122530746</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.705150881296835</v>
+        <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.950743601174375</v>
+        <v>-4.919679800226326</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.724497016513338</v>
+        <v>1.773105089234601</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3231490264227639</v>
+        <v>0.3552225132799159</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.899040297150494</v>
+        <v>3.954466941606828</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.704338591733265</v>
+        <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.978113533858807</v>
+        <v>-4.947049732910759</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.712736753875995</v>
+        <v>1.761344826597258</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3231490264227639</v>
+        <v>0.3552225132799159</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.898228007586924</v>
+        <v>3.953654652043258</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.714207370858337</v>
+        <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.988498728748697</v>
+        <v>-4.957434927800648</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.718451455045111</v>
+        <v>1.767059527766374</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3127638315328746</v>
+        <v>0.3448373183900266</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.901865669778062</v>
+        <v>3.957292314234397</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735283</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.785044376634763</v>
+        <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.007086887470922</v>
+        <v>-4.976023086522873</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.781853197332647</v>
+        <v>1.83046127005391</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.2941756728106492</v>
+        <v>0.3262491596678013</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.961549780321152</v>
+        <v>4.016976424777487</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.781913387453061</v>
+        <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.007385434166958</v>
+        <v>-4.976321633218909</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.778602789472531</v>
+        <v>1.827210862193794</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.2941756728106492</v>
+        <v>0.3262491596678013</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.958418791139451</v>
+        <v>4.013845435595785</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108858</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.786444282392452</v>
+        <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.90656230047653</v>
+        <v>-4.875498499528481</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.823462937888093</v>
+        <v>1.872071010609356</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.306639888295003</v>
+        <v>0.3387133751521551</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.970428215369455</v>
+        <v>4.025854859825789</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.786573535870996</v>
+        <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.715780939724123</v>
+        <v>-4.684717138776074</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.899904735667599</v>
+        <v>1.948512808388862</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4974212490474104</v>
+        <v>0.5294947359045625</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.085026285299442</v>
+        <v>4.140452929755777</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.766410381608592</v>
+        <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.697264085682303</v>
+        <v>-4.666200284734254</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.887148323021924</v>
+        <v>1.935756395743187</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5103513784726186</v>
+        <v>0.5424248653297707</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.072621208692164</v>
+        <v>4.128047853148498</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912985</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.801377318220651</v>
+        <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.672070901180985</v>
+        <v>-4.641007100232936</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.93219253343451</v>
+        <v>1.980800606155773</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.5355445629739369</v>
+        <v>0.5676180498310891</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.122704056005013</v>
+        <v>4.178130700461348</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.795063886122088</v>
+        <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.660016774268022</v>
+        <v>-4.628952973319973</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.930700752101132</v>
+        <v>1.979308824822395</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.5475986898868997</v>
+        <v>0.5796721767440519</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.123623100054228</v>
+        <v>4.179049744510563</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811009</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.796944516306224</v>
+        <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.66664002095838</v>
+        <v>-4.635576220010331</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.929932083609125</v>
+        <v>1.978540156330388</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5409754431965415</v>
+        <v>0.5730489300536936</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.121529782224149</v>
+        <v>4.176956426680484</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.809795542184107</v>
+        <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.563759431429787</v>
+        <v>-4.532695630481738</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.983935345298445</v>
+        <v>2.032543418019707</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6438560327251344</v>
+        <v>0.6759295195822865</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.196109161819187</v>
+        <v>4.251535806275522</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.829998212357701</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.587201470609874</v>
+        <v>-4.556137669661825</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.994761199800004</v>
+        <v>2.043369272521267</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6438560327251344</v>
+        <v>0.6759295195822865</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.216311831992781</v>
+        <v>4.271738476449117</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.829998212357701</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.605273978901486</v>
+        <v>-4.574210177953437</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.987532196483359</v>
+        <v>2.036140269204623</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6438560327251344</v>
+        <v>0.6759295195822865</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.216311831992781</v>
+        <v>4.271738476449117</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.790250125951168</v>
+        <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.836447772778118</v>
+        <v>-4.805383971830069</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.855314592526173</v>
+        <v>1.903922665247436</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6438560327251344</v>
+        <v>0.6759295195822865</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.176563745586249</v>
+        <v>4.231990390042583</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.797272744948108</v>
+        <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.805161752237662</v>
+        <v>-4.774097951289614</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.874851619739295</v>
+        <v>1.923459692460558</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.6751420532655897</v>
+        <v>0.7072155401227419</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.202357976907462</v>
+        <v>4.257784621363796</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.896443744521012</v>
+        <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.652136360124378</v>
+        <v>-4.621072559176329</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.035232776157514</v>
+        <v>2.083840848878776</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.8281674453788739</v>
+        <v>0.860240932236026</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.393344211748337</v>
+        <v>4.448770856204671</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.083909969429304</v>
+        <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.680443673997648</v>
+        <v>-4.649379873049599</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.211376075516498</v>
+        <v>2.259984148237761</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.8281674453788739</v>
+        <v>0.860240932236026</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.580810436656629</v>
+        <v>4.636237081112963</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699135800903171</v>
       </c>
       <c r="C2053" t="n">
-        <v>4.053312920783386</v>
+        <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.841940097835073</v>
+        <v>-4.810876296887024</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.11618045733561</v>
+        <v>2.164788530056873</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.6666710215414492</v>
+        <v>0.6987445083986014</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.453315533708256</v>
+        <v>4.50874217816459</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.789444212357721</v>
+        <v>3.797544777223255</v>
       </c>
       <c r="C2054" t="n">
-        <v>4.300754571337287</v>
+        <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.841940097835073</v>
+        <v>-4.781514073697103</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.11618045733561</v>
+        <v>2.180209821994559</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.6666710215414492</v>
+        <v>0.7712172100541138</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.293818368323655</v>
+        <v>4.555902201819616</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240812.xlsx
+++ b/tame_output/ON/bt/strategyON_20240812.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>60.9%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>86.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>79.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.0%</t>
+          <t>109.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>124.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>94.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-48.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-74.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.8%</t>
+          <t>430.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-639.7%</t>
+          <t>-653.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-158.2%</t>
+          <t>-181.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-338.5%</t>
+          <t>-490.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-146.9%</t>
+          <t>-166.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>83.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>-20.0%</t>
         </is>
       </c>
     </row>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812099</v>
+        <v>3.684843823812098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.813393147188711</v>
+        <v>-8.696054629692815</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3431965743562881</v>
+        <v>-0.2962611673579301</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.393999021290599</v>
+        <v>-1.359442021348793</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.346117696058584</v>
+        <v>2.366851896023668</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.741259971900829</v>
+        <v>-8.623921454404934</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3086096000024994</v>
+        <v>-0.2616741930041413</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.393999021290599</v>
+        <v>-1.359442021348793</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.351851400297221</v>
+        <v>2.372585600262305</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.669893579291182</v>
+        <v>-8.552555061795287</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2898003053525056</v>
+        <v>-0.2428648983541475</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.288075628739145</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.384933973469144</v>
+        <v>2.405668173434228</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.576434545305958</v>
+        <v>-8.459096027810062</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2623001730713233</v>
+        <v>-0.2153647660729652</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.288075628739145</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.375050492156237</v>
+        <v>2.395784692121321</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.565781363752526</v>
+        <v>-8.448442846256631</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2598734609493243</v>
+        <v>-0.2129380539509662</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.288075628739145</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.373215931656863</v>
+        <v>2.393950131621947</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.467874325076036</v>
+        <v>-8.35053580758014</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.221010960452189</v>
+        <v>-0.174075553453831</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.254646878820395</v>
+        <v>-1.220089878878588</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.413707066599736</v>
+        <v>2.43444126656482</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.443920784100078</v>
+        <v>-8.326582266604182</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2107610379163121</v>
+        <v>-0.163825630917954</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.230693337844438</v>
+        <v>-1.196136337902631</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.428747697330804</v>
+        <v>2.449481897295888</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.179860845777281</v>
+        <v>-8.062522328281386</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1183973787489458</v>
+        <v>-0.07146197175058777</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.9666333995216414</v>
+        <v>-0.9320763995798345</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.57392334416273</v>
+        <v>2.594657544127814</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.472781222272443</v>
+        <v>-7.355442704776547</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1616474369926886</v>
+        <v>0.2085828439910467</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.9666333995216414</v>
+        <v>-0.9320763995798345</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.571136310502429</v>
+        <v>2.591870510467513</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.432596923906252</v>
+        <v>-7.315258406410357</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1780647802270061</v>
+        <v>0.2250001872253642</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9264491011554506</v>
+        <v>-0.8918921012136437</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.595590513409984</v>
+        <v>2.616324713375068</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.26919705296689</v>
+        <v>-7.151858535470994</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.242791549823508</v>
+        <v>0.2897269568218661</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.7630492302160882</v>
+        <v>-0.7284922302742812</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.692997257194359</v>
+        <v>2.713731457159443</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.035715830737291</v>
+        <v>-6.918377313241396</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3441084675532</v>
+        <v>0.3910438745515581</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5295680079864896</v>
+        <v>-0.4950110080446827</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.841010419369971</v>
+        <v>2.861744619335055</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.886049439729776</v>
+        <v>-6.768710922233881</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4010828136432467</v>
+        <v>0.4480182206416048</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4366645167439537</v>
+        <v>-0.4021075168021467</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.893860303802533</v>
+        <v>2.914594503767617</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.75377396609889</v>
+        <v>-6.636435448602994</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4493604898426287</v>
+        <v>0.4962958968409867</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.304389043113067</v>
+        <v>-0.2698320431712601</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.968593074728092</v>
+        <v>2.989327274693176</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.598035633539148</v>
+        <v>-6.480697116043252</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.514470883554162</v>
+        <v>0.5614062905525201</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1486507105533255</v>
+        <v>-0.1140937106115185</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.064851134951573</v>
+        <v>3.085585334916658</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.513070966809828</v>
+        <v>-6.395732449313932</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5613630914695489</v>
+        <v>0.608298498467907</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.06368604382400589</v>
+        <v>-0.02912904388219895</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.128736276212824</v>
+        <v>3.149470476177908</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.618660956582932</v>
+        <v>-6.501322439087037</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3911511659610882</v>
+        <v>0.4380865729594463</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1692760335971102</v>
+        <v>-0.1347190336553033</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.937406352749742</v>
+        <v>2.958140552714827</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.550426371957505</v>
+        <v>-6.433087854461609</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4669893416883455</v>
+        <v>0.5139247486867036</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1508607107245742</v>
+        <v>-0.1163037107827673</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.99699988835035</v>
+        <v>3.017734088315435</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.419499039716699</v>
+        <v>-6.28514781305401</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3994813518965001</v>
+        <v>0.4532218425615757</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.09846630795886496</v>
+        <v>-0.09598279487420974</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.908557607321609</v>
+        <v>2.910047715172402</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.366529517462711</v>
+        <v>-6.232178290800022</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4119551745446173</v>
+        <v>0.4656956652096929</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.04549678570487609</v>
+        <v>-0.04301327262022087</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.931625334420524</v>
+        <v>2.933115442271317</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.20074132150242</v>
+        <v>-6.066390094839731</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4713098408336407</v>
+        <v>0.5250503314987163</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.04549678570487609</v>
+        <v>-0.04301327262022087</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.924664722325431</v>
+        <v>2.926154830176224</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.167378115023651</v>
+        <v>-6.033026888360962</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.499117477806291</v>
+        <v>0.5528579684713666</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.04549678570487609</v>
+        <v>-0.04301327262022087</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.939127076706574</v>
+        <v>2.940617184557367</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.05911897790113</v>
+        <v>-5.92476775123844</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5369532531144947</v>
+        <v>0.5906937437795707</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.04549678570487609</v>
+        <v>-0.04301327262022087</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.933659197165769</v>
+        <v>2.935149305016562</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.935827843083999</v>
+        <v>-5.80147661642131</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5837678010519243</v>
+        <v>0.6375082917169999</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.07779434911225441</v>
+        <v>0.08027786219690963</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.005131972066624</v>
+        <v>3.006622079917417</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.883130975952708</v>
+        <v>-5.748779749290018</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6125475261417659</v>
+        <v>0.6662880168068415</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.1304912162435456</v>
+        <v>0.1329747293282008</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.044451070582724</v>
+        <v>3.045941178433517</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.639365533969263</v>
+        <v>-5.505014307306574</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7058344112821944</v>
+        <v>0.75957490194727</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.1304912162435456</v>
+        <v>0.1329747293282008</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.040231778929774</v>
+        <v>3.041721886780568</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.549589861592791</v>
+        <v>-5.415238634930102</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7438689941527992</v>
+        <v>0.7976094848178747</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1920906611578556</v>
+        <v>0.1945741742425108</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.079315759798376</v>
+        <v>3.08080586764917</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.299739467643716</v>
+        <v>-5.165388240981027</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8365512267161312</v>
+        <v>0.8902917173812068</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1920906611578556</v>
+        <v>0.1945741742425108</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.072057834782079</v>
+        <v>3.073547942632872</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.123847375176284</v>
+        <v>-4.989496148513595</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9105071872237525</v>
+        <v>0.9642476778888283</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1920906611578556</v>
+        <v>0.1945741742425108</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.075656958302727</v>
+        <v>3.077147066153521</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.952400912153821</v>
+        <v>-4.818049685491132</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9924132784872917</v>
+        <v>1.046153769152367</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.3635371241803187</v>
+        <v>0.366020637264974</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.191852342170759</v>
+        <v>3.193342450021552</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.878111346415482</v>
+        <v>-4.743760119752793</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.021149582398924</v>
+        <v>1.074890073064</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.437826689918658</v>
+        <v>0.4403102030033132</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.235446559230059</v>
+        <v>3.236936667080852</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.814475604181547</v>
+        <v>-4.680124377518858</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.051298680346815</v>
+        <v>1.105039171011891</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.5014624321525926</v>
+        <v>0.5039459452372478</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.278322805624737</v>
+        <v>3.279812913475531</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.703048844855627</v>
+        <v>-4.568697618192938</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.077063642860979</v>
+        <v>1.130804133526055</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.5014624321525926</v>
+        <v>0.5039459452372478</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.259517064408533</v>
+        <v>3.261007172259326</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.713551467920916</v>
+        <v>-4.579200241258227</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.074605670259741</v>
+        <v>1.128346160924817</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4909598090873037</v>
+        <v>0.493443322171959</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.254958567194237</v>
+        <v>3.25644867504503</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.641308899749721</v>
+        <v>-4.506957673087032</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.107432011363039</v>
+        <v>1.161172502028115</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4909598090873037</v>
+        <v>0.493443322171959</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.258887881029057</v>
+        <v>3.260377988879851</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.623595212871856</v>
+        <v>-4.489243986209167</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.115196070031525</v>
+        <v>1.168936560696601</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4941411379842205</v>
+        <v>0.4966246510688758</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.261475262284547</v>
+        <v>3.26296537013534</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.514790327392129</v>
+        <v>-4.38043910072944</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.155716095443409</v>
+        <v>1.209456586108485</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4941411379842205</v>
+        <v>0.4966246510688758</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.258473333504541</v>
+        <v>3.259963441355334</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.294769529355118</v>
+        <v>-4.160418302692429</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.245303451668828</v>
+        <v>1.299043942333904</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.6353609830522008</v>
+        <v>0.637844496136856</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.344784277555943</v>
+        <v>3.346274385406736</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.161901840291841</v>
+        <v>-4.027550613629152</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.314344710095962</v>
+        <v>1.368085200761038</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.6353609830522008</v>
+        <v>0.637844496136856</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.360678460357767</v>
+        <v>3.36216856820856</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.041728756927342</v>
+        <v>-3.907377530264653</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.363559787882064</v>
+        <v>1.417300278547139</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7555340664166997</v>
+        <v>0.758017579501355</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.433928154816768</v>
+        <v>3.435418262667561</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.906475395597365</v>
+        <v>-3.772124168934676</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.427749234975494</v>
+        <v>1.48148972564057</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8907874277466769</v>
+        <v>0.8932709408313321</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.525168274176194</v>
+        <v>3.526658382026987</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.966350222955057</v>
+        <v>-3.831998996292368</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.389836795433843</v>
+        <v>1.443577286098919</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.8309126003889847</v>
+        <v>0.83339611347364</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.475280869163004</v>
+        <v>3.476770977013798</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.84652999204422</v>
+        <v>-3.712178765381531</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.453054057032387</v>
+        <v>1.506794547697462</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.8309126003889847</v>
+        <v>0.83339611347364</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.490570038397213</v>
+        <v>3.492060146248006</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.848999698506026</v>
+        <v>-3.714648471843337</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.359710373770106</v>
+        <v>1.413450864435181</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.8284428939271786</v>
+        <v>0.8309264070118338</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.396732413842571</v>
+        <v>3.398222521693364</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.917369884830036</v>
+        <v>-3.783018658167347</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.251624160725803</v>
+        <v>1.305364651390879</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8377185929633936</v>
+        <v>0.8402021060480488</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.321559694749601</v>
+        <v>3.323049802600394</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.969840912514969</v>
+        <v>-3.796806711014393</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.221072458283721</v>
+        <v>1.290286138883951</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8377185929633936</v>
+        <v>0.8402021060480488</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.311996403381492</v>
+        <v>3.313486511232286</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.025360988407558</v>
+        <v>-3.852326786906983</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.335895264618888</v>
+        <v>1.405108945219118</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8377185929633936</v>
+        <v>0.8402021060480488</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.449027240073695</v>
+        <v>3.450517347924488</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.849886728615088</v>
+        <v>-3.676852527114514</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.410652200527664</v>
+        <v>1.479865881127894</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8377185929633936</v>
+        <v>0.8402021060480488</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.453594472065483</v>
+        <v>3.455084579916276</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.960822981256337</v>
+        <v>-3.787788779755762</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.342019728232371</v>
+        <v>1.411233408832601</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8377185929633936</v>
+        <v>0.8402021060480488</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.42933650082669</v>
+        <v>3.430826608677483</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.927159435784055</v>
+        <v>-3.75412523428348</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.284023459822734</v>
+        <v>1.353237140422964</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8713821384356755</v>
+        <v>0.8738656515203307</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.378072941511509</v>
+        <v>3.379563049362302</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.867306816580332</v>
+        <v>-3.694272615079757</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.318136893936355</v>
+        <v>1.387350574536585</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8713821384356755</v>
+        <v>0.8738656515203307</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.388245327943641</v>
+        <v>3.389735435794434</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.781063353553955</v>
+        <v>-3.60802915205338</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.347580549720767</v>
+        <v>1.416794230320997</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8713821384356755</v>
+        <v>0.8738656515203307</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.383191598517501</v>
+        <v>3.384681706368295</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.826370172952934</v>
+        <v>-3.65333597145236</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.3212335974057</v>
+        <v>1.39044727800593</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.8305719754264447</v>
+        <v>0.8330554885110999</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.350481276156488</v>
+        <v>3.351971384007281</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.855403277655236</v>
+        <v>-3.682369076154661</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.310172228557881</v>
+        <v>1.379385909158111</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.8305719754264447</v>
+        <v>0.8330554885110999</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.35103314918959</v>
+        <v>3.352523257040383</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.762592796204377</v>
+        <v>-3.589558594703802</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.27656911302959</v>
+        <v>1.34578279362982</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.923382456877304</v>
+        <v>0.9258659699619592</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.335992129951471</v>
+        <v>3.337482237802264</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.806982265533804</v>
+        <v>-3.63394806403323</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.26068680122242</v>
+        <v>1.32990048182265</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8789929875478764</v>
+        <v>0.8814765006325316</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.311231924278415</v>
+        <v>3.312722032129209</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.923523870639147</v>
+        <v>-3.750489669138573</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.209145867692006</v>
+        <v>1.278359548292236</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7624513824425336</v>
+        <v>0.7649348955271889</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.236382669726933</v>
+        <v>3.237872777577726</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.963447965221719</v>
+        <v>-3.790413763721144</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.198667525689645</v>
+        <v>1.267881206289875</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7624513824425336</v>
+        <v>0.7649348955271889</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.2418739655576</v>
+        <v>3.243364073408393</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.991228363123072</v>
+        <v>-3.818194161622497</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.199052568297643</v>
+        <v>1.268266248897872</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7346709845411805</v>
+        <v>0.7371544976258357</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.236702928585327</v>
+        <v>3.23819303643612</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.10960903585321</v>
+        <v>-3.936574834352636</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9900560192062406</v>
+        <v>1.05926969980647</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6674531323902043</v>
+        <v>0.6699366454748595</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.034727937295395</v>
+        <v>3.036218045146188</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.218223114296541</v>
+        <v>-4.045188912795966</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.066760048548114</v>
+        <v>1.135973729148344</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6674531323902043</v>
+        <v>0.6699366454748595</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.1548775980146</v>
+        <v>3.156367705865394</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.182814076048398</v>
+        <v>-4.009779874547823</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.095436689949694</v>
+        <v>1.164650370549924</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6674531323902043</v>
+        <v>0.6699366454748595</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.169390624116923</v>
+        <v>3.170880731967717</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.144430413490247</v>
+        <v>-3.971396211989672</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.108209596315323</v>
+        <v>1.177423276915553</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7058367949483555</v>
+        <v>0.7083203080330107</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.189840262994183</v>
+        <v>3.191330370844976</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.967314083455081</v>
+        <v>-3.794279881954506</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.175785157174691</v>
+        <v>1.244998837774921</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7058367949483555</v>
+        <v>0.7083203080330107</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.186569291839485</v>
+        <v>3.188059399690278</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.012406328288627</v>
+        <v>-3.839372126788052</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.158431651003186</v>
+        <v>1.227645331603416</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6439407517789657</v>
+        <v>0.6464242648636209</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.150115057699764</v>
+        <v>3.151605165550557</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.833030907049859</v>
+        <v>-3.659996705549284</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.223968794805108</v>
+        <v>1.293182475405338</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8007175099496844</v>
+        <v>0.8032010230343396</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.23796808790861</v>
+        <v>3.239458195759402</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.878045120570465</v>
+        <v>-3.705010919069891</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.186770564728455</v>
+        <v>1.255984245328685</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7703686146350798</v>
+        <v>0.772852127719735</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.200566206051437</v>
+        <v>3.20205631390223</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.145049630842901</v>
+        <v>-3.972015429342326</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.085660322958427</v>
+        <v>1.154874003558656</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5760055765921313</v>
+        <v>0.5784890896767865</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.089639945564613</v>
+        <v>3.091130053415406</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.246247412280074</v>
+        <v>-4.073213210779499</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.044385132280059</v>
+        <v>1.113598812880289</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5075967630468121</v>
+        <v>0.5100802761314673</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.047798579333923</v>
+        <v>3.049288687184716</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.239736445665761</v>
+        <v>-4.066702244165186</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.044589480480101</v>
+        <v>1.113803161080331</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5075967630468121</v>
+        <v>0.5100802761314673</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.04539854088824</v>
+        <v>3.046888648739033</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.220698317958464</v>
+        <v>-4.047664116457889</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.048729450771265</v>
+        <v>1.117943131371494</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4494131517156176</v>
+        <v>0.4518966648002728</v>
       </c>
       <c r="G1962" t="n">
-        <v>3.007013093297768</v>
+        <v>3.008503201148561</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.273214120233284</v>
+        <v>-4.100179918732709</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.147017531495527</v>
+        <v>1.216231212095757</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4494131517156176</v>
+        <v>0.4518966648002728</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.126307494931958</v>
+        <v>3.127797602782751</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.287080881567202</v>
+        <v>-4.114046680066627</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.142304155948093</v>
+        <v>1.211517836548323</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4115552349817946</v>
+        <v>0.4140387480664499</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.104426073877798</v>
+        <v>3.105916181728591</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.242276710027272</v>
+        <v>-4.069242508526697</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.166234354960991</v>
+        <v>1.235448035561221</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4115552349817946</v>
+        <v>0.4140387480664499</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.110434604274724</v>
+        <v>3.111924712125517</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.094533739792269</v>
+        <v>-3.921499538291695</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.123281764332192</v>
+        <v>1.192495444932421</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5793625922166779</v>
+        <v>0.5818461053013331</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.109069239892853</v>
+        <v>3.110559347743647</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.178354961066968</v>
+        <v>-4.005320759566393</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.092546897353793</v>
+        <v>1.161760577954023</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5793625922166779</v>
+        <v>0.5818461053013331</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.111862861424334</v>
+        <v>3.113352969275128</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.172202255014184</v>
+        <v>-3.999168053513609</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.095670328166565</v>
+        <v>1.164884008766795</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5855152982694621</v>
+        <v>0.5879988113541174</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.116216833447663</v>
+        <v>3.117706941298457</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.189011553164685</v>
+        <v>-4.015977351664111</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.088027085646475</v>
+        <v>1.157240766246705</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5687060001189606</v>
+        <v>0.5711895132036158</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.105211731297473</v>
+        <v>3.106701839148266</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.126713554388563</v>
+        <v>-3.953679352887989</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.179281838953744</v>
+        <v>1.248495519553974</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.6140002643934026</v>
+        <v>0.6164837774780578</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.198723843658959</v>
+        <v>3.200213951509752</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.924923356723405</v>
+        <v>-3.90869512764662</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.062289919733935</v>
+        <v>1.068781211364649</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.812018456562557</v>
+        <v>0.6920567865077165</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.119826760674579</v>
+        <v>3.047849758641674</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.9758100694096</v>
+        <v>-3.959581840332814</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.112225466981632</v>
+        <v>1.118716758612346</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7611317438763625</v>
+        <v>0.641170073821522</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.159584965385037</v>
+        <v>3.087607963352133</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.889199326759793</v>
+        <v>-3.872971097683007</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.161497500157599</v>
+        <v>1.167988791788313</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8397574750815208</v>
+        <v>0.7197958050266803</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.221388140224176</v>
+        <v>3.149411138191271</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.949408624765077</v>
+        <v>-3.933180395688292</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.135949761780156</v>
+        <v>1.142441053410871</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7795481770762362</v>
+        <v>0.6595865070213958</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.183798542245677</v>
+        <v>3.111821540212772</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.87298657833315</v>
+        <v>-3.856758349256365</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.165010198392856</v>
+        <v>1.17150149002357</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7795481770762362</v>
+        <v>0.6595865070213958</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.182290160285605</v>
+        <v>3.110313158252701</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.828613446694582</v>
+        <v>-3.812385217617796</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.182622318483719</v>
+        <v>1.189113610114434</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8239213087148048</v>
+        <v>0.7039596386599644</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.208776906704182</v>
+        <v>3.136799904671278</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.851093797553466</v>
+        <v>-3.834865568476681</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.168023972278756</v>
+        <v>1.17451526390947</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8239213087148048</v>
+        <v>0.7039596386599644</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.203170700842773</v>
+        <v>3.131193698809869</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.803438066992411</v>
+        <v>-3.787209837915626</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.193468021530983</v>
+        <v>1.199959313161697</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8715770392758605</v>
+        <v>0.75161536922102</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.238145896207211</v>
+        <v>3.166168894174307</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.702919908493656</v>
+        <v>-3.686691679416871</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.23856765830521</v>
+        <v>1.245058949935924</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9720951977746151</v>
+        <v>0.8521335277197746</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.303349164681189</v>
+        <v>3.231372162648285</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.687014579061303</v>
+        <v>-3.670786349984518</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.231684462554023</v>
+        <v>1.238175754184737</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8929825370653761</v>
+        <v>0.7730208670105356</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.242636240731517</v>
+        <v>3.170659238698613</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.642176177452905</v>
+        <v>-3.62594794837612</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.253717525808011</v>
+        <v>1.260208817438725</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8975259700102456</v>
+        <v>0.7775642999554051</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.249460003109068</v>
+        <v>3.177483001076164</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.661674633694914</v>
+        <v>-3.645446404618129</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.250079082942285</v>
+        <v>1.256570374572999</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8494413287303413</v>
+        <v>0.7294796586755008</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.224770157972203</v>
+        <v>3.152793155939299</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.617471796609013</v>
+        <v>-3.601243567532228</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.273639820304483</v>
+        <v>1.280131111935197</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8936441658162417</v>
+        <v>0.7736824957614012</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.257171462751581</v>
+        <v>3.185194460718676</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.62503146244606</v>
+        <v>-3.608803233369275</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.269025954438912</v>
+        <v>1.275517246069626</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.948447569826061</v>
+        <v>0.8284858997712206</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.28846350562672</v>
+        <v>3.216486503593815</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.466740044906788</v>
+        <v>-3.450511815830003</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.38359028663766</v>
+        <v>1.390081578268374</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.948447569826061</v>
+        <v>0.8284858997712206</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.339711270809759</v>
+        <v>3.267734268776855</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.259098041272312</v>
+        <v>-3.242869812195527</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.465087792685704</v>
+        <v>1.471579084316418</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.156089573460537</v>
+        <v>1.036127903405697</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.462737177584698</v>
+        <v>3.390760175551794</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.208065948549784</v>
+        <v>-3.191837719472999</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.480448858012985</v>
+        <v>1.486940149643699</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.207121666183065</v>
+        <v>1.087159996128225</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.488304661456485</v>
+        <v>3.416327659423581</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.142841767422578</v>
+        <v>-3.126613538345793</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.523725934556572</v>
+        <v>1.530217226187286</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.272345847310271</v>
+        <v>1.15238417725543</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.544626574225513</v>
+        <v>3.472649572192609</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.105414747351444</v>
+        <v>-3.089186518274659</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.534657714884306</v>
+        <v>1.54114900651502</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.277597385339452</v>
+        <v>1.157635715284612</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.543738469342303</v>
+        <v>3.471761467309398</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.125526403386152</v>
+        <v>-3.109298174309367</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.527869844801663</v>
+        <v>1.534361136432377</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.288624730336872</v>
+        <v>1.168663060282031</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.551611668671995</v>
+        <v>3.47963466663909</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.071781588958947</v>
+        <v>-3.055553359882162</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.709925541593756</v>
+        <v>1.71641683322447</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.298688039777334</v>
+        <v>1.178726369722493</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.718207425357482</v>
+        <v>3.646230423324578</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.996999327933935</v>
+        <v>-2.98077109885715</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.859951355221578</v>
+        <v>1.866442646852292</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.373470300802346</v>
+        <v>1.253508630747506</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.883189691190307</v>
+        <v>3.811212689157403</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.970915243670127</v>
+        <v>-2.954687014593342</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.86209296494096</v>
+        <v>1.868584256571674</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.373470300802346</v>
+        <v>1.253508630747506</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.874897667204166</v>
+        <v>3.802920665171262</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.883037330561006</v>
+        <v>-2.866809101484221</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.895437325768388</v>
+        <v>1.901928617399102</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.489395943225698</v>
+        <v>1.369434273170857</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.942646248241957</v>
+        <v>3.870669246209052</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.874144869167723</v>
+        <v>-2.857916640090938</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.916548716052493</v>
+        <v>1.923040007683206</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.489395943225698</v>
+        <v>1.369434273170857</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.960200653968748</v>
+        <v>3.888223651935844</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.042620986137601</v>
+        <v>-3.026392757060816</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.841013316669125</v>
+        <v>1.847504608299839</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.461448107509117</v>
+        <v>1.341486437454276</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.935286999943383</v>
+        <v>3.863309997910479</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.344821457276018</v>
+        <v>-2.328593228199233</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.101402825401621</v>
+        <v>2.107894117032334</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.391100048138706</v>
+        <v>1.271138378083866</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.874347861508999</v>
+        <v>3.802370859476095</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.322100353592865</v>
+        <v>-2.30587212451608</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.101155289371786</v>
+        <v>2.1076465810025</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.391100048138706</v>
+        <v>1.271138378083866</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.865011884005903</v>
+        <v>3.793034881972999</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.451302166886907</v>
+        <v>-2.435073937810122</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.208380689905338</v>
+        <v>2.214871981536052</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.261898234844664</v>
+        <v>1.141936564789823</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.946396921880647</v>
+        <v>3.874419919847742</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.606083173665163</v>
+        <v>-2.589854944588378</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.183546109687683</v>
+        <v>2.190037401318397</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.228530560790188</v>
+        <v>1.108568890735347</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.963454139941608</v>
+        <v>3.891477137908704</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.599028483449989</v>
+        <v>-2.582800254373204</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.183043341763297</v>
+        <v>2.189534633394011</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.235585251005362</v>
+        <v>1.115623580950521</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.964362310060257</v>
+        <v>3.892385308027353</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.572077259123501</v>
+        <v>-2.555849030046716</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.203829985138634</v>
+        <v>2.210321276769348</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.250465597033081</v>
+        <v>1.13050392697824</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.98329667132163</v>
+        <v>3.911319669288726</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.417120445246741</v>
+        <v>3.26630790447962</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.708030267179818</v>
+        <v>-2.691802038103033</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.333551914061067</v>
+        <v>2.18923066492466</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.250465597033081</v>
+        <v>1.13050392697824</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.16739980346659</v>
+        <v>3.944610260666565</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.409237140149735</v>
+        <v>3.258424599382614</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.73043838498469</v>
+        <v>-2.714210155907905</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.316705361842112</v>
+        <v>2.172384112705704</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.250465597033081</v>
+        <v>1.13050392697824</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.159516498369583</v>
+        <v>3.936726955569558</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.411291139699372</v>
+        <v>3.260478598932251</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.75866262056229</v>
+        <v>-2.742434391485505</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.307469667160709</v>
+        <v>2.163148418024302</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.268442349484389</v>
+        <v>1.148480679429549</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.172356549390006</v>
+        <v>3.94956700658998</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.467544857421219</v>
+        <v>3.316732316654098</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.76810354645082</v>
+        <v>-2.751875317374035</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.359947014527144</v>
+        <v>2.215625765390737</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.390869467027781</v>
+        <v>1.27090779697294</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.302066537637888</v>
+        <v>4.079276994837863</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.47043595196652</v>
+        <v>3.319623411199399</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.820377153786461</v>
+        <v>-2.804148924709676</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.341928666138188</v>
+        <v>2.197607417001781</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.338595859692139</v>
+        <v>1.218634189637299</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.273593467781804</v>
+        <v>4.050803924981778</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347704</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.468547764860295</v>
+        <v>3.317735224093174</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.896707131387367</v>
+        <v>-2.880478902310582</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.309508487991601</v>
+        <v>2.165187238855194</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.338595859692139</v>
+        <v>1.218634189637299</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.27170528067558</v>
+        <v>4.048915737875554</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.463367994463157</v>
+        <v>3.312555453696036</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.098960851711721</v>
+        <v>-3.082732622634936</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.223427229464722</v>
+        <v>2.079105980328315</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.136342139367786</v>
+        <v>1.016380469312945</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.14517327808383</v>
+        <v>3.922383735283804</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.46180200467331</v>
+        <v>3.310989463906189</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.260529277238976</v>
+        <v>-3.244301048162191</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.157233869463972</v>
+        <v>2.012912620327565</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.009559215569907</v>
+        <v>0.8895975455150661</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.067537534015254</v>
+        <v>3.844747991215229</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.75459613538935</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.474875411539228</v>
+        <v>3.324062870772107</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.392830569336529</v>
+        <v>-3.376602340259744</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.11738675949087</v>
+        <v>1.973065510354463</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.009559215569907</v>
+        <v>0.8895975455150661</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.080610940881173</v>
+        <v>3.857821398081147</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749882691378392</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.466880608322168</v>
+        <v>3.316068067555047</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.578698880175759</v>
+        <v>-3.562470651098974</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.035044631938117</v>
+        <v>1.89072338280171</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.850993622249959</v>
+        <v>0.7310319521951184</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.977476781672144</v>
+        <v>3.754687238872119</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.46540464944917</v>
+        <v>3.314592108682049</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.606599667285232</v>
+        <v>-3.590371438208447</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.02240835822133</v>
+        <v>1.878087109084923</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8163966981070242</v>
+        <v>0.6964350280521836</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.955242668313385</v>
+        <v>3.73245312551336</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.462169093426369</v>
+        <v>3.311356552659248</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.729125769988126</v>
+        <v>-3.712897540911341</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.970162361117372</v>
+        <v>1.825841111980965</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6938705954041303</v>
+        <v>0.5739089253492897</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.878491450668847</v>
+        <v>3.655701907868822</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.528875053016873</v>
+        <v>3.378062512249752</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.959640266173714</v>
+        <v>-3.943412037096929</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.94466252223364</v>
+        <v>1.800341273097233</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4633560992185416</v>
+        <v>0.343394429163701</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.806888712547998</v>
+        <v>3.584099169747973</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.66918677201872</v>
+        <v>3.518374231251599</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.216361084168538</v>
+        <v>-4.200132855091754</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.982285914037558</v>
+        <v>1.83796466490115</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3549415250747268</v>
+        <v>0.2349798550198862</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.882151687063556</v>
+        <v>3.659362144263531</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.73816704116436</v>
+        <v>3.587354500397239</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.370347501944678</v>
+        <v>-4.354119272867894</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.989671616072741</v>
+        <v>1.845350366936334</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3549415250747268</v>
+        <v>0.2349798550198862</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.951131956209196</v>
+        <v>3.72834241340917</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.724218243284481</v>
+        <v>3.57340570251736</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.319825598117013</v>
+        <v>-4.303597369040228</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.995931579723928</v>
+        <v>1.851610330587521</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3549415250747268</v>
+        <v>0.2349798550198862</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.937183158329317</v>
+        <v>3.714393615529291</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.736088732339895</v>
+        <v>3.585276191572774</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.572300752124737</v>
+        <v>-4.556072523047953</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.906812007176252</v>
+        <v>1.762490758039845</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3549415250747268</v>
+        <v>0.2349798550198862</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.949053647384731</v>
+        <v>3.726264104584705</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.737299266858838</v>
+        <v>3.586486726091717</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.865196508604149</v>
+        <v>-4.848968279527365</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.790864239103431</v>
+        <v>1.646542989967024</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3549415250747268</v>
+        <v>0.2349798550198862</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.950264181903675</v>
+        <v>3.727474639103649</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.74142100908616</v>
+        <v>3.590608468319039</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.022740580333591</v>
+        <v>-5.006512351256807</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.731968352638976</v>
+        <v>1.587647103502569</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2880397199344523</v>
+        <v>0.1680780498796117</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.914244841046831</v>
+        <v>3.691455298246806</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.736498861822349</v>
+        <v>3.585686321055228</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.300704975916864</v>
+        <v>-5.28447674684008</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.615860447141856</v>
+        <v>1.471539198005449</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.198419985648968</v>
+        <v>0.07845831559412741</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.85555085321173</v>
+        <v>3.632761310411705</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.898702918521393</v>
+        <v>3.747890377754272</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.417672668555755</v>
+        <v>-5.401444439478971</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.731277426785344</v>
+        <v>1.586956177648937</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.198419985648968</v>
+        <v>0.07845831559412741</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.017754909910774</v>
+        <v>3.794965367110749</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.893549556485207</v>
+        <v>3.742737015718086</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.502390610776708</v>
+        <v>-5.486162381699924</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.692236887860777</v>
+        <v>1.54791563872437</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1133039567209216</v>
+        <v>-0.006657713333918958</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.961531930517761</v>
+        <v>3.738742387717735</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.903778974053699</v>
+        <v>3.752966433286578</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.584325429045592</v>
+        <v>-5.568097199968808</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.669692378121715</v>
+        <v>1.525371128985307</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1033692111338415</v>
+        <v>-0.01659245892099914</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.965800500734003</v>
+        <v>3.743010957933978</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.912704612509601</v>
+        <v>3.76189207174248</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.686301551293999</v>
+        <v>-5.670073322217215</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.637827567678254</v>
+        <v>1.493506318541847</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.00139308888543388</v>
+        <v>-0.1185685811694067</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.913540465840861</v>
+        <v>3.690750923040836</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.904857499753776</v>
+        <v>3.754044958986655</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.576295267816778</v>
+        <v>-5.560067038739994</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.673982968313318</v>
+        <v>1.529661719176911</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.02459766080270909</v>
+        <v>-0.09536400925213151</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.919616096235402</v>
+        <v>3.696826553435377</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.909107510475751</v>
+        <v>3.75829496970863</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.433235692075852</v>
+        <v>-5.417007462999068</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.735456809331662</v>
+        <v>1.591135560195255</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.03261108739268836</v>
+        <v>-0.08735058266215223</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.928674162911364</v>
+        <v>3.705884620111338</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.916368393358287</v>
+        <v>3.765555852591166</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.131788966604015</v>
+        <v>-5.115560737527231</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.863296382402933</v>
+        <v>1.718975133266526</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3340578128645256</v>
+        <v>0.214096142809685</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.116803081077002</v>
+        <v>3.894013538276977</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.917339571110997</v>
+        <v>3.766527030343876</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.156379210839199</v>
+        <v>-5.140150981762415</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.85443146246157</v>
+        <v>1.710110213325163</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3340578128645256</v>
+        <v>0.214096142809685</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.117774258829713</v>
+        <v>3.894984716029688</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.918182475490752</v>
+        <v>3.767369934723632</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.105340834832679</v>
+        <v>-5.089112605755894</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.875689717243934</v>
+        <v>1.731368468107527</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3340578128645256</v>
+        <v>0.214096142809685</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.118617163209468</v>
+        <v>3.895827620409443</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.937220574364898</v>
+        <v>3.786408033597777</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.064201539966048</v>
+        <v>-5.047973310889263</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.911183534064731</v>
+        <v>1.766862284928325</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3751971077311564</v>
+        <v>0.2552354376763158</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.162338839003592</v>
+        <v>3.939549296203567</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700479</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.753404570488832</v>
+        <v>3.602592029721712</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.953595399886446</v>
+        <v>-4.937367170809662</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.771609986220507</v>
+        <v>1.6272887370841</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4858032478107585</v>
+        <v>0.3658415777559179</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.044886519175288</v>
+        <v>3.822096976375263</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.756906614562796</v>
+        <v>3.606094073795676</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.084176134417288</v>
+        <v>-5.067947905340504</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.722879736482133</v>
+        <v>1.578558487345727</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3552225132799159</v>
+        <v>0.2352608432250753</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.970040122530746</v>
+        <v>3.747250579730721</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.741333433638879</v>
+        <v>3.590520892871758</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.919679800226326</v>
+        <v>-4.903451571149542</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.773105089234601</v>
+        <v>1.628783840098194</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3552225132799159</v>
+        <v>0.2352608432250753</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.954466941606828</v>
+        <v>3.731677398806804</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.740521144075308</v>
+        <v>3.589708603308188</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.947049732910759</v>
+        <v>-4.930821503833974</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.761344826597258</v>
+        <v>1.617023577460851</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3552225132799159</v>
+        <v>0.2352608432250753</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.953654652043258</v>
+        <v>3.730865109243234</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.750389923200381</v>
+        <v>3.599577382433261</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.957434927800648</v>
+        <v>-4.941206698723864</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.767059527766374</v>
+        <v>1.622738278629968</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3448373183900266</v>
+        <v>0.224875648335186</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.957292314234397</v>
+        <v>3.734502771434372</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735283</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.821226928976806</v>
+        <v>3.670414388209686</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.976023086522873</v>
+        <v>-4.959794857446089</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.83046127005391</v>
+        <v>1.686140020917503</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3262491596678013</v>
+        <v>0.2062874896129607</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.016976424777487</v>
+        <v>3.794186881977462</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.818095939795104</v>
+        <v>3.667283399027984</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.976321633218909</v>
+        <v>-4.960093404142125</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.827210862193794</v>
+        <v>1.682889613057387</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3262491596678013</v>
+        <v>0.2062874896129607</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.013845435595785</v>
+        <v>3.791055892795761</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108858</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.822626834734496</v>
+        <v>3.671814293967376</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.875498499528481</v>
+        <v>-4.859270270451697</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.872071010609356</v>
+        <v>1.72774976147295</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3387133751521551</v>
+        <v>0.2187517050973145</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.025854859825789</v>
+        <v>3.803065317025764</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.822756088213039</v>
+        <v>3.671943547445919</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.684717138776074</v>
+        <v>-4.66848890969929</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.948512808388862</v>
+        <v>1.804191559252456</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5294947359045625</v>
+        <v>0.4095330658497219</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.140452929755777</v>
+        <v>3.917663386955752</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.802592933950636</v>
+        <v>3.651780393183516</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.666200284734254</v>
+        <v>-4.64997205565747</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.935756395743187</v>
+        <v>1.79143514660678</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5424248653297707</v>
+        <v>0.4224631952749301</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.128047853148498</v>
+        <v>3.905258310348474</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912985</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.837559870562694</v>
+        <v>3.686747329795574</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.641007100232936</v>
+        <v>-4.624778871156152</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.980800606155773</v>
+        <v>1.836479357019366</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.5676180498310891</v>
+        <v>0.4476563797762484</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.178130700461348</v>
+        <v>3.955341157661323</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.831246438464132</v>
+        <v>3.680433897697012</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.628952973319973</v>
+        <v>-4.612724744243189</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.979308824822395</v>
+        <v>1.834987575685989</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.5796721767440519</v>
+        <v>0.4597105066892113</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.179049744510563</v>
+        <v>3.956260201710538</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811009</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.833127068648268</v>
+        <v>3.682314527881148</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.635576220010331</v>
+        <v>-4.619347990933547</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.978540156330388</v>
+        <v>1.834218907193981</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5730489300536936</v>
+        <v>0.4530872599988529</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.176956426680484</v>
+        <v>3.954166883880459</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.84597809452615</v>
+        <v>3.69516555375903</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.532695630481738</v>
+        <v>-4.516467401404954</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.032543418019707</v>
+        <v>1.888222168883301</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6759295195822865</v>
+        <v>0.5559678495274458</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.251535806275522</v>
+        <v>4.028746263475497</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.866180764699744</v>
+        <v>3.715368223932624</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.556137669661825</v>
+        <v>-4.539909440585041</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.043369272521267</v>
+        <v>1.899048023384861</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6759295195822865</v>
+        <v>0.5559678495274458</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.271738476449117</v>
+        <v>4.048948933649092</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.866180764699744</v>
+        <v>3.715368223932624</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.574210177953437</v>
+        <v>-4.557981948876653</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.036140269204623</v>
+        <v>1.891819020068216</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6759295195822865</v>
+        <v>0.5559678495274458</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.271738476449117</v>
+        <v>4.048948933649092</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.826432678293211</v>
+        <v>3.675620137526091</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.805383971830069</v>
+        <v>-4.789155742753285</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.903922665247436</v>
+        <v>1.75960141611103</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6759295195822865</v>
+        <v>0.5559678495274458</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.231990390042583</v>
+        <v>4.009200847242559</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.833455297290151</v>
+        <v>3.682642756523031</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.774097951289614</v>
+        <v>-4.757869722212829</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.923459692460558</v>
+        <v>1.779138443324152</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.7072155401227419</v>
+        <v>0.5872538700679012</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.257784621363796</v>
+        <v>4.034995078563772</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.932626296863055</v>
+        <v>3.781813756095935</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.621072559176329</v>
+        <v>-4.604844330099545</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.083840848878776</v>
+        <v>1.93951959974237</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.860240932236026</v>
+        <v>0.7402792621811853</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.448770856204671</v>
+        <v>4.225981313404647</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.120092521771348</v>
+        <v>3.969279981004227</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.649379873049599</v>
+        <v>-4.633151643972815</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.259984148237761</v>
+        <v>2.115662899101354</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.860240932236026</v>
+        <v>0.7402792621811853</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.636237081112963</v>
+        <v>4.413447538312939</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699135800903171</v>
       </c>
       <c r="C2053" t="n">
-        <v>4.08949547312543</v>
+        <v>3.93868293235831</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.810876296887024</v>
+        <v>-4.79464806781024</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.164788530056873</v>
+        <v>2.020467280920466</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.6987445083986014</v>
+        <v>0.5787828383437607</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.50874217816459</v>
+        <v>4.285952635364566</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.797544777223255</v>
+        <v>3.889537530536817</v>
       </c>
       <c r="C2054" t="n">
-        <v>4.093171875787148</v>
+        <v>3.912889593436962</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.781514073697103</v>
+        <v>-4.920857966523712</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.180209821994559</v>
+        <v>1.94418998251373</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7712172100541138</v>
+        <v>0.5787828383437607</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.555902201819616</v>
+        <v>4.260159296443219</v>
       </c>
     </row>
   </sheetData>
